--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -190,24 +190,24 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>Russia Russian Premier League</t>
+  </si>
+  <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
-    <t>Russia Russian Premier League</t>
+    <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
@@ -229,15 +229,15 @@
     <t>Switzerland Super League</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -268,33 +268,33 @@
     <t>Neftekhimik</t>
   </si>
   <si>
+    <t>Krylya Sovetov</t>
+  </si>
+  <si>
+    <t>Jaro</t>
+  </si>
+  <si>
     <t>Vaprus</t>
   </si>
   <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Cracovia Kraków</t>
+  </si>
+  <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
-    <t>Jaro</t>
-  </si>
-  <si>
-    <t>Krylya Sovetov</t>
-  </si>
-  <si>
     <t>Znicz Pruszków</t>
   </si>
   <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Cracovia Kraków</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
     <t>Metaloglobus</t>
   </si>
   <si>
@@ -319,16 +319,31 @@
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
     <t>Stal Rzeszów</t>
   </si>
   <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
     <t>Zürich</t>
   </si>
   <si>
-    <t>Csikszereda</t>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
   </si>
   <si>
     <t>Royal Antwerp FC</t>
@@ -337,33 +352,18 @@
     <t>Athlone Town</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
     <t>Kerry</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
     <t>Sarmiento</t>
   </si>
   <si>
+    <t>Ulytau</t>
+  </si>
+  <si>
     <t>HFX Wanderers FC</t>
   </si>
   <si>
-    <t>Ulytau</t>
-  </si>
-  <si>
     <t>Deportes Limache</t>
   </si>
   <si>
@@ -385,12 +385,12 @@
     <t>FC Dallas</t>
   </si>
   <si>
+    <t>Austin II</t>
+  </si>
+  <si>
     <t>Houston Dynamo</t>
   </si>
   <si>
-    <t>Austin II</t>
-  </si>
-  <si>
     <t>Vancouver FC</t>
   </si>
   <si>
@@ -409,33 +409,33 @@
     <t>Orenburg</t>
   </si>
   <si>
+    <t>Olimpiyets</t>
+  </si>
+  <si>
+    <t>VPS</t>
+  </si>
+  <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Nieciecza</t>
+  </si>
+  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
     <t>Chrudim</t>
   </si>
   <si>
-    <t>VPS</t>
-  </si>
-  <si>
-    <t>Olimpiyets</t>
-  </si>
-  <si>
     <t>Stal Mielec</t>
   </si>
   <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Nieciecza</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
     <t>Petrolul 52</t>
   </si>
   <si>
@@ -460,16 +460,31 @@
     <t>Ludogorets</t>
   </si>
   <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
     <t>Śląsk Wrocław</t>
   </si>
   <si>
-    <t>Radomiak Radom</t>
-  </si>
-  <si>
     <t>Sion</t>
   </si>
   <si>
-    <t>Rapid Bucureşti</t>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Wexford</t>
   </si>
   <si>
     <t>Union Saint-Gilloise</t>
@@ -478,33 +493,18 @@
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Wexford</t>
-  </si>
-  <si>
     <t>Lanús</t>
   </si>
   <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
     <t>Forge FC</t>
   </si>
   <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
     <t>Ñublense</t>
   </si>
   <si>
@@ -526,10 +526,10 @@
     <t>New York City</t>
   </si>
   <si>
+    <t>Houston Dynamo FC II</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
-  </si>
-  <si>
-    <t>Houston Dynamo FC II</t>
   </si>
   <si>
     <t>Valour FC</t>
@@ -1065,52 +1065,52 @@
         <v>175</v>
       </c>
       <c r="L2">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N2">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB2">
         <v>1.57</v>
@@ -1119,22 +1119,22 @@
         <v>2.35</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ2" t="s">
         <v>177</v>
@@ -1389,7 +1389,7 @@
         <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -1413,76 +1413,76 @@
         <v>175</v>
       </c>
       <c r="L5">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="M5">
-        <v>3.47</v>
+        <v>3.59</v>
       </c>
       <c r="N5">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="O5">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q5">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R5">
+        <v>1.35</v>
+      </c>
+      <c r="S5">
+        <v>3.02</v>
+      </c>
+      <c r="T5">
+        <v>2.76</v>
+      </c>
+      <c r="U5">
+        <v>1.41</v>
+      </c>
+      <c r="V5">
+        <v>7</v>
+      </c>
+      <c r="W5">
+        <v>1.05</v>
+      </c>
+      <c r="X5">
+        <v>1.01</v>
+      </c>
+      <c r="Y5">
+        <v>11.7</v>
+      </c>
+      <c r="Z5">
         <v>1.25</v>
       </c>
-      <c r="S5">
-        <v>3.6</v>
-      </c>
-      <c r="T5">
-        <v>2.25</v>
-      </c>
-      <c r="U5">
-        <v>1.6</v>
-      </c>
-      <c r="V5">
-        <v>4.85</v>
-      </c>
-      <c r="W5">
-        <v>1.13</v>
-      </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
-      <c r="Y5">
-        <v>11.5</v>
-      </c>
-      <c r="Z5">
-        <v>1.13</v>
-      </c>
       <c r="AA5">
-        <v>4.6</v>
+        <v>3.56</v>
       </c>
       <c r="AB5">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AC5">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AD5">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="AE5">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AF5">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="AH5">
-        <v>3.8</v>
+        <v>6.1</v>
       </c>
       <c r="AI5">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AJ5" t="s">
         <v>177</v>
@@ -1505,7 +1505,7 @@
         <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>85</v>
@@ -1529,76 +1529,76 @@
         <v>175</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ6" t="s">
         <v>177</v>
@@ -1618,10 +1618,10 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
         <v>86</v>
@@ -1645,76 +1645,76 @@
         <v>175</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ7" t="s">
         <v>177</v>
@@ -1734,10 +1734,10 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -1761,76 +1761,76 @@
         <v>175</v>
       </c>
       <c r="L8">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="s">
         <v>177</v>
@@ -1850,7 +1850,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
         <v>80</v>
@@ -1877,76 +1877,76 @@
         <v>175</v>
       </c>
       <c r="L9">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="M9">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="N9">
-        <v>3.39</v>
+        <v>3.78</v>
       </c>
       <c r="O9">
         <v>1.67</v>
       </c>
       <c r="P9">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S9">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="T9">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="U9">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC9">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AD9">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AH9">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="s">
         <v>177</v>
@@ -1966,7 +1966,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
         <v>80</v>
@@ -1993,13 +1993,13 @@
         <v>175</v>
       </c>
       <c r="L10">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
         <v>80</v>
@@ -2198,7 +2198,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
         <v>80</v>
@@ -2225,13 +2225,13 @@
         <v>175</v>
       </c>
       <c r="L12">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2273,10 +2273,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
         <v>80</v>
@@ -2341,13 +2341,13 @@
         <v>175</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2359,58 +2359,58 @@
         <v>0</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ13" t="s">
         <v>177</v>
@@ -2576,10 +2576,10 @@
         <v>1.84</v>
       </c>
       <c r="M15">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="N15">
-        <v>4.94</v>
+        <v>4.88</v>
       </c>
       <c r="O15">
         <v>1.6</v>
@@ -2591,46 +2591,46 @@
         <v>3.18</v>
       </c>
       <c r="R15">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S15">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="T15">
-        <v>3.56</v>
+        <v>3.34</v>
       </c>
       <c r="U15">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="Z15">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AA15">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="AB15">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="AC15">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AD15">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AE15">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
         <v>2.25</v>
@@ -2639,10 +2639,10 @@
         <v>1.58</v>
       </c>
       <c r="AH15">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI15">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="s">
         <v>177</v>
@@ -2689,13 +2689,13 @@
         <v>175</v>
       </c>
       <c r="L16">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="M16">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N16">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="O16">
         <v>1.71</v>
@@ -2707,58 +2707,58 @@
         <v>2.4</v>
       </c>
       <c r="R16">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S16">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="T16">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="U16">
         <v>1.4</v>
       </c>
       <c r="V16">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W16">
         <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>9.65</v>
+        <v>9.5</v>
       </c>
       <c r="Z16">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AA16">
         <v>3.32</v>
       </c>
       <c r="AB16">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC16">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AD16">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AE16">
         <v>1.29</v>
       </c>
       <c r="AF16">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH16">
-        <v>6.64</v>
+        <v>7</v>
       </c>
       <c r="AI16">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AJ16" t="s">
         <v>177</v>
@@ -2921,40 +2921,40 @@
         <v>175</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P18">
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
         <v>0</v>
@@ -2969,10 +2969,10 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH18">
         <v>0</v>
@@ -3037,13 +3037,13 @@
         <v>175</v>
       </c>
       <c r="L19">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="M19">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="N19">
-        <v>3.53</v>
+        <v>3.65</v>
       </c>
       <c r="O19">
         <v>1.58</v>
@@ -3058,19 +3058,19 @@
         <v>1.29</v>
       </c>
       <c r="S19">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="T19">
         <v>2.23</v>
       </c>
       <c r="U19">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3079,28 +3079,28 @@
         <v>14.4</v>
       </c>
       <c r="Z19">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AA19">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AB19">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AC19">
         <v>2.38</v>
       </c>
       <c r="AD19">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AE19">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AF19">
         <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH19">
         <v>3.8</v>
@@ -3153,13 +3153,13 @@
         <v>175</v>
       </c>
       <c r="L20">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="M20">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N20">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="O20">
         <v>1.62</v>
@@ -3201,10 +3201,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC20">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         <v>175</v>
       </c>
       <c r="L21">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="N21">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="O21">
         <v>4</v>
@@ -3287,58 +3287,58 @@
         <v>1.33</v>
       </c>
       <c r="R21">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S21">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="T21">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="U21">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V21">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z21">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AA21">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AB21">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC21">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AD21">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="AE21">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF21">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AG21">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AH21">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AI21">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AJ21" t="s">
         <v>177</v>
@@ -3385,76 +3385,76 @@
         <v>175</v>
       </c>
       <c r="L22">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="M22">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N22">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ22" t="s">
         <v>177</v>
@@ -3474,7 +3474,7 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
         <v>80</v>
@@ -3501,76 +3501,76 @@
         <v>175</v>
       </c>
       <c r="L23">
-        <v>2.31</v>
+        <v>3.8</v>
       </c>
       <c r="M23">
-        <v>3.03</v>
+        <v>3.19</v>
       </c>
       <c r="N23">
-        <v>2.8</v>
+        <v>1.84</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AB23">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC23">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ23" t="s">
         <v>177</v>
@@ -3590,7 +3590,7 @@
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
         <v>80</v>
@@ -3617,76 +3617,76 @@
         <v>175</v>
       </c>
       <c r="L24">
-        <v>1.76</v>
+        <v>4.05</v>
       </c>
       <c r="M24">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N24">
-        <v>3.79</v>
+        <v>1.77</v>
       </c>
       <c r="O24">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="P24">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="R24">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S24">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="T24">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="U24">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V24">
-        <v>5.65</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z24">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AA24">
-        <v>3.64</v>
+        <v>4.12</v>
       </c>
       <c r="AB24">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC24">
         <v>1.95</v>
       </c>
       <c r="AD24">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="AE24">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AF24">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AH24">
-        <v>5</v>
+        <v>4.69</v>
       </c>
       <c r="AI24">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AJ24" t="s">
         <v>177</v>
@@ -3706,7 +3706,7 @@
         <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
         <v>80</v>
@@ -3733,76 +3733,76 @@
         <v>175</v>
       </c>
       <c r="L25">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="M25">
-        <v>3.19</v>
+        <v>3.65</v>
       </c>
       <c r="N25">
-        <v>1.84</v>
+        <v>4.1</v>
       </c>
       <c r="O25">
-        <v>2.71</v>
+        <v>1.57</v>
       </c>
       <c r="P25">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q25">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="R25">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="S25">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="T25">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="U25">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="V25">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>8.5</v>
+        <v>12.9</v>
       </c>
       <c r="Z25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AA25">
-        <v>2.98</v>
+        <v>3.75</v>
       </c>
       <c r="AB25">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AC25">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AD25">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
       <c r="AE25">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AF25">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AG25">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AH25">
-        <v>7.1</v>
+        <v>5.05</v>
       </c>
       <c r="AI25">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AJ25" t="s">
         <v>177</v>
@@ -3825,7 +3825,7 @@
         <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" t="s">
         <v>105</v>
@@ -3849,76 +3849,76 @@
         <v>175</v>
       </c>
       <c r="L26">
-        <v>3.07</v>
+        <v>2.39</v>
       </c>
       <c r="M26">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="N26">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="O26">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="P26">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q26">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="R26">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="S26">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="T26">
+        <v>3.4</v>
+      </c>
+      <c r="U26">
+        <v>1.29</v>
+      </c>
+      <c r="V26">
+        <v>9</v>
+      </c>
+      <c r="W26">
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <v>1.09</v>
+      </c>
+      <c r="Y26">
+        <v>6.8</v>
+      </c>
+      <c r="Z26">
+        <v>1.49</v>
+      </c>
+      <c r="AA26">
         <v>2.5</v>
       </c>
-      <c r="U26">
-        <v>1.5</v>
-      </c>
-      <c r="V26">
-        <v>6.5</v>
-      </c>
-      <c r="W26">
-        <v>1.11</v>
-      </c>
-      <c r="X26">
-        <v>1.05</v>
-      </c>
-      <c r="Y26">
-        <v>9.5</v>
-      </c>
-      <c r="Z26">
-        <v>1.28</v>
-      </c>
-      <c r="AA26">
-        <v>3.6</v>
-      </c>
       <c r="AB26">
-        <v>1.8</v>
+        <v>2.57</v>
       </c>
       <c r="AC26">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AD26">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AE26">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AH26">
-        <v>5.75</v>
+        <v>9</v>
       </c>
       <c r="AI26">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AJ26" t="s">
         <v>177</v>
@@ -3965,76 +3965,76 @@
         <v>175</v>
       </c>
       <c r="L27">
-        <v>3.03</v>
+        <v>5.69</v>
       </c>
       <c r="M27">
-        <v>3.39</v>
+        <v>4.25</v>
       </c>
       <c r="N27">
-        <v>2.02</v>
+        <v>1.49</v>
       </c>
       <c r="O27">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q27">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="R27">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S27">
-        <v>3.26</v>
+        <v>3.14</v>
       </c>
       <c r="T27">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="U27">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V27">
         <v>6</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z27">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AA27">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AB27">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AC27">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AD27">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AE27">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH27">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AI27">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AJ27" t="s">
         <v>177</v>
@@ -4054,7 +4054,7 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
         <v>79</v>
@@ -4081,76 +4081,76 @@
         <v>175</v>
       </c>
       <c r="L28">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="M28">
-        <v>4.2</v>
+        <v>3.31</v>
       </c>
       <c r="N28">
-        <v>1.48</v>
+        <v>3.39</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="P28">
-        <v>14.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q28">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="R28">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S28">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="T28">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="U28">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V28">
-        <v>5.5</v>
+        <v>7.3</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="Z28">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AA28">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AB28">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AC28">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AD28">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AE28">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG28">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AH28">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AI28">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AJ28" t="s">
         <v>177</v>
@@ -4170,7 +4170,7 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
         <v>79</v>
@@ -4197,13 +4197,13 @@
         <v>175</v>
       </c>
       <c r="L29">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="M29">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N29">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>1.53</v>
@@ -4218,25 +4218,25 @@
         <v>1.33</v>
       </c>
       <c r="S29">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="T29">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
         <v>1.4</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>10.8</v>
+        <v>7.8</v>
       </c>
       <c r="Z29">
         <v>1.25</v>
@@ -4245,28 +4245,28 @@
         <v>3.64</v>
       </c>
       <c r="AB29">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AC29">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AD29">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AE29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF29">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG29">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH29">
         <v>5.5</v>
       </c>
       <c r="AI29">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ29" t="s">
         <v>177</v>
@@ -4286,7 +4286,7 @@
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
         <v>79</v>
@@ -4313,76 +4313,76 @@
         <v>175</v>
       </c>
       <c r="L30">
-        <v>2.28</v>
+        <v>1.31</v>
       </c>
       <c r="M30">
-        <v>2.91</v>
+        <v>4.94</v>
       </c>
       <c r="N30">
-        <v>2.96</v>
+        <v>8</v>
       </c>
       <c r="O30">
+        <v>1.29</v>
+      </c>
+      <c r="P30">
+        <v>16.25</v>
+      </c>
+      <c r="Q30">
+        <v>3.75</v>
+      </c>
+      <c r="R30">
+        <v>1.29</v>
+      </c>
+      <c r="S30">
+        <v>3.4</v>
+      </c>
+      <c r="T30">
+        <v>2.32</v>
+      </c>
+      <c r="U30">
+        <v>1.55</v>
+      </c>
+      <c r="V30">
+        <v>5</v>
+      </c>
+      <c r="W30">
+        <v>1.12</v>
+      </c>
+      <c r="X30">
+        <v>1</v>
+      </c>
+      <c r="Y30">
+        <v>13.3</v>
+      </c>
+      <c r="Z30">
+        <v>1.18</v>
+      </c>
+      <c r="AA30">
+        <v>4.33</v>
+      </c>
+      <c r="AB30">
+        <v>1.57</v>
+      </c>
+      <c r="AC30">
+        <v>2.24</v>
+      </c>
+      <c r="AD30">
+        <v>2.4</v>
+      </c>
+      <c r="AE30">
+        <v>1.46</v>
+      </c>
+      <c r="AF30">
         <v>1.83</v>
       </c>
-      <c r="P30">
-        <v>6.4</v>
-      </c>
-      <c r="Q30">
-        <v>2.3</v>
-      </c>
-      <c r="R30">
-        <v>1.54</v>
-      </c>
-      <c r="S30">
-        <v>2.32</v>
-      </c>
-      <c r="T30">
-        <v>3.42</v>
-      </c>
-      <c r="U30">
-        <v>1.23</v>
-      </c>
-      <c r="V30">
-        <v>9.75</v>
-      </c>
-      <c r="W30">
-        <v>1.03</v>
-      </c>
-      <c r="X30">
-        <v>1.08</v>
-      </c>
-      <c r="Y30">
-        <v>6.5</v>
-      </c>
-      <c r="Z30">
-        <v>1.4</v>
-      </c>
-      <c r="AA30">
-        <v>2.6</v>
-      </c>
-      <c r="AB30">
-        <v>2.15</v>
-      </c>
-      <c r="AC30">
-        <v>1.57</v>
-      </c>
-      <c r="AD30">
-        <v>4.4</v>
-      </c>
-      <c r="AE30">
-        <v>1.17</v>
-      </c>
-      <c r="AF30">
+      <c r="AG30">
         <v>1.95</v>
       </c>
-      <c r="AG30">
-        <v>1.75</v>
-      </c>
       <c r="AH30">
-        <v>9</v>
+        <v>4.48</v>
       </c>
       <c r="AI30">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AJ30" t="s">
         <v>177</v>
@@ -4405,7 +4405,7 @@
         <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E31" t="s">
         <v>110</v>
@@ -4429,76 +4429,76 @@
         <v>175</v>
       </c>
       <c r="L31">
-        <v>1.97</v>
+        <v>3.07</v>
       </c>
       <c r="M31">
-        <v>3.21</v>
+        <v>3.34</v>
       </c>
       <c r="N31">
-        <v>3.31</v>
+        <v>2.02</v>
       </c>
       <c r="O31">
+        <v>2.25</v>
+      </c>
+      <c r="P31">
+        <v>10.5</v>
+      </c>
+      <c r="Q31">
         <v>1.67</v>
       </c>
-      <c r="P31">
-        <v>11.75</v>
-      </c>
-      <c r="Q31">
-        <v>2.38</v>
-      </c>
       <c r="R31">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S31">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="T31">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="U31">
+        <v>1.5</v>
+      </c>
+      <c r="V31">
+        <v>6.5</v>
+      </c>
+      <c r="W31">
+        <v>1.11</v>
+      </c>
+      <c r="X31">
+        <v>1.05</v>
+      </c>
+      <c r="Y31">
+        <v>9.5</v>
+      </c>
+      <c r="Z31">
+        <v>1.28</v>
+      </c>
+      <c r="AA31">
+        <v>3.6</v>
+      </c>
+      <c r="AB31">
+        <v>1.8</v>
+      </c>
+      <c r="AC31">
+        <v>1.91</v>
+      </c>
+      <c r="AD31">
+        <v>3</v>
+      </c>
+      <c r="AE31">
         <v>1.38</v>
       </c>
-      <c r="V31">
-        <v>6.75</v>
-      </c>
-      <c r="W31">
-        <v>1.08</v>
-      </c>
-      <c r="X31">
-        <v>1.02</v>
-      </c>
-      <c r="Y31">
-        <v>10</v>
-      </c>
-      <c r="Z31">
-        <v>1.25</v>
-      </c>
-      <c r="AA31">
-        <v>3.4</v>
-      </c>
-      <c r="AB31">
-        <v>1.85</v>
-      </c>
-      <c r="AC31">
-        <v>1.85</v>
-      </c>
-      <c r="AD31">
-        <v>3.1</v>
-      </c>
-      <c r="AE31">
-        <v>1.3</v>
-      </c>
       <c r="AF31">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH31">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AI31">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ31" t="s">
         <v>177</v>
@@ -4545,76 +4545,76 @@
         <v>175</v>
       </c>
       <c r="L32">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="M32">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="N32">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="O32">
+        <v>2.3</v>
+      </c>
+      <c r="P32">
+        <v>13.5</v>
+      </c>
+      <c r="Q32">
+        <v>1.67</v>
+      </c>
+      <c r="R32">
+        <v>1.32</v>
+      </c>
+      <c r="S32">
+        <v>3.1</v>
+      </c>
+      <c r="T32">
+        <v>2.46</v>
+      </c>
+      <c r="U32">
+        <v>1.48</v>
+      </c>
+      <c r="V32">
+        <v>6.1</v>
+      </c>
+      <c r="W32">
+        <v>1.09</v>
+      </c>
+      <c r="X32">
+        <v>1.02</v>
+      </c>
+      <c r="Y32">
+        <v>10</v>
+      </c>
+      <c r="Z32">
+        <v>1.2</v>
+      </c>
+      <c r="AA32">
+        <v>4.22</v>
+      </c>
+      <c r="AB32">
+        <v>1.7</v>
+      </c>
+      <c r="AC32">
+        <v>2.03</v>
+      </c>
+      <c r="AD32">
+        <v>2.73</v>
+      </c>
+      <c r="AE32">
+        <v>1.39</v>
+      </c>
+      <c r="AF32">
+        <v>1.62</v>
+      </c>
+      <c r="AG32">
         <v>2.25</v>
       </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>1.8</v>
-      </c>
-      <c r="R32">
-        <v>1.43</v>
-      </c>
-      <c r="S32">
-        <v>2.82</v>
-      </c>
-      <c r="T32">
-        <v>3.05</v>
-      </c>
-      <c r="U32">
-        <v>1.35</v>
-      </c>
-      <c r="V32">
-        <v>8</v>
-      </c>
-      <c r="W32">
-        <v>1.08</v>
-      </c>
-      <c r="X32">
-        <v>1.06</v>
-      </c>
-      <c r="Y32">
-        <v>8.5</v>
-      </c>
-      <c r="Z32">
-        <v>1.29</v>
-      </c>
-      <c r="AA32">
-        <v>3.1</v>
-      </c>
-      <c r="AB32">
-        <v>2.2</v>
-      </c>
-      <c r="AC32">
-        <v>1.65</v>
-      </c>
-      <c r="AD32">
-        <v>3.61</v>
-      </c>
-      <c r="AE32">
-        <v>1.25</v>
-      </c>
-      <c r="AF32">
-        <v>1.75</v>
-      </c>
-      <c r="AG32">
-        <v>1.91</v>
-      </c>
       <c r="AH32">
-        <v>6.75</v>
+        <v>5</v>
       </c>
       <c r="AI32">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AJ32" t="s">
         <v>177</v>
@@ -4661,76 +4661,76 @@
         <v>175</v>
       </c>
       <c r="L33">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="M33">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="N33">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="O33">
+        <v>2.25</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>1.8</v>
+      </c>
+      <c r="R33">
+        <v>1.4</v>
+      </c>
+      <c r="S33">
+        <v>2.62</v>
+      </c>
+      <c r="T33">
+        <v>2.98</v>
+      </c>
+      <c r="U33">
+        <v>1.34</v>
+      </c>
+      <c r="V33">
+        <v>8</v>
+      </c>
+      <c r="W33">
+        <v>1.07</v>
+      </c>
+      <c r="X33">
+        <v>1.02</v>
+      </c>
+      <c r="Y33">
+        <v>8.5</v>
+      </c>
+      <c r="Z33">
+        <v>1.32</v>
+      </c>
+      <c r="AA33">
+        <v>3</v>
+      </c>
+      <c r="AB33">
+        <v>2.06</v>
+      </c>
+      <c r="AC33">
+        <v>1.73</v>
+      </c>
+      <c r="AD33">
+        <v>3.61</v>
+      </c>
+      <c r="AE33">
         <v>1.29</v>
       </c>
-      <c r="P33">
-        <v>16.25</v>
-      </c>
-      <c r="Q33">
-        <v>3.75</v>
-      </c>
-      <c r="R33">
-        <v>1.29</v>
-      </c>
-      <c r="S33">
-        <v>3.3</v>
-      </c>
-      <c r="T33">
-        <v>2.32</v>
-      </c>
-      <c r="U33">
-        <v>1.54</v>
-      </c>
-      <c r="V33">
-        <v>5.25</v>
-      </c>
-      <c r="W33">
-        <v>1.12</v>
-      </c>
-      <c r="X33">
-        <v>1.03</v>
-      </c>
-      <c r="Y33">
-        <v>15</v>
-      </c>
-      <c r="Z33">
-        <v>1.18</v>
-      </c>
-      <c r="AA33">
-        <v>4.5</v>
-      </c>
-      <c r="AB33">
-        <v>1.73</v>
-      </c>
-      <c r="AC33">
-        <v>2.08</v>
-      </c>
-      <c r="AD33">
-        <v>2.5</v>
-      </c>
-      <c r="AE33">
-        <v>1.44</v>
-      </c>
       <c r="AF33">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH33">
-        <v>4.6</v>
+        <v>6.75</v>
       </c>
       <c r="AI33">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AJ33" t="s">
         <v>177</v>
@@ -4866,7 +4866,7 @@
         <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D35" t="s">
         <v>79</v>
@@ -4893,40 +4893,40 @@
         <v>175</v>
       </c>
       <c r="L35">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P35">
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X35">
         <v>0</v>
@@ -4941,10 +4941,10 @@
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD35">
         <v>0</v>
@@ -4953,10 +4953,10 @@
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH35">
         <v>0</v>
@@ -4982,7 +4982,7 @@
         <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D36" t="s">
         <v>79</v>
@@ -5009,40 +5009,40 @@
         <v>175</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P36">
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD36">
         <v>0</v>
@@ -5069,10 +5069,10 @@
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH36">
         <v>0</v>
@@ -5473,40 +5473,40 @@
         <v>175</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P40">
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X40">
         <v>0</v>
@@ -5515,34 +5515,34 @@
         <v>0</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ40" t="s">
         <v>177</v>
@@ -5910,7 +5910,7 @@
         <v>52</v>
       </c>
       <c r="C44" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D44" t="s">
         <v>79</v>
@@ -5937,76 +5937,76 @@
         <v>175</v>
       </c>
       <c r="L44">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="M44">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="N44">
-        <v>2.98</v>
+        <v>2.46</v>
       </c>
       <c r="O44">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="P44">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R44">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S44">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="T44">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U44">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V44">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="W44">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AA44">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AB44">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AC44">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="AD44">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AE44">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF44">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AG44">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AH44">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="AI44">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AJ44" t="s">
         <v>177</v>
@@ -6026,7 +6026,7 @@
         <v>52</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D45" t="s">
         <v>79</v>
@@ -6053,76 +6053,76 @@
         <v>175</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH45">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ45" t="s">
         <v>177</v>
@@ -6217,10 +6217,10 @@
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AC46">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD46">
         <v>0</v>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="185">
   <si>
     <t>Date</t>
   </si>
@@ -157,6 +157,9 @@
     <t>15:45</t>
   </si>
   <si>
+    <t>16:00</t>
+  </si>
+  <si>
     <t>19:00</t>
   </si>
   <si>
@@ -184,39 +187,39 @@
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Russia FNL</t>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Finland Veikkausliiga</t>
   </si>
   <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
@@ -238,6 +241,9 @@
     <t>Belgium Pro League</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -262,16 +268,34 @@
     <t>Manly United</t>
   </si>
   <si>
+    <t>Neftekhimik</t>
+  </si>
+  <si>
     <t>Zhenys</t>
   </si>
   <si>
-    <t>Neftekhimik</t>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Cracovia Kraków</t>
+  </si>
+  <si>
+    <t>GKS Katowice</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Jaro</t>
   </si>
   <si>
     <t>Krylya Sovetov</t>
   </si>
   <si>
-    <t>Jaro</t>
+    <t>Zbrojovka Brno</t>
   </si>
   <si>
     <t>Vaprus</t>
@@ -280,33 +304,18 @@
     <t>Ústí nad Labem</t>
   </si>
   <si>
-    <t>Cracovia Kraków</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
     <t>Metaloglobus</t>
   </si>
   <si>
     <t>Arsenal Tula</t>
   </si>
   <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
     <t>AGF</t>
   </si>
   <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
@@ -319,51 +328,54 @@
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>Zürich</t>
+  </si>
+  <si>
+    <t>Stal Rzeszów</t>
+  </si>
+  <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
-    <t>Zürich</t>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Royal Antwerp FC</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
   </si>
   <si>
     <t>Derry City</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Royal Antwerp FC</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Kerry</t>
+    <t>Recoleta</t>
   </si>
   <si>
     <t>Sarmiento</t>
   </si>
   <si>
+    <t>HFX Wanderers FC</t>
+  </si>
+  <si>
     <t>Ulytau</t>
   </si>
   <si>
-    <t>HFX Wanderers FC</t>
-  </si>
-  <si>
     <t>Deportes Limache</t>
   </si>
   <si>
@@ -385,12 +397,12 @@
     <t>FC Dallas</t>
   </si>
   <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
     <t>Austin II</t>
   </si>
   <si>
-    <t>Houston Dynamo</t>
-  </si>
-  <si>
     <t>Vancouver FC</t>
   </si>
   <si>
@@ -403,16 +415,34 @@
     <t>Western Sydney W. II</t>
   </si>
   <si>
+    <t>Orenburg</t>
+  </si>
+  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
-    <t>Orenburg</t>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Nieciecza</t>
+  </si>
+  <si>
+    <t>Zagłębie Lubin</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>VPS</t>
   </si>
   <si>
     <t>Olimpiyets</t>
   </si>
   <si>
-    <t>VPS</t>
+    <t>Sparta Praha II</t>
   </si>
   <si>
     <t>Harju Jalgpallikool</t>
@@ -421,33 +451,18 @@
     <t>Vlašim</t>
   </si>
   <si>
-    <t>Nieciecza</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
     <t>Petrolul 52</t>
   </si>
   <si>
     <t>Shinnik</t>
   </si>
   <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
     <t>Randers</t>
   </si>
   <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
@@ -460,51 +475,54 @@
     <t>Ludogorets</t>
   </si>
   <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Sion</t>
+  </si>
+  <si>
+    <t>Śląsk Wrocław</t>
+  </si>
+  <si>
     <t>Radomiak Radom</t>
   </si>
   <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
-    <t>Śląsk Wrocław</t>
-  </si>
-  <si>
-    <t>Sion</t>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Union Saint-Gilloise</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Wexford</t>
   </si>
   <si>
     <t>Bohemians</t>
   </si>
   <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Union Saint-Gilloise</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>UCD</t>
+    <t>Concepción</t>
   </si>
   <si>
     <t>Lanús</t>
   </si>
   <si>
+    <t>Forge FC</t>
+  </si>
+  <si>
     <t>Aktobe</t>
   </si>
   <si>
-    <t>Forge FC</t>
-  </si>
-  <si>
     <t>Ñublense</t>
   </si>
   <si>
@@ -526,12 +544,12 @@
     <t>New York City</t>
   </si>
   <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
     <t>Valour FC</t>
   </si>
   <si>
@@ -545,6 +563,9 @@
   </si>
   <si>
     <t>canceled</t>
+  </si>
+  <si>
+    <t>suspended</t>
   </si>
   <si>
     <t>[]</t>
@@ -911,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL48"/>
+  <dimension ref="A1:AL50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -1038,16 +1059,16 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1062,16 +1083,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L2">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="M2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
         <v>1.64</v>
@@ -1083,31 +1104,31 @@
         <v>2.19</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
         <v>3.3</v>
       </c>
       <c r="T2">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="U2">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V2">
         <v>5.5</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
         <v>14</v>
       </c>
       <c r="Z2">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AA2">
         <v>4.33</v>
@@ -1119,16 +1140,16 @@
         <v>2.35</v>
       </c>
       <c r="AD2">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AE2">
         <v>1.5</v>
       </c>
       <c r="AF2">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG2">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH2">
         <v>4.4</v>
@@ -1137,10 +1158,10 @@
         <v>1.2</v>
       </c>
       <c r="AJ2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL2" s="3">
         <v>45863.27083333334</v>
@@ -1154,16 +1175,16 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1178,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1253,10 +1274,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL3" s="3">
         <v>45863.45833333334</v>
@@ -1270,16 +1291,16 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1294,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1369,10 +1390,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK4" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL4" s="3">
         <v>45863.45833333334</v>
@@ -1386,16 +1407,16 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1410,85 +1431,85 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L5">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK5" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL5" s="3">
         <v>45863.54166666666</v>
@@ -1502,16 +1523,16 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1526,85 +1547,85 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L6">
-        <v>3.51</v>
+        <v>2.12</v>
       </c>
       <c r="M6">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="N6">
-        <v>1.95</v>
+        <v>3.23</v>
       </c>
       <c r="O6">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="P6">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="T6">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="U6">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="V6">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA6">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="AB6">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC6">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AD6">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="AE6">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF6">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH6">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AI6">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AJ6" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK6" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL6" s="3">
         <v>45863.54166666666</v>
@@ -1618,16 +1639,16 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1642,85 +1663,85 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L7">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M7">
-        <v>3.6</v>
+        <v>3.09</v>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O7">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="T7">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="U7">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="V7">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AC7">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AD7">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH7">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK7" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL7" s="3">
         <v>45863.54166666666</v>
@@ -1737,13 +1758,13 @@
         <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1758,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1833,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK8" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL8" s="3">
         <v>45863.54166666666</v>
@@ -1850,16 +1871,16 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1874,43 +1895,43 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L9">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9">
         <v>0</v>
@@ -1925,10 +1946,10 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -1937,10 +1958,10 @@
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1949,10 +1970,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK9" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL9" s="3">
         <v>45863.54166666666</v>
@@ -1966,16 +1987,16 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1990,85 +2011,85 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK10" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL10" s="3">
         <v>45863.54166666666</v>
@@ -2082,16 +2103,16 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2106,85 +2127,85 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ11" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK11" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL11" s="3">
         <v>45863.54166666666</v>
@@ -2198,16 +2219,16 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2222,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2297,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK12" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL12" s="3">
         <v>45863.54166666666</v>
@@ -2314,16 +2335,16 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2338,85 +2359,85 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L13">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="M13">
-        <v>3.25</v>
+        <v>3.47</v>
       </c>
       <c r="N13">
-        <v>2.94</v>
+        <v>3.61</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R13">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T13">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="U13">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="V13">
-        <v>5.85</v>
+        <v>4.75</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>9.5</v>
+        <v>13.9</v>
       </c>
       <c r="Z13">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AA13">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="AB13">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AC13">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="AD13">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="AE13">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AF13">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="AG13">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AH13">
-        <v>5.4</v>
+        <v>3.78</v>
       </c>
       <c r="AI13">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AJ13" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK13" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL13" s="3">
         <v>45863.54166666666</v>
@@ -2430,16 +2451,16 @@
         <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2454,85 +2475,85 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L14">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK14" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL14" s="3">
         <v>45863.54166666666</v>
@@ -2543,19 +2564,19 @@
         <v>45863</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2570,88 +2591,88 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L15">
-        <v>1.84</v>
+        <v>4.1</v>
       </c>
       <c r="M15">
-        <v>3.12</v>
+        <v>3.21</v>
       </c>
       <c r="N15">
-        <v>4.88</v>
+        <v>1.77</v>
       </c>
       <c r="O15">
-        <v>1.6</v>
+        <v>2.96</v>
       </c>
       <c r="P15">
-        <v>6.05</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q15">
-        <v>3.18</v>
+        <v>1.55</v>
       </c>
       <c r="R15">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S15">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="T15">
-        <v>3.34</v>
+        <v>2.89</v>
       </c>
       <c r="U15">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V15">
-        <v>9.300000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="W15">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="Z15">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AA15">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AB15">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="AC15">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AD15">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AE15">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AF15">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AG15">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AH15">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AI15">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AJ15" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK15" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL15" s="3">
-        <v>45863.57291666666</v>
+        <v>45863.54166666666</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2659,19 +2680,19 @@
         <v>45863</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F16" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2686,88 +2707,88 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L16">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="M16">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="N16">
-        <v>3.3</v>
+        <v>4.78</v>
       </c>
       <c r="O16">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="P16">
-        <v>8.75</v>
+        <v>6.05</v>
       </c>
       <c r="Q16">
-        <v>2.4</v>
+        <v>3.18</v>
       </c>
       <c r="R16">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S16">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="T16">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="U16">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="V16">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X16">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>9.5</v>
+        <v>7.6</v>
       </c>
       <c r="Z16">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AA16">
-        <v>3.32</v>
+        <v>2.3</v>
       </c>
       <c r="AB16">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AC16">
-        <v>1.89</v>
+        <v>1.51</v>
       </c>
       <c r="AD16">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="AE16">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF16">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AH16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AI16">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AJ16" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK16" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL16" s="3">
-        <v>45863.58333333334</v>
+        <v>45863.57291666666</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2781,13 +2802,13 @@
         <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F17" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2802,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L17">
         <v>1.64</v>
@@ -2877,10 +2898,10 @@
         <v>1.18</v>
       </c>
       <c r="AJ17" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK17" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL17" s="3">
         <v>45863.58333333334</v>
@@ -2891,19 +2912,19 @@
         <v>45863</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
         <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F18" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2918,88 +2939,88 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L18">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="M18">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="N18">
-        <v>2.25</v>
+        <v>3.31</v>
       </c>
       <c r="O18">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="Q18">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="R18">
+        <v>1.4</v>
+      </c>
+      <c r="S18">
+        <v>2.8</v>
+      </c>
+      <c r="T18">
+        <v>2.84</v>
+      </c>
+      <c r="U18">
+        <v>1.38</v>
+      </c>
+      <c r="V18">
+        <v>6.5</v>
+      </c>
+      <c r="W18">
+        <v>1.08</v>
+      </c>
+      <c r="X18">
+        <v>1.06</v>
+      </c>
+      <c r="Y18">
+        <v>9.5</v>
+      </c>
+      <c r="Z18">
         <v>1.3</v>
       </c>
-      <c r="S18">
+      <c r="AA18">
+        <v>3.3</v>
+      </c>
+      <c r="AB18">
+        <v>1.94</v>
+      </c>
+      <c r="AC18">
+        <v>1.76</v>
+      </c>
+      <c r="AD18">
         <v>3.4</v>
       </c>
-      <c r="T18">
-        <v>2.5</v>
-      </c>
-      <c r="U18">
-        <v>1.5</v>
-      </c>
-      <c r="V18">
-        <v>5.5</v>
-      </c>
-      <c r="W18">
-        <v>1.13</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>1.66</v>
-      </c>
-      <c r="AC18">
-        <v>2.15</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF18">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>6.64</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ18" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK18" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL18" s="3">
-        <v>45863.60416666666</v>
+        <v>45863.58333333334</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -3010,16 +3031,16 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3034,85 +3055,85 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L19">
-        <v>1.8</v>
+        <v>2.57</v>
       </c>
       <c r="M19">
-        <v>3.74</v>
+        <v>3.32</v>
       </c>
       <c r="N19">
-        <v>3.65</v>
+        <v>2.33</v>
       </c>
       <c r="O19">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="P19">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="R19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S19">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="T19">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="U19">
+        <v>1.5</v>
+      </c>
+      <c r="V19">
+        <v>5.5</v>
+      </c>
+      <c r="W19">
+        <v>1.13</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>1.65</v>
+      </c>
+      <c r="AC19">
+        <v>2.2</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
         <v>1.57</v>
       </c>
-      <c r="V19">
-        <v>5.05</v>
-      </c>
-      <c r="W19">
-        <v>1.15</v>
-      </c>
-      <c r="X19">
-        <v>1.01</v>
-      </c>
-      <c r="Y19">
-        <v>14.4</v>
-      </c>
-      <c r="Z19">
-        <v>1.15</v>
-      </c>
-      <c r="AA19">
-        <v>5</v>
-      </c>
-      <c r="AB19">
-        <v>1.46</v>
-      </c>
-      <c r="AC19">
-        <v>2.38</v>
-      </c>
-      <c r="AD19">
-        <v>2.26</v>
-      </c>
-      <c r="AE19">
-        <v>1.57</v>
-      </c>
-      <c r="AF19">
-        <v>1.5</v>
-      </c>
       <c r="AG19">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH19">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI19">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK19" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL19" s="3">
         <v>45863.60416666666</v>
@@ -3123,19 +3144,19 @@
         <v>45863</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
         <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F20" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3150,88 +3171,88 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L20">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="M20">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N20">
-        <v>3.39</v>
+        <v>3.53</v>
       </c>
       <c r="O20">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q20">
+        <v>2.33</v>
+      </c>
+      <c r="R20">
+        <v>1.29</v>
+      </c>
+      <c r="S20">
+        <v>3.4</v>
+      </c>
+      <c r="T20">
+        <v>2.22</v>
+      </c>
+      <c r="U20">
+        <v>1.57</v>
+      </c>
+      <c r="V20">
+        <v>4.75</v>
+      </c>
+      <c r="W20">
+        <v>1.15</v>
+      </c>
+      <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>15</v>
+      </c>
+      <c r="Z20">
+        <v>1.15</v>
+      </c>
+      <c r="AA20">
+        <v>5</v>
+      </c>
+      <c r="AB20">
+        <v>1.53</v>
+      </c>
+      <c r="AC20">
+        <v>2.4</v>
+      </c>
+      <c r="AD20">
+        <v>2.24</v>
+      </c>
+      <c r="AE20">
+        <v>1.58</v>
+      </c>
+      <c r="AF20">
+        <v>1.5</v>
+      </c>
+      <c r="AG20">
         <v>2.5</v>
       </c>
-      <c r="R20">
-        <v>1.36</v>
-      </c>
-      <c r="S20">
-        <v>3</v>
-      </c>
-      <c r="T20">
-        <v>2.63</v>
-      </c>
-      <c r="U20">
-        <v>1.44</v>
-      </c>
-      <c r="V20">
-        <v>7</v>
-      </c>
-      <c r="W20">
-        <v>1.1</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>1.8</v>
-      </c>
-      <c r="AC20">
-        <v>2</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>1.67</v>
-      </c>
-      <c r="AG20">
-        <v>2.1</v>
-      </c>
       <c r="AH20">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ20" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK20" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL20" s="3">
-        <v>45863.625</v>
+        <v>45863.60416666666</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3245,13 +3266,13 @@
         <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F21" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3266,85 +3287,85 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L21">
-        <v>9</v>
+        <v>1.99</v>
       </c>
       <c r="M21">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="N21">
-        <v>1.32</v>
+        <v>3.14</v>
       </c>
       <c r="O21">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="P21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S21">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T21">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U21">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V21">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AC21">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AD21">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>2.29</v>
+        <v>1.67</v>
       </c>
       <c r="AG21">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AH21">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK21" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL21" s="3">
         <v>45863.625</v>
@@ -3355,19 +3376,19 @@
         <v>45863</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3382,88 +3403,88 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L22">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="M22">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N22">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="O22">
-        <v>1.93</v>
+        <v>4</v>
       </c>
       <c r="P22">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>2.05</v>
+        <v>1.33</v>
       </c>
       <c r="R22">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S22">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T22">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U22">
         <v>1.4</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W22">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="Z22">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AA22">
         <v>3.3</v>
       </c>
       <c r="AB22">
+        <v>1.75</v>
+      </c>
+      <c r="AC22">
         <v>1.91</v>
       </c>
-      <c r="AC22">
-        <v>1.83</v>
-      </c>
       <c r="AD22">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AE22">
         <v>1.3</v>
       </c>
       <c r="AF22">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AG22">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AH22">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AI22">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AJ22" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK22" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL22" s="3">
-        <v>45863.64583333334</v>
+        <v>45863.625</v>
       </c>
     </row>
     <row r="23" spans="1:38">
@@ -3474,16 +3495,16 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3498,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L23">
         <v>3.8</v>
@@ -3549,10 +3570,10 @@
         <v>2.98</v>
       </c>
       <c r="AB23">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC23">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD23">
         <v>3.52</v>
@@ -3573,10 +3594,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ23" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK23" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL23" s="3">
         <v>45863.64583333334</v>
@@ -3590,16 +3611,16 @@
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F24" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3614,85 +3635,85 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L24">
-        <v>4.05</v>
+        <v>1.76</v>
       </c>
       <c r="M24">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N24">
-        <v>1.77</v>
+        <v>3.79</v>
       </c>
       <c r="O24">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q24">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="R24">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S24">
         <v>3</v>
       </c>
       <c r="T24">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U24">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z24">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AA24">
-        <v>4.12</v>
+        <v>3.75</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC24">
         <v>1.95</v>
       </c>
       <c r="AD24">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AE24">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF24">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH24">
-        <v>4.69</v>
+        <v>5.05</v>
       </c>
       <c r="AI24">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AJ24" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK24" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL24" s="3">
         <v>45863.64583333334</v>
@@ -3706,16 +3727,16 @@
         <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E25" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F25" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3730,85 +3751,85 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L25">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M25">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N25">
-        <v>4.1</v>
+        <v>1.75</v>
       </c>
       <c r="O25">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="P25">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q25">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="R25">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S25">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="T25">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U25">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="W25">
         <v>1.12</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="Z25">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AA25">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB25">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC25">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD25">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AE25">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AF25">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AH25">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="AI25">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AJ25" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK25" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL25" s="3">
         <v>45863.64583333334</v>
@@ -3819,19 +3840,19 @@
         <v>45863</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3846,88 +3867,88 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L26">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="M26">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="N26">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O26">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="P26">
-        <v>6.4</v>
+        <v>8.75</v>
       </c>
       <c r="Q26">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="R26">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="S26">
-        <v>2.32</v>
+        <v>3.02</v>
       </c>
       <c r="T26">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="U26">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="W26">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AA26">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="AB26">
-        <v>2.57</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AD26">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="AE26">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AF26">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG26">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH26">
-        <v>9</v>
+        <v>6.75</v>
       </c>
       <c r="AI26">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ26" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK26" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL26" s="3">
-        <v>45863.65625</v>
+        <v>45863.64583333334</v>
       </c>
     </row>
     <row r="27" spans="1:38">
@@ -3941,13 +3962,13 @@
         <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3962,85 +3983,85 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L27">
-        <v>5.69</v>
+        <v>1.76</v>
       </c>
       <c r="M27">
-        <v>4.25</v>
+        <v>3.45</v>
       </c>
       <c r="N27">
-        <v>1.49</v>
+        <v>3.84</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>1.53</v>
       </c>
       <c r="P27">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Q27">
+        <v>2.75</v>
+      </c>
+      <c r="R27">
+        <v>1.33</v>
+      </c>
+      <c r="S27">
+        <v>2.7</v>
+      </c>
+      <c r="T27">
+        <v>2.64</v>
+      </c>
+      <c r="U27">
         <v>1.4</v>
       </c>
-      <c r="R27">
-        <v>1.34</v>
-      </c>
-      <c r="S27">
-        <v>3.14</v>
-      </c>
-      <c r="T27">
-        <v>2.55</v>
-      </c>
-      <c r="U27">
-        <v>1.45</v>
-      </c>
       <c r="V27">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W27">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA27">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AB27">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AC27">
+        <v>1.91</v>
+      </c>
+      <c r="AD27">
+        <v>2.9</v>
+      </c>
+      <c r="AE27">
+        <v>1.33</v>
+      </c>
+      <c r="AF27">
+        <v>1.73</v>
+      </c>
+      <c r="AG27">
         <v>2</v>
       </c>
-      <c r="AD27">
-        <v>2.8</v>
-      </c>
-      <c r="AE27">
-        <v>1.38</v>
-      </c>
-      <c r="AF27">
-        <v>1.75</v>
-      </c>
-      <c r="AG27">
-        <v>2.05</v>
-      </c>
       <c r="AH27">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AI27">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ27" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK27" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL27" s="3">
         <v>45863.65625</v>
@@ -4054,16 +4075,16 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F28" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -4078,85 +4099,85 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L28">
+        <v>3.03</v>
+      </c>
+      <c r="M28">
+        <v>3.39</v>
+      </c>
+      <c r="N28">
+        <v>2.02</v>
+      </c>
+      <c r="O28">
+        <v>2.3</v>
+      </c>
+      <c r="P28">
+        <v>13.5</v>
+      </c>
+      <c r="Q28">
+        <v>1.67</v>
+      </c>
+      <c r="R28">
+        <v>1.32</v>
+      </c>
+      <c r="S28">
+        <v>3.1</v>
+      </c>
+      <c r="T28">
+        <v>2.5</v>
+      </c>
+      <c r="U28">
+        <v>1.48</v>
+      </c>
+      <c r="V28">
+        <v>6.1</v>
+      </c>
+      <c r="W28">
+        <v>1.09</v>
+      </c>
+      <c r="X28">
+        <v>1.02</v>
+      </c>
+      <c r="Y28">
+        <v>10</v>
+      </c>
+      <c r="Z28">
+        <v>1.2</v>
+      </c>
+      <c r="AA28">
+        <v>4.19</v>
+      </c>
+      <c r="AB28">
+        <v>1.67</v>
+      </c>
+      <c r="AC28">
         <v>2</v>
       </c>
-      <c r="M28">
-        <v>3.31</v>
-      </c>
-      <c r="N28">
-        <v>3.39</v>
-      </c>
-      <c r="O28">
-        <v>1.67</v>
-      </c>
-      <c r="P28">
-        <v>11.75</v>
-      </c>
-      <c r="Q28">
-        <v>2.38</v>
-      </c>
-      <c r="R28">
-        <v>1.37</v>
-      </c>
-      <c r="S28">
-        <v>2.8</v>
-      </c>
-      <c r="T28">
-        <v>2.75</v>
-      </c>
-      <c r="U28">
-        <v>1.38</v>
-      </c>
-      <c r="V28">
-        <v>7.3</v>
-      </c>
-      <c r="W28">
-        <v>1.1</v>
-      </c>
-      <c r="X28">
-        <v>1</v>
-      </c>
-      <c r="Y28">
-        <v>7.8</v>
-      </c>
-      <c r="Z28">
-        <v>1.25</v>
-      </c>
-      <c r="AA28">
-        <v>3.4</v>
-      </c>
-      <c r="AB28">
-        <v>1.91</v>
-      </c>
-      <c r="AC28">
-        <v>1.9</v>
-      </c>
       <c r="AD28">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AE28">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AF28">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="AH28">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AI28">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AJ28" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK28" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL28" s="3">
         <v>45863.65625</v>
@@ -4170,16 +4191,16 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F29" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -4194,85 +4215,85 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L29">
-        <v>1.81</v>
+        <v>2.59</v>
       </c>
       <c r="M29">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="O29">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="P29">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="R29">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S29">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T29">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="U29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V29">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
         <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z29">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AA29">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="AB29">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC29">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AD29">
-        <v>3.1</v>
+        <v>3.61</v>
       </c>
       <c r="AE29">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF29">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
         <v>2</v>
       </c>
       <c r="AH29">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AI29">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AJ29" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK29" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL29" s="3">
         <v>45863.65625</v>
@@ -4286,16 +4307,16 @@
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F30" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4310,85 +4331,85 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L30">
-        <v>1.31</v>
+        <v>4.9</v>
       </c>
       <c r="M30">
-        <v>4.94</v>
+        <v>4.2</v>
       </c>
       <c r="N30">
-        <v>8</v>
+        <v>1.48</v>
       </c>
       <c r="O30">
-        <v>1.29</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>16.25</v>
+        <v>14.5</v>
       </c>
       <c r="Q30">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="R30">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S30">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T30">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="U30">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W30">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
         <v>1</v>
       </c>
       <c r="Y30">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="Z30">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA30">
-        <v>4.33</v>
+        <v>3.72</v>
       </c>
       <c r="AB30">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AC30">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AD30">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AE30">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AF30">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH30">
-        <v>4.48</v>
+        <v>5</v>
       </c>
       <c r="AI30">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AJ30" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK30" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL30" s="3">
         <v>45863.65625</v>
@@ -4402,16 +4423,16 @@
         <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F31" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4426,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L31">
         <v>3.07</v>
@@ -4501,10 +4522,10 @@
         <v>1.13</v>
       </c>
       <c r="AJ31" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK31" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL31" s="3">
         <v>45863.65625</v>
@@ -4521,13 +4542,13 @@
         <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F32" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4542,85 +4563,85 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L32">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="M32">
-        <v>3.55</v>
+        <v>3.21</v>
       </c>
       <c r="N32">
-        <v>2.06</v>
+        <v>3.31</v>
       </c>
       <c r="O32">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="P32">
-        <v>13.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q32">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="R32">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S32">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="T32">
-        <v>2.46</v>
+        <v>2.65</v>
       </c>
       <c r="U32">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V32">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>1.09</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="Z32">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA32">
-        <v>4.22</v>
+        <v>3.5</v>
       </c>
       <c r="AB32">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC32">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AD32">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="AE32">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AF32">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG32">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH32">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="AI32">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ32" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK32" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL32" s="3">
         <v>45863.65625</v>
@@ -4634,16 +4655,16 @@
         <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4658,85 +4679,85 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L33">
-        <v>2.8</v>
+        <v>1.37</v>
       </c>
       <c r="M33">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="N33">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="O33">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="Q33">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="R33">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S33">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="T33">
-        <v>2.98</v>
+        <v>2.33</v>
       </c>
       <c r="U33">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>8.5</v>
+        <v>13.3</v>
       </c>
       <c r="Z33">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AA33">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AB33">
-        <v>2.06</v>
+        <v>1.57</v>
       </c>
       <c r="AC33">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AD33">
-        <v>3.61</v>
+        <v>2.16</v>
       </c>
       <c r="AE33">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AF33">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH33">
-        <v>6.75</v>
+        <v>4.53</v>
       </c>
       <c r="AI33">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AJ33" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK33" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL33" s="3">
         <v>45863.65625</v>
@@ -4747,19 +4768,19 @@
         <v>45863</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D34" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F34" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4774,88 +4795,88 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ34" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK34" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL34" s="3">
-        <v>45863.79166666666</v>
+        <v>45863.65625</v>
       </c>
     </row>
     <row r="35" spans="1:38">
@@ -4866,16 +4887,16 @@
         <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E35" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F35" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4890,16 +4911,16 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -4941,10 +4962,10 @@
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD35">
         <v>0</v>
@@ -4965,13 +4986,13 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK35" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL35" s="3">
-        <v>45863.79166666666</v>
+        <v>45863.66666666666</v>
       </c>
     </row>
     <row r="36" spans="1:38">
@@ -4979,19 +5000,19 @@
         <v>45863</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E36" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F36" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -5006,43 +5027,43 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L36">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P36">
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X36">
         <v>0</v>
@@ -5057,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD36">
         <v>0</v>
@@ -5069,10 +5090,10 @@
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH36">
         <v>0</v>
@@ -5081,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK36" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL36" s="3">
         <v>45863.79166666666</v>
@@ -5098,16 +5119,16 @@
         <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F37" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -5122,88 +5143,88 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L37">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="M37">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N37">
+        <v>2.28</v>
+      </c>
+      <c r="O37">
+        <v>2.25</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>1.8</v>
+      </c>
+      <c r="R37">
+        <v>1.44</v>
+      </c>
+      <c r="S37">
+        <v>2.63</v>
+      </c>
+      <c r="T37">
         <v>3</v>
       </c>
-      <c r="O37">
-        <v>1.85</v>
-      </c>
-      <c r="P37">
-        <v>8.5</v>
-      </c>
-      <c r="Q37">
-        <v>2.25</v>
-      </c>
-      <c r="R37">
-        <v>1.38</v>
-      </c>
-      <c r="S37">
-        <v>2.8</v>
-      </c>
-      <c r="T37">
-        <v>2.75</v>
-      </c>
       <c r="U37">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V37">
         <v>7</v>
       </c>
       <c r="W37">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AB37">
+        <v>1.99</v>
+      </c>
+      <c r="AC37">
+        <v>1.72</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
         <v>1.91</v>
       </c>
-      <c r="AC37">
-        <v>1.83</v>
-      </c>
-      <c r="AD37">
-        <v>3.3</v>
-      </c>
-      <c r="AE37">
-        <v>1.3</v>
-      </c>
-      <c r="AF37">
-        <v>1.67</v>
-      </c>
       <c r="AG37">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH37">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AI37">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK37" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL37" s="3">
-        <v>45863.83333333334</v>
+        <v>45863.79166666666</v>
       </c>
     </row>
     <row r="38" spans="1:38">
@@ -5211,19 +5232,19 @@
         <v>45863</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E38" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F38" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5238,88 +5259,88 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH38">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AI38">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK38" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL38" s="3">
-        <v>45863.85416666666</v>
+        <v>45863.79166666666</v>
       </c>
     </row>
     <row r="39" spans="1:38">
@@ -5330,16 +5351,16 @@
         <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E39" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F39" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -5354,88 +5375,88 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L39">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="M39">
-        <v>3.79</v>
+        <v>3.3</v>
       </c>
       <c r="N39">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="O39">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="P39">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="Q39">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="R39">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S39">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T39">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="U39">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V39">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="W39">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Z39">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AA39">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="AB39">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AC39">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD39">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="AE39">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AF39">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH39">
-        <v>4.75</v>
+        <v>5.8</v>
       </c>
       <c r="AI39">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AJ39" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK39" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL39" s="3">
-        <v>45863.85416666666</v>
+        <v>45863.83333333334</v>
       </c>
     </row>
     <row r="40" spans="1:38">
@@ -5446,16 +5467,16 @@
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E40" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F40" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5470,88 +5491,88 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L40">
+        <v>2</v>
+      </c>
+      <c r="M40">
+        <v>3.6</v>
+      </c>
+      <c r="N40">
+        <v>2.92</v>
+      </c>
+      <c r="O40">
+        <v>1.77</v>
+      </c>
+      <c r="P40">
+        <v>17</v>
+      </c>
+      <c r="Q40">
+        <v>2.1</v>
+      </c>
+      <c r="R40">
+        <v>1.25</v>
+      </c>
+      <c r="S40">
+        <v>3.5</v>
+      </c>
+      <c r="T40">
+        <v>2.15</v>
+      </c>
+      <c r="U40">
         <v>1.62</v>
       </c>
-      <c r="M40">
-        <v>3.9</v>
-      </c>
-      <c r="N40">
-        <v>4.1</v>
-      </c>
-      <c r="O40">
+      <c r="V40">
+        <v>4.5</v>
+      </c>
+      <c r="W40">
+        <v>1.17</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>17</v>
+      </c>
+      <c r="Z40">
+        <v>1.17</v>
+      </c>
+      <c r="AA40">
+        <v>5</v>
+      </c>
+      <c r="AB40">
+        <v>1.5</v>
+      </c>
+      <c r="AC40">
+        <v>2.4</v>
+      </c>
+      <c r="AD40">
+        <v>2.2</v>
+      </c>
+      <c r="AE40">
+        <v>1.6</v>
+      </c>
+      <c r="AF40">
         <v>1.44</v>
       </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>2.75</v>
-      </c>
-      <c r="R40">
-        <v>1.22</v>
-      </c>
-      <c r="S40">
-        <v>3.8</v>
-      </c>
-      <c r="T40">
-        <v>2.1</v>
-      </c>
-      <c r="U40">
-        <v>1.67</v>
-      </c>
-      <c r="V40">
-        <v>4.33</v>
-      </c>
-      <c r="W40">
-        <v>1.18</v>
-      </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>0</v>
-      </c>
-      <c r="Z40">
-        <v>1.12</v>
-      </c>
-      <c r="AA40">
-        <v>5.25</v>
-      </c>
-      <c r="AB40">
-        <v>1.44</v>
-      </c>
-      <c r="AC40">
+      <c r="AG40">
         <v>2.6</v>
       </c>
-      <c r="AD40">
-        <v>2.1</v>
-      </c>
-      <c r="AE40">
-        <v>1.65</v>
-      </c>
-      <c r="AF40">
-        <v>1.5</v>
-      </c>
-      <c r="AG40">
-        <v>2.4</v>
-      </c>
       <c r="AH40">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="AI40">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AJ40" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK40" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL40" s="3">
-        <v>45863.875</v>
+        <v>45863.85416666666</v>
       </c>
     </row>
     <row r="41" spans="1:38">
@@ -5559,19 +5580,19 @@
         <v>45863</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E41" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F41" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -5586,88 +5607,88 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH41">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ41" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK41" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL41" s="3">
-        <v>45863.88541666666</v>
+        <v>45863.85416666666</v>
       </c>
     </row>
     <row r="42" spans="1:38">
@@ -5678,16 +5699,16 @@
         <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E42" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F42" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -5702,43 +5723,43 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P42">
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X42">
         <v>0</v>
@@ -5747,43 +5768,43 @@
         <v>0</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI42">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ42" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK42" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL42" s="3">
-        <v>45863.88541666666</v>
+        <v>45863.875</v>
       </c>
     </row>
     <row r="43" spans="1:38">
@@ -5794,16 +5815,16 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D43" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E43" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F43" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -5818,88 +5839,88 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L43">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N43">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH43">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI43">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK43" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL43" s="3">
-        <v>45863.89583333334</v>
+        <v>45863.88541666666</v>
       </c>
     </row>
     <row r="44" spans="1:38">
@@ -5910,16 +5931,16 @@
         <v>52</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D44" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E44" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F44" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -5934,43 +5955,43 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L44">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M44">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N44">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P44">
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X44">
         <v>0</v>
@@ -5979,43 +6000,43 @@
         <v>0</v>
       </c>
       <c r="Z44">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH44">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI44">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK44" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL44" s="3">
-        <v>45863.89583333334</v>
+        <v>45863.88541666666</v>
       </c>
     </row>
     <row r="45" spans="1:38">
@@ -6023,19 +6044,19 @@
         <v>45863</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D45" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E45" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F45" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -6050,43 +6071,43 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L45">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="M45">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N45">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="O45">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="P45">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q45">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S45">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T45">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U45">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V45">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W45">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X45">
         <v>1.04</v>
@@ -6098,13 +6119,13 @@
         <v>1.2</v>
       </c>
       <c r="AA45">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB45">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC45">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD45">
         <v>2.55</v>
@@ -6113,22 +6134,22 @@
         <v>1.5</v>
       </c>
       <c r="AF45">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG45">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH45">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AI45">
         <v>1.2</v>
       </c>
       <c r="AJ45" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK45" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL45" s="3">
         <v>45863.89583333334</v>
@@ -6142,16 +6163,16 @@
         <v>53</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E46" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F46" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -6166,37 +6187,37 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L46">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="M46">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N46">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="O46">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q46">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R46">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S46">
         <v>3.4</v>
       </c>
       <c r="T46">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U46">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V46">
         <v>5</v>
@@ -6205,49 +6226,49 @@
         <v>1.14</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB46">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC46">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF46">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG46">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AH46">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI46">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ46" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK46" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL46" s="3">
-        <v>45863.95833333334</v>
+        <v>45863.89583333334</v>
       </c>
     </row>
     <row r="47" spans="1:38">
@@ -6255,19 +6276,19 @@
         <v>45863</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D47" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E47" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F47" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -6282,43 +6303,43 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L47">
+        <v>2.41</v>
+      </c>
+      <c r="M47">
+        <v>3.52</v>
+      </c>
+      <c r="N47">
+        <v>2.5</v>
+      </c>
+      <c r="O47">
+        <v>1.8</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>2</v>
+      </c>
+      <c r="R47">
+        <v>1.22</v>
+      </c>
+      <c r="S47">
+        <v>3.8</v>
+      </c>
+      <c r="T47">
         <v>2.1</v>
       </c>
-      <c r="M47">
-        <v>3.56</v>
-      </c>
-      <c r="N47">
-        <v>2.75</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
       <c r="U47">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X47">
         <v>0</v>
@@ -6327,43 +6348,43 @@
         <v>0</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB47">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AC47">
+        <v>2.66</v>
+      </c>
+      <c r="AD47">
         <v>2.1</v>
       </c>
-      <c r="AD47">
-        <v>0</v>
-      </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH47">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AI47">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ47" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AK47" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AL47" s="3">
-        <v>45863.97916666666</v>
+        <v>45863.89583333334</v>
       </c>
     </row>
     <row r="48" spans="1:38">
@@ -6377,108 +6398,340 @@
         <v>77</v>
       </c>
       <c r="D48" t="s">
+        <v>81</v>
+      </c>
+      <c r="E48" t="s">
+        <v>129</v>
+      </c>
+      <c r="F48" t="s">
+        <v>178</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
+        <v>181</v>
+      </c>
+      <c r="L48">
+        <v>2.04</v>
+      </c>
+      <c r="M48">
+        <v>3.55</v>
+      </c>
+      <c r="N48">
+        <v>3.05</v>
+      </c>
+      <c r="O48">
+        <v>1.67</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>2.3</v>
+      </c>
+      <c r="R48">
+        <v>1.3</v>
+      </c>
+      <c r="S48">
+        <v>3.4</v>
+      </c>
+      <c r="T48">
+        <v>2.38</v>
+      </c>
+      <c r="U48">
+        <v>1.53</v>
+      </c>
+      <c r="V48">
+        <v>5</v>
+      </c>
+      <c r="W48">
+        <v>1.14</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>1.59</v>
+      </c>
+      <c r="AC48">
+        <v>2.2</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>1.62</v>
+      </c>
+      <c r="AG48">
+        <v>2.2</v>
+      </c>
+      <c r="AH48">
+        <v>0</v>
+      </c>
+      <c r="AI48">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>184</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>184</v>
+      </c>
+      <c r="AL48" s="3">
+        <v>45863.95833333334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:38">
+      <c r="A49" s="2">
+        <v>45863</v>
+      </c>
+      <c r="B49" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" t="s">
         <v>79</v>
       </c>
-      <c r="E48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F48" t="s">
-        <v>174</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48" t="s">
-        <v>175</v>
-      </c>
-      <c r="L48">
+      <c r="D49" t="s">
+        <v>81</v>
+      </c>
+      <c r="E49" t="s">
+        <v>130</v>
+      </c>
+      <c r="F49" t="s">
+        <v>179</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" t="s">
+        <v>181</v>
+      </c>
+      <c r="L49">
+        <v>2.1</v>
+      </c>
+      <c r="M49">
+        <v>3.56</v>
+      </c>
+      <c r="N49">
+        <v>2.75</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>1.65</v>
+      </c>
+      <c r="AC49">
+        <v>2.1</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49">
+        <v>0</v>
+      </c>
+      <c r="AI49">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="s">
+        <v>184</v>
+      </c>
+      <c r="AK49" t="s">
+        <v>184</v>
+      </c>
+      <c r="AL49" s="3">
+        <v>45863.97916666666</v>
+      </c>
+    </row>
+    <row r="50" spans="1:38">
+      <c r="A50" s="2">
+        <v>45863</v>
+      </c>
+      <c r="B50" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50" t="s">
+        <v>81</v>
+      </c>
+      <c r="E50" t="s">
+        <v>131</v>
+      </c>
+      <c r="F50" t="s">
+        <v>180</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" t="s">
+        <v>181</v>
+      </c>
+      <c r="L50">
         <v>1.43</v>
       </c>
-      <c r="M48">
+      <c r="M50">
         <v>4.2</v>
       </c>
-      <c r="N48">
+      <c r="N50">
         <v>5.5</v>
       </c>
-      <c r="O48">
+      <c r="O50">
         <v>1.43</v>
       </c>
-      <c r="P48">
+      <c r="P50">
         <v>15</v>
       </c>
-      <c r="Q48">
+      <c r="Q50">
         <v>2.95</v>
       </c>
-      <c r="R48">
+      <c r="R50">
         <v>1.25</v>
       </c>
-      <c r="S48">
+      <c r="S50">
         <v>3.6</v>
       </c>
-      <c r="T48">
+      <c r="T50">
         <v>2.1</v>
       </c>
-      <c r="U48">
+      <c r="U50">
         <v>1.63</v>
       </c>
-      <c r="V48">
+      <c r="V50">
         <v>4.6</v>
       </c>
-      <c r="W48">
+      <c r="W50">
         <v>1.17</v>
       </c>
-      <c r="X48">
+      <c r="X50">
         <v>1.03</v>
       </c>
-      <c r="Y48">
+      <c r="Y50">
         <v>11</v>
       </c>
-      <c r="Z48">
+      <c r="Z50">
         <v>1.14</v>
       </c>
-      <c r="AA48">
+      <c r="AA50">
         <v>5.5</v>
       </c>
-      <c r="AB48">
+      <c r="AB50">
         <v>1.53</v>
       </c>
-      <c r="AC48">
+      <c r="AC50">
         <v>2.37</v>
       </c>
-      <c r="AD48">
+      <c r="AD50">
         <v>2.15</v>
       </c>
-      <c r="AE48">
+      <c r="AE50">
         <v>1.7</v>
       </c>
-      <c r="AF48">
+      <c r="AF50">
         <v>1.6</v>
       </c>
-      <c r="AG48">
+      <c r="AG50">
         <v>2.15</v>
       </c>
-      <c r="AH48">
+      <c r="AH50">
         <v>3.55</v>
       </c>
-      <c r="AI48">
+      <c r="AI50">
         <v>1.28</v>
       </c>
-      <c r="AJ48" t="s">
-        <v>177</v>
-      </c>
-      <c r="AK48" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL48" s="3">
+      <c r="AJ50" t="s">
+        <v>184</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>184</v>
+      </c>
+      <c r="AL50" s="3">
         <v>45863.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -802,7 +802,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,40 +1070,40 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1130,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1198,80 +1198,80 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1330,80 +1330,80 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>2.68</v>
       </c>
       <c r="M10" t="n">
-        <v>3.09</v>
+        <v>3.31</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.67</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.3</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.1</v>
+        <v>2.01</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>3.59</v>
       </c>
       <c r="N14" t="n">
-        <v>1.77</v>
+        <v>3.39</v>
       </c>
       <c r="O14" t="n">
-        <v>2.96</v>
+        <v>1.67</v>
       </c>
       <c r="P14" t="n">
-        <v>8.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V14" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.5</v>
+        <v>11.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>3.56</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>3.26</v>
+        <v>3.39</v>
       </c>
       <c r="N16" t="n">
-        <v>4.78</v>
+        <v>5.21</v>
       </c>
       <c r="O16" t="n">
         <v>1.6</v>
@@ -2540,19 +2540,19 @@
         <v>3.18</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U16" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
@@ -2561,28 +2561,28 @@
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AG16" t="n">
         <v>1.58</v>
@@ -2591,7 +2591,7 @@
         <v>10</v>
       </c>
       <c r="AI16" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="M17" t="n">
-        <v>3.21</v>
+        <v>3.68</v>
       </c>
       <c r="N17" t="n">
-        <v>3.31</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.4</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.84</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.65</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.64</v>
+        <v>4.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.64</v>
+        <v>2.01</v>
       </c>
       <c r="M18" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1.3</v>
       </c>
-      <c r="S18" t="n">
+      <c r="AA18" t="n">
         <v>3.2</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.6</v>
+        <v>3.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.57</v>
+        <v>3.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
         <v>2</v>
@@ -2966,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
         <v>2.2</v>
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>3.53</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.58</v>
@@ -3089,7 +3089,7 @@
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>14.1</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
         <v>1.15</v>
@@ -3098,16 +3098,16 @@
         <v>4.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
         <v>1.5</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>8.5</v>
+        <v>2.04</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.28</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="R21" t="n">
         <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.99</v>
+        <v>8.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.14</v>
+        <v>1.33</v>
       </c>
       <c r="O22" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T22" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.37</v>
+        <v>3.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.64</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O23" t="n">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="P23" t="n">
-        <v>14.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="T23" t="n">
-        <v>2.39</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>1.57</v>
@@ -3596,22 +3596,22 @@
         <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
         <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -3620,19 +3620,19 @@
         <v>10</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC24" t="n">
         <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AE24" t="n">
         <v>1.36</v>
@@ -3641,10 +3641,10 @@
         <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH24" t="n">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="AI24" t="n">
         <v>1.1</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.31</v>
+        <v>4.05</v>
       </c>
       <c r="M25" t="n">
-        <v>3.03</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="O25" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>8.75</v>
+        <v>14.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>10.8</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>6.24</v>
+        <v>4.8</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.8</v>
+        <v>2.36</v>
       </c>
       <c r="M26" t="n">
-        <v>3.19</v>
+        <v>3.42</v>
       </c>
       <c r="N26" t="n">
-        <v>1.84</v>
+        <v>2.89</v>
       </c>
       <c r="O26" t="n">
-        <v>2.71</v>
+        <v>1.93</v>
       </c>
       <c r="P26" t="n">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z26" t="n">
         <v>1.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AH26" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.28</v>
+        <v>4.9</v>
       </c>
       <c r="M27" t="n">
-        <v>2.91</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.96</v>
+        <v>1.48</v>
       </c>
       <c r="O27" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U27" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.94</v>
+        <v>2.75</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AH27" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.03</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>3.39</v>
+        <v>2.91</v>
       </c>
       <c r="N28" t="n">
-        <v>2.02</v>
+        <v>2.96</v>
       </c>
       <c r="O28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2.3</v>
       </c>
-      <c r="P28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.67</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="S28" t="n">
-        <v>3.26</v>
+        <v>2.3</v>
       </c>
       <c r="T28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V28" t="n">
+        <v>10</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AA28" t="n">
         <v>2.5</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4.19</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AC28" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.59</v>
+        <v>4.94</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.61</v>
+        <v>2.08</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.24</v>
+        <v>1.72</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.88</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.97</v>
+        <v>2.59</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.31</v>
+        <v>2.45</v>
       </c>
       <c r="O29" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="P29" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="T29" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="U29" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="Z29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.29</v>
       </c>
-      <c r="AA29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AF29" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG29" t="n">
         <v>2</v>
       </c>
       <c r="AH29" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.59</v>
+        <v>1.76</v>
       </c>
       <c r="M30" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>2.45</v>
+        <v>3.84</v>
       </c>
       <c r="O30" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>2.65</v>
+        <v>2.93</v>
       </c>
       <c r="T30" t="n">
-        <v>2.98</v>
+        <v>2.64</v>
       </c>
       <c r="U30" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AC30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF30" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD30" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG30" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH30" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.9</v>
+        <v>1.97</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>1.48</v>
+        <v>3.31</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="P31" t="n">
-        <v>14.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.14</v>
+        <v>2.79</v>
       </c>
       <c r="T31" t="n">
         <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
         <v>6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AA31" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG31" t="n">
         <v>2</v>
       </c>
-      <c r="AD31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH31" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.76</v>
+        <v>3.07</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="N33" t="n">
-        <v>3.84</v>
+        <v>2.02</v>
       </c>
       <c r="O33" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="P33" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
         <v>6.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
         <v>1.91</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="N34" t="n">
         <v>2.02</v>
       </c>
       <c r="O34" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="P34" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="Q34" t="n">
         <v>1.67</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="T34" t="n">
         <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V34" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.6</v>
+        <v>4.19</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AH34" t="n">
-        <v>5.75</v>
+        <v>4.88</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.39</v>
+        <v>2.57</v>
       </c>
       <c r="M35" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5072,34 +5072,34 @@
         <v>7</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AA35" t="n">
         <v>2.62</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD35" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AE35" t="n">
         <v>1.2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH35" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,40 +5162,40 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5222,10 +5222,10 @@
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,40 +5426,40 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O40" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P40" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC40" t="n">
         <v>2.1</v>
       </c>
-      <c r="R40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG40" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH40" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="O41" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P41" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE41" t="n">
         <v>1.6</v>
       </c>
-      <c r="P41" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V41" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF41" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH41" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,40 +6350,40 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="M45" t="n">
-        <v>3.33</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>2.54</v>
+        <v>2.98</v>
       </c>
       <c r="O45" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="P45" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R45" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S45" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T45" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="U45" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V45" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X45" t="n">
         <v>1.04</v>
@@ -6395,13 +6395,13 @@
         <v>1.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD45" t="n">
         <v>2.55</v>
@@ -6410,13 +6410,13 @@
         <v>1.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI45" t="n">
         <v>1.2</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,40 +6614,40 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="M47" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N47" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="O47" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S47" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T47" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U47" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V47" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W47" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X47" t="n">
         <v>1.04</v>
@@ -6659,13 +6659,13 @@
         <v>1.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD47" t="n">
         <v>2.55</v>
@@ -6674,13 +6674,13 @@
         <v>1.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AI47" t="n">
         <v>1.2</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>3.56</v>
       </c>
       <c r="N49" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="O49" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC49" t="n">
         <v>2.1</v>
       </c>
-      <c r="U49" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V49" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AD49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P50" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T50" t="n">
         <v>2.1</v>
       </c>
-      <c r="M50" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="M2" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1.64</v>
@@ -695,55 +695,55 @@
         <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V2" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="n">
         <v>4.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.39</v>
       </c>
       <c r="O5" t="n">
         <v>1.67</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1462,80 +1462,80 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.68</v>
+        <v>1.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.31</v>
+        <v>3.62</v>
       </c>
       <c r="N10" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="O10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2.3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.67</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AG10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.01</v>
+        <v>3.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1.67</v>
       </c>
-      <c r="P14" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.07</v>
+        <v>1.89</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
         <v>3.4</v>
       </c>
       <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG19" t="n">
         <v>2.5</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.89</v>
+        <v>3.07</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
         <v>3.4</v>
       </c>
       <c r="T20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG20" t="n">
         <v>2.25</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AH20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.04</v>
+        <v>8.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="O21" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T21" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2</v>
-      </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8.5</v>
+        <v>2.04</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="P22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.8</v>
+        <v>2.36</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>3.42</v>
       </c>
       <c r="N23" t="n">
-        <v>1.84</v>
+        <v>2.89</v>
       </c>
       <c r="O23" t="n">
-        <v>2.71</v>
+        <v>1.93</v>
       </c>
       <c r="P23" t="n">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="n">
         <v>1.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AH23" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>3.19</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>1.84</v>
       </c>
       <c r="O24" t="n">
-        <v>1.57</v>
+        <v>2.71</v>
       </c>
       <c r="P24" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Z24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.22</v>
       </c>
-      <c r="AA24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>2.89</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="P26" t="n">
-        <v>8.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
         <v>10</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AH26" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,73 +3974,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P27" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="R27" t="n">
         <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AA27" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AI27" t="n">
         <v>1.13</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="M28" t="n">
-        <v>2.91</v>
+        <v>3.31</v>
       </c>
       <c r="N28" t="n">
-        <v>2.96</v>
+        <v>3.34</v>
       </c>
       <c r="O28" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="P28" t="n">
-        <v>6.4</v>
+        <v>11.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R28" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.29</v>
       </c>
-      <c r="V28" t="n">
-        <v>10</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF28" t="n">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="AH28" t="n">
-        <v>9.199999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="S29" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.98</v>
+        <v>3.42</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="V29" t="n">
-        <v>7.3</v>
+        <v>9.75</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.19</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AC29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD29" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2</v>
-      </c>
       <c r="AH29" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.76</v>
+        <v>1.31</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>4.99</v>
       </c>
       <c r="N30" t="n">
-        <v>3.84</v>
+        <v>7.18</v>
       </c>
       <c r="O30" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="P30" t="n">
-        <v>13</v>
+        <v>16.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.699999999999999</v>
+        <v>14.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.97</v>
+        <v>5.69</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>3.31</v>
+        <v>1.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>11.75</v>
+        <v>14.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="R31" t="n">
         <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U31" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V31" t="n">
         <v>6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD31" t="n">
         <v>2.9</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG31" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH31" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.37</v>
+        <v>3.1</v>
       </c>
       <c r="M32" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>6.2</v>
+        <v>2.07</v>
       </c>
       <c r="O32" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="P32" t="n">
-        <v>16.25</v>
+        <v>13.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S32" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="T32" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="V32" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W32" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="M33" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="O33" t="n">
         <v>2.25</v>
       </c>
       <c r="P33" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="R33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V33" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z33" t="n">
         <v>1.33</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V33" t="n">
+      <c r="AA33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH33" t="n">
         <v>6.5</v>
       </c>
-      <c r="W33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AI33" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.03</v>
+        <v>1.81</v>
       </c>
       <c r="M34" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="O34" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="P34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="R34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1.32</v>
       </c>
-      <c r="S34" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V34" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC34" t="n">
+      <c r="AF34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG34" t="n">
         <v>2</v>
       </c>
-      <c r="AD34" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AH34" t="n">
-        <v>4.88</v>
+        <v>5.7</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5039,13 +5039,13 @@
         <v>2.57</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R35" t="n">
         <v>1.5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,40 +5294,40 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,40 +5426,40 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="O40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE40" t="n">
         <v>1.6</v>
       </c>
-      <c r="P40" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N41" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O41" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P41" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V41" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC41" t="n">
         <v>2.1</v>
       </c>
-      <c r="R41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD41" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG41" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH41" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>2.1</v>
       </c>
       <c r="U42" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="V42" t="n">
         <v>4.33</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M46" t="n">
         <v>3.85</v>
       </c>
       <c r="N46" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="O46" t="n">
         <v>1.8</v>
@@ -6536,7 +6536,7 @@
         <v>2.62</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE46" t="n">
         <v>1.67</v>
@@ -6548,7 +6548,7 @@
         <v>2.7</v>
       </c>
       <c r="AH46" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AI46" t="n">
         <v>1.29</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1462,44 +1462,44 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1526,10 +1526,10 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>2.92</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="R9" t="n">
         <v>1.33</v>
@@ -1622,52 +1622,52 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
         <v>2.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,40 +1730,40 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="U13" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.75</v>
+        <v>3.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.1</v>
+        <v>2.01</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>3.39</v>
       </c>
       <c r="O14" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="P14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V14" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AH14" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>8.5</v>
+        <v>2.04</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.04</v>
+        <v>8.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="O22" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T22" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2</v>
-      </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.36</v>
+        <v>4.05</v>
       </c>
       <c r="M23" t="n">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>2.89</v>
+        <v>1.93</v>
       </c>
       <c r="O23" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>8.75</v>
+        <v>14.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.8</v>
+        <v>2.36</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>3.42</v>
       </c>
       <c r="N24" t="n">
-        <v>1.84</v>
+        <v>2.89</v>
       </c>
       <c r="O24" t="n">
-        <v>2.71</v>
+        <v>1.93</v>
       </c>
       <c r="P24" t="n">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z24" t="n">
         <v>1.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AH24" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>3.19</v>
       </c>
       <c r="N25" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="P25" t="n">
-        <v>14.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="T25" t="n">
-        <v>2.48</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="V25" t="n">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.17</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.07</v>
+        <v>1.98</v>
       </c>
       <c r="M27" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.34</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.02</v>
-      </c>
       <c r="O27" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="P27" t="n">
-        <v>10.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC27" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AH27" t="n">
         <v>5.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.98</v>
+        <v>1.31</v>
       </c>
       <c r="M28" t="n">
-        <v>3.31</v>
+        <v>4.99</v>
       </c>
       <c r="N28" t="n">
-        <v>3.34</v>
+        <v>7.18</v>
       </c>
       <c r="O28" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="P28" t="n">
-        <v>11.75</v>
+        <v>16.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>10</v>
+        <v>14.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.16</v>
+        <v>2.42</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="M30" t="n">
-        <v>4.99</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>7.18</v>
+        <v>4.2</v>
       </c>
       <c r="O30" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="P30" t="n">
-        <v>16.25</v>
+        <v>13</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="U30" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>14.3</v>
+        <v>10.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.33</v>
+        <v>3.64</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.69</v>
+        <v>2.88</v>
       </c>
       <c r="M31" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="O31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V31" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA31" t="n">
         <v>3.1</v>
       </c>
-      <c r="P31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V31" t="n">
-        <v>6</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AF31" t="n">
         <v>1.8</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O32" t="n">
         <v>3.1</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.3</v>
-      </c>
       <c r="P32" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.67</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V32" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC32" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD32" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="O33" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="R33" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S33" t="n">
-        <v>2.65</v>
+        <v>3.26</v>
       </c>
       <c r="T33" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="V33" t="n">
-        <v>7.3</v>
+        <v>5.75</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AB33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC33" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC33" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD33" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="AH33" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.81</v>
+        <v>3.07</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>4.2</v>
+        <v>2.02</v>
       </c>
       <c r="O34" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="P34" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="R34" t="n">
         <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T34" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V34" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X34" t="n">
         <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>10.8</v>
+        <v>9.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG34" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,40 +5294,40 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,40 +5426,40 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O40" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P40" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC40" t="n">
         <v>2.1</v>
       </c>
-      <c r="R40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG40" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH40" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="O41" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P41" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE41" t="n">
         <v>1.6</v>
       </c>
-      <c r="P41" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V41" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF41" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH41" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,40 +6350,40 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N45" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="O45" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="P45" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S45" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T45" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U45" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V45" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W45" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X45" t="n">
         <v>1.04</v>
@@ -6395,13 +6395,13 @@
         <v>1.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD45" t="n">
         <v>2.55</v>
@@ -6410,13 +6410,13 @@
         <v>1.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AI45" t="n">
         <v>1.2</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,40 +6614,40 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="M47" t="n">
-        <v>3.33</v>
+        <v>3.65</v>
       </c>
       <c r="N47" t="n">
-        <v>2.54</v>
+        <v>2.98</v>
       </c>
       <c r="O47" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="P47" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S47" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T47" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="U47" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V47" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X47" t="n">
         <v>1.04</v>
@@ -6659,13 +6659,13 @@
         <v>1.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD47" t="n">
         <v>2.55</v>
@@ -6674,13 +6674,13 @@
         <v>1.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI47" t="n">
         <v>1.2</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P49" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T49" t="n">
         <v>2.1</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="M50" t="n">
-        <v>4.2</v>
+        <v>3.56</v>
       </c>
       <c r="N50" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC50" t="n">
         <v>2.1</v>
       </c>
-      <c r="U50" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V50" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AD50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL50"/>
+  <dimension ref="A1:AL51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,40 +1334,40 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="M8" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.3</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1594,80 +1594,80 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2386,80 +2386,80 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="M16" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="N16" t="n">
-        <v>5.21</v>
+        <v>4.78</v>
       </c>
       <c r="O16" t="n">
         <v>1.6</v>
@@ -2564,28 +2564,28 @@
         <v>7.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="AE16" t="n">
         <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
         <v>10</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.64</v>
+        <v>2.01</v>
       </c>
       <c r="M17" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z17" t="n">
         <v>1.3</v>
       </c>
-      <c r="S17" t="n">
+      <c r="AA17" t="n">
         <v>3.2</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.6</v>
+        <v>3.32</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="N18" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.4</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.84</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.32</v>
+        <v>2.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.58</v>
@@ -2936,22 +2936,22 @@
         <v>2.33</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V19" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
         <v>1.03</v>
@@ -2960,34 +2960,34 @@
         <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AC19" t="n">
         <v>2.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AE19" t="n">
         <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AH19" t="n">
         <v>3.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="M20" t="n">
         <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.04</v>
+        <v>8.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="O21" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T21" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2</v>
-      </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8.5</v>
+        <v>2.04</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="P22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.05</v>
+        <v>2.37</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O23" t="n">
         <v>1.93</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.25</v>
-      </c>
       <c r="P23" t="n">
-        <v>14.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>5.25</v>
+        <v>7.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.17</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.36</v>
+        <v>3.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.42</v>
+        <v>3.19</v>
       </c>
       <c r="N24" t="n">
-        <v>2.89</v>
+        <v>1.84</v>
       </c>
       <c r="O24" t="n">
-        <v>1.93</v>
+        <v>2.71</v>
       </c>
       <c r="P24" t="n">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Z24" t="n">
         <v>1.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="O25" t="n">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>2.69</v>
+        <v>3.14</v>
       </c>
       <c r="T25" t="n">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.52</v>
+        <v>2.65</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>7.1</v>
+        <v>4.72</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M26" t="n">
         <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="O26" t="n">
         <v>1.57</v>
@@ -3860,58 +3860,58 @@
         <v>2.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T26" t="n">
         <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z26" t="n">
         <v>1.22</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
         <v>2.07</v>
       </c>
       <c r="AH26" t="n">
-        <v>5.25</v>
+        <v>5.37</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.98</v>
+        <v>3.07</v>
       </c>
       <c r="M27" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>3.34</v>
+        <v>2.02</v>
       </c>
       <c r="O27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1.67</v>
       </c>
-      <c r="P27" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.38</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="n">
         <v>5.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.31</v>
+        <v>1.98</v>
       </c>
       <c r="M28" t="n">
-        <v>4.99</v>
+        <v>3.31</v>
       </c>
       <c r="N28" t="n">
-        <v>7.18</v>
+        <v>3.34</v>
       </c>
       <c r="O28" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="P28" t="n">
-        <v>16.25</v>
+        <v>11.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>14.3</v>
+        <v>10</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.42</v>
+        <v>3.16</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AH28" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="M29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.9</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.42</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>9.75</v>
+        <v>7.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.08</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="O31" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
-        <v>2.65</v>
+        <v>3.26</v>
       </c>
       <c r="T31" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>7.3</v>
+        <v>5.75</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AB31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC31" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD31" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N33" t="n">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q33" t="n">
         <v>2.3</v>
       </c>
-      <c r="P33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.67</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="S33" t="n">
-        <v>3.26</v>
+        <v>2.3</v>
       </c>
       <c r="T33" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V33" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA33" t="n">
         <v>2.5</v>
       </c>
-      <c r="U33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V33" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AB33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG33" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AH33" t="n">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.07</v>
+        <v>1.31</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>4.99</v>
       </c>
       <c r="N34" t="n">
-        <v>2.02</v>
+        <v>7.18</v>
       </c>
       <c r="O34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P34" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC34" t="n">
         <v>2.25</v>
       </c>
-      <c r="P34" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U34" t="n">
+      <c r="AD34" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1.5</v>
       </c>
-      <c r="V34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF34" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,40 +5294,40 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,40 +5426,40 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="O40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE40" t="n">
         <v>1.6</v>
       </c>
-      <c r="P40" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N41" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O41" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P41" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V41" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC41" t="n">
         <v>2.1</v>
       </c>
-      <c r="R41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD41" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG41" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH41" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5972,58 +5972,58 @@
         <v>2.75</v>
       </c>
       <c r="R42" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T42" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG42" t="n">
         <v>2.1</v>
       </c>
-      <c r="U42" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V42" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AH42" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,40 +6350,40 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="M45" t="n">
-        <v>3.33</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>2.54</v>
+        <v>2.98</v>
       </c>
       <c r="O45" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="P45" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R45" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S45" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T45" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="U45" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V45" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X45" t="n">
         <v>1.04</v>
@@ -6395,13 +6395,13 @@
         <v>1.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD45" t="n">
         <v>2.55</v>
@@ -6410,13 +6410,13 @@
         <v>1.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI45" t="n">
         <v>1.2</v>
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="M46" t="n">
-        <v>3.85</v>
+        <v>3.79</v>
       </c>
       <c r="N46" t="n">
-        <v>2.28</v>
+        <v>3.51</v>
       </c>
       <c r="O46" t="n">
         <v>1.8</v>
@@ -6500,58 +6500,58 @@
         <v>2</v>
       </c>
       <c r="R46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V46" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AI46" t="n">
         <v>1.22</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V46" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.29</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,40 +6614,40 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="M47" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N47" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="O47" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S47" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T47" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U47" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V47" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W47" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X47" t="n">
         <v>1.04</v>
@@ -6659,13 +6659,13 @@
         <v>1.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD47" t="n">
         <v>2.55</v>
@@ -6674,13 +6674,13 @@
         <v>1.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AI47" t="n">
         <v>1.2</v>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,59 +6746,59 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.04</v>
+        <v>2.69</v>
       </c>
       <c r="M48" t="n">
-        <v>3.55</v>
+        <v>2.52</v>
       </c>
       <c r="N48" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="O48" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC48" t="n">
         <v>1.3</v>
       </c>
-      <c r="S48" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V48" t="n">
-        <v>5</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AD48" t="n">
         <v>0</v>
       </c>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="AL48" s="3" t="n">
-        <v>45863.95833333334</v>
+        <v>45863.91666666666</v>
       </c>
     </row>
     <row r="49">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="N49" t="n">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="O49" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="P49" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="R49" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T49" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U49" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="V49" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X49" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH49" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="AL49" s="3" t="n">
-        <v>45863.97916666666</v>
+        <v>45863.95833333334</v>
       </c>
     </row>
     <row r="50">
@@ -6984,114 +6984,246 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P50" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL50" s="3" t="n">
+        <v>45863.97916666666</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Nashville SC</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="L51" t="n">
         <v>2.1</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M51" t="n">
         <v>3.56</v>
       </c>
-      <c r="N50" t="n">
+      <c r="N51" t="n">
         <v>2.75</v>
       </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AC51" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL50" s="3" t="n">
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL51" s="3" t="n">
         <v>45863.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL51"/>
+  <dimension ref="A1:AL50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.64</v>
@@ -698,13 +698,13 @@
         <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U2" t="n">
         <v>1.52</v>
       </c>
       <c r="V2" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.11</v>
@@ -713,34 +713,34 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="AI2" t="n">
         <v>1.11</v>
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -802,7 +802,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -934,26 +934,26 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.01</v>
+        <v>2.68</v>
       </c>
       <c r="M5" t="n">
-        <v>3.59</v>
+        <v>3.31</v>
       </c>
       <c r="N5" t="n">
-        <v>3.39</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1.67</v>
       </c>
-      <c r="P5" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.76</v>
+        <v>2.51</v>
       </c>
       <c r="U5" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.22</v>
+        <v>2.74</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,40 +1334,40 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1594,80 +1594,80 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>3.09</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>3.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.96</v>
+        <v>1.67</v>
       </c>
       <c r="P15" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.4</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.84</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.32</v>
+        <v>2.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
-        <v>3.68</v>
+        <v>3.21</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>3.31</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.6</v>
+        <v>3.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.88</v>
+        <v>2.57</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>3.32</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>2.33</v>
       </c>
       <c r="O19" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG19" t="n">
         <v>2.25</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.44</v>
-      </c>
       <c r="AH19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.8</v>
+        <v>1.79</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.27</v>
+        <v>3.53</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>8.5</v>
+        <v>1.99</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>1.33</v>
+        <v>3.14</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD21" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.04</v>
+        <v>8.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA22" t="n">
         <v>3.2</v>
       </c>
-      <c r="O22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V22" t="n">
-        <v>7</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="AB22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.37</v>
+        <v>1.76</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>3.79</v>
       </c>
       <c r="O23" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="P23" t="n">
-        <v>8.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.38</v>
       </c>
-      <c r="V23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH23" t="n">
-        <v>6.75</v>
+        <v>5.37</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.6</v>
+        <v>2.31</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.03</v>
       </c>
       <c r="N25" t="n">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="P25" t="n">
-        <v>14.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="T25" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>5.25</v>
+        <v>7.6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.17</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.75</v>
+        <v>3.37</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>1.83</v>
       </c>
       <c r="O26" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="W26" t="n">
         <v>1.12</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>5.37</v>
+        <v>4.72</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="M28" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N28" t="n">
         <v>3.31</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.34</v>
       </c>
       <c r="O28" t="n">
         <v>1.67</v>
@@ -4127,52 +4127,52 @@
         <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
         <v>10</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AA28" t="n">
         <v>3.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
         <v>3.16</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AH28" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI28" t="n">
         <v>1.1</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T29" t="n">
         <v>3.2</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V29" t="n">
-        <v>7.3</v>
+        <v>10</v>
       </c>
       <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.07</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y29" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AH29" t="n">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.81</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N30" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="O30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P30" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.53</v>
       </c>
-      <c r="P30" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V30" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>10.8</v>
+        <v>15</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.64</v>
+        <v>4.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AG30" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O31" t="n">
         <v>3.1</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.3</v>
-      </c>
       <c r="P31" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.67</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG31" t="n">
         <v>2.05</v>
       </c>
-      <c r="AD31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AH31" t="n">
-        <v>4.7</v>
+        <v>5.45</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.69</v>
+        <v>2.59</v>
       </c>
       <c r="M32" t="n">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="N32" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P32" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="T32" t="n">
-        <v>2.62</v>
+        <v>2.93</v>
       </c>
       <c r="U32" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="M33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P33" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD33" t="n">
         <v>2.9</v>
       </c>
-      <c r="N33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P33" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V33" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AE33" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="n">
-        <v>9.199999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="AI33" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.31</v>
+        <v>3.03</v>
       </c>
       <c r="M34" t="n">
-        <v>4.99</v>
+        <v>3.39</v>
       </c>
       <c r="N34" t="n">
-        <v>7.18</v>
+        <v>2.02</v>
       </c>
       <c r="O34" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="P34" t="n">
-        <v>16.25</v>
+        <v>13.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="R34" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="T34" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="W34" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X34" t="n">
         <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>14.3</v>
+        <v>10.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="AB34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF34" t="n">
         <v>1.61</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AG34" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD34" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH34" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.57</v>
+        <v>2.39</v>
       </c>
       <c r="M35" t="n">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="N35" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="O35" t="n">
         <v>1.97</v>
@@ -5048,58 +5048,58 @@
         <v>2.15</v>
       </c>
       <c r="R35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V35" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Z35" t="n">
         <v>1.5</v>
       </c>
-      <c r="S35" t="n">
+      <c r="AA35" t="n">
         <v>2.4</v>
       </c>
-      <c r="T35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AB35" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AC35" t="n">
         <v>1.57</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH35" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,40 +5162,40 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5222,10 +5222,10 @@
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,40 +5294,40 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>1.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AD40" t="n">
         <v>2.2</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>3.79</v>
       </c>
       <c r="N45" t="n">
-        <v>2.98</v>
+        <v>3.51</v>
       </c>
       <c r="O45" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="P45" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T45" t="n">
         <v>2.2</v>
       </c>
-      <c r="R45" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V45" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD45" t="n">
         <v>2.25</v>
       </c>
-      <c r="U45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V45" t="n">
-        <v>5</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB45" t="n">
+      <c r="AE45" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE45" t="n">
+      <c r="AF45" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF45" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG45" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="M46" t="n">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="N46" t="n">
-        <v>3.51</v>
+        <v>2.98</v>
       </c>
       <c r="O46" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S46" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T46" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U46" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="V46" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH46" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,40 +6746,40 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.69</v>
+        <v>2.04</v>
       </c>
       <c r="M48" t="n">
-        <v>2.52</v>
+        <v>3.55</v>
       </c>
       <c r="N48" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
@@ -6788,16 +6788,16 @@
         <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH48" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="AL48" s="3" t="n">
-        <v>45863.91666666666</v>
+        <v>45863.95833333334</v>
       </c>
     </row>
     <row r="49">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.04</v>
+        <v>1.43</v>
       </c>
       <c r="M49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P49" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH49" t="n">
         <v>3.55</v>
       </c>
-      <c r="N49" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V49" t="n">
-        <v>5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="AL49" s="3" t="n">
-        <v>45863.95833333334</v>
+        <v>45863.97916666666</v>
       </c>
     </row>
     <row r="50">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="M50" t="n">
-        <v>4.2</v>
+        <v>3.56</v>
       </c>
       <c r="N50" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC50" t="n">
         <v>2.1</v>
       </c>
-      <c r="U50" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V50" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AD50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7092,138 +7092,6 @@
         </is>
       </c>
       <c r="AL50" s="3" t="n">
-        <v>45863.97916666666</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL51" s="3" t="n">
         <v>45863.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL50"/>
+  <dimension ref="A1:AL51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -802,80 +802,80 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -934,26 +934,26 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1594,80 +1594,80 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,40 +1730,40 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1858,80 +1858,80 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.1</v>
+        <v>2.01</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>3.59</v>
       </c>
       <c r="N14" t="n">
-        <v>1.77</v>
+        <v>3.39</v>
       </c>
       <c r="O14" t="n">
-        <v>2.96</v>
+        <v>1.67</v>
       </c>
       <c r="P14" t="n">
-        <v>8.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V14" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.5</v>
+        <v>11.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>3.56</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>3.7</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>1.67</v>
+        <v>2.96</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z15" t="n">
         <v>1.33</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="AA15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH15" t="n">
         <v>6.5</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45863.54166666666</v>
+        <v>45863.57291666666</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>3.68</v>
+        <v>3.21</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>3.31</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.6</v>
+        <v>3.32</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="M18" t="n">
-        <v>3.21</v>
+        <v>3.68</v>
       </c>
       <c r="N18" t="n">
-        <v>3.31</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.4</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.32</v>
+        <v>2.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.57</v>
+        <v>1.79</v>
       </c>
       <c r="M19" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2.33</v>
       </c>
-      <c r="O19" t="n">
-        <v>2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.83</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V19" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.53</v>
+        <v>1.35</v>
       </c>
       <c r="O20" t="n">
-        <v>1.58</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>15</v>
+        <v>10.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.52</v>
+        <v>1.81</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.52</v>
+        <v>2.35</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.44</v>
+        <v>1.57</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3141,12 +3141,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,40 +3182,40 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.99</v>
+        <v>2.57</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N21" t="n">
-        <v>3.14</v>
+        <v>2.33</v>
       </c>
       <c r="O21" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.5</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3242,10 +3242,10 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>45863.625</v>
+        <v>45863.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8.5</v>
+        <v>1.99</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>1.28</v>
+        <v>3.14</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="P22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC22" t="n">
         <v>1.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.34</v>
+        <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,37 +3578,37 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.8</v>
+        <v>2.31</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="N24" t="n">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
-        <v>2.71</v>
+        <v>1.93</v>
       </c>
       <c r="P24" t="n">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W24" t="n">
         <v>1.03</v>
@@ -3617,13 +3617,13 @@
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z24" t="n">
         <v>1.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="AB24" t="n">
         <v>1.95</v>
@@ -3632,19 +3632,19 @@
         <v>1.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="n">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="AI24" t="n">
         <v>1.04</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.31</v>
+        <v>3.37</v>
       </c>
       <c r="M25" t="n">
-        <v>3.03</v>
+        <v>3.64</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="O25" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>8.75</v>
+        <v>14.5</v>
       </c>
       <c r="Q25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC25" t="n">
         <v>2.05</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD25" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG25" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>6.75</v>
+        <v>4.72</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3801,27 +3801,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.37</v>
+        <v>1.37</v>
       </c>
       <c r="M26" t="n">
-        <v>3.64</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.83</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="P26" t="n">
-        <v>14.5</v>
+        <v>16.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.73</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.12</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AA26" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.65</v>
+        <v>2.16</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="AL26" s="3" t="n">
-        <v>45863.64583333334</v>
+        <v>45863.65625</v>
       </c>
     </row>
     <row r="27">
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.07</v>
+        <v>2.59</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="N27" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="O27" t="n">
         <v>2.25</v>
       </c>
       <c r="P27" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.93</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="n">
-        <v>5.75</v>
+        <v>6.7</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>3.21</v>
+        <v>2.91</v>
       </c>
       <c r="N28" t="n">
-        <v>3.31</v>
+        <v>2.96</v>
       </c>
       <c r="O28" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="P28" t="n">
-        <v>11.75</v>
+        <v>6.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="T28" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.16</v>
+        <v>4.75</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AH28" t="n">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>4.9</v>
       </c>
       <c r="M29" t="n">
-        <v>2.91</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.96</v>
+        <v>1.48</v>
       </c>
       <c r="O29" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.46</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="n">
-        <v>9.199999999999999</v>
+        <v>5.45</v>
       </c>
       <c r="AI29" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>3.03</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4</v>
+        <v>3.39</v>
       </c>
       <c r="N30" t="n">
-        <v>6.2</v>
+        <v>2.02</v>
       </c>
       <c r="O30" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="P30" t="n">
-        <v>16.25</v>
+        <v>13.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="T30" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
         <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="Z30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.18</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.9</v>
+        <v>1.97</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>1.48</v>
+        <v>3.31</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="P31" t="n">
-        <v>14.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="U31" t="n">
         <v>1.42</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
         <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC31" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.7</v>
+        <v>3.16</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.45</v>
+        <v>6.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.59</v>
+        <v>3.07</v>
       </c>
       <c r="M32" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="N32" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="O32" t="n">
         <v>2.25</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.8</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V32" t="n">
-        <v>7</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC32" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG32" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.7</v>
+        <v>5.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4857,12 +4857,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.03</v>
+        <v>2.39</v>
       </c>
       <c r="M34" t="n">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="N34" t="n">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="O34" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="P34" t="n">
-        <v>13.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V34" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.67</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V34" t="n">
-        <v>6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH34" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>45863.65625</v>
+        <v>45863.66666666666</v>
       </c>
     </row>
     <row r="35">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.39</v>
+        <v>3.8</v>
       </c>
       <c r="M35" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>1.84</v>
       </c>
       <c r="O35" t="n">
-        <v>1.97</v>
+        <v>2.71</v>
       </c>
       <c r="P35" t="n">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="R35" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="S35" t="n">
-        <v>2.34</v>
+        <v>2.69</v>
       </c>
       <c r="T35" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="U35" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.35</v>
+        <v>8.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>2.98</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.55</v>
+        <v>3.52</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45863.79166666666</v>
+        <v>45863.83333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD39" t="n">
         <v>2.2</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P39" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>7</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AE39" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG39" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AH39" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>45863.83333333334</v>
+        <v>45863.85416666666</v>
       </c>
     </row>
     <row r="40">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O40" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P40" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC40" t="n">
         <v>2.1</v>
       </c>
-      <c r="R40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AD40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG40" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH40" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="M41" t="n">
-        <v>3.79</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="O41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE41" t="n">
         <v>1.6</v>
       </c>
-      <c r="P41" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V41" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC41" t="n">
+      <c r="AF41" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG41" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD41" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AH41" t="n">
-        <v>4.75</v>
+        <v>3.58</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="AL41" s="3" t="n">
-        <v>45863.85416666666</v>
+        <v>45863.875</v>
       </c>
     </row>
     <row r="42">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,40 +5954,40 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -5996,34 +5996,34 @@
         <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.45</v>
+        <v>3.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.46</v>
+        <v>1.33</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="AL42" s="3" t="n">
-        <v>45863.875</v>
+        <v>45863.88194444445</v>
       </c>
     </row>
     <row r="43">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="M45" t="n">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>3.51</v>
+        <v>2.98</v>
       </c>
       <c r="O45" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R45" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S45" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T45" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U45" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="V45" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH45" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,40 +6482,40 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="M46" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N46" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="O46" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="P46" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S46" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T46" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U46" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V46" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W46" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X46" t="n">
         <v>1.04</v>
@@ -6527,13 +6527,13 @@
         <v>1.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD46" t="n">
         <v>2.55</v>
@@ -6542,13 +6542,13 @@
         <v>1.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AI46" t="n">
         <v>1.2</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="M47" t="n">
-        <v>3.33</v>
+        <v>3.79</v>
       </c>
       <c r="N47" t="n">
-        <v>2.54</v>
+        <v>3.51</v>
       </c>
       <c r="O47" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="P47" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S47" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T47" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="U47" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V47" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF47" t="n">
         <v>1.5</v>
       </c>
-      <c r="V47" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG47" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH47" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,16 +6746,16 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="M48" t="n">
-        <v>3.55</v>
+        <v>2.62</v>
       </c>
       <c r="N48" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="O48" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -6764,22 +6764,22 @@
         <v>2.3</v>
       </c>
       <c r="R48" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="S48" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="T48" t="n">
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="U48" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="V48" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="W48" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
@@ -6788,16 +6788,16 @@
         <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="AC48" t="n">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.62</v>
+        <v>2.63</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AH48" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="AL48" s="3" t="n">
-        <v>45863.95833333334</v>
+        <v>45863.91666666666</v>
       </c>
     </row>
     <row r="49">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="N49" t="n">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="O49" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="P49" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="R49" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T49" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U49" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="V49" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X49" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH49" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="AL49" s="3" t="n">
-        <v>45863.97916666666</v>
+        <v>45863.95833333334</v>
       </c>
     </row>
     <row r="50">
@@ -6984,114 +6984,246 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P50" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL50" s="3" t="n">
+        <v>45863.97916666666</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Nashville SC</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="L51" t="n">
         <v>2.1</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M51" t="n">
         <v>3.56</v>
       </c>
-      <c r="N50" t="n">
+      <c r="N51" t="n">
         <v>2.75</v>
       </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AC51" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL50" s="3" t="n">
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL51" s="3" t="n">
         <v>45863.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1198,80 +1198,80 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="O10" t="n">
         <v>1.67</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>8</v>
+        <v>2.57</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>3.32</v>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>2.33</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.57</v>
+        <v>8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.32</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.33</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="R21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="Z21" t="n">
         <v>1.3</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG21" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="M24" t="n">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O24" t="n">
         <v>1.93</v>
@@ -3599,13 +3599,13 @@
         <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
         <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V24" t="n">
         <v>7.6</v>
@@ -3617,7 +3617,7 @@
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="Z24" t="n">
         <v>1.3</v>
@@ -3626,10 +3626,10 @@
         <v>3.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AD24" t="n">
         <v>3.25</v>
@@ -3638,7 +3638,7 @@
         <v>1.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
         <v>2</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.37</v>
+        <v>3.07</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>3.34</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>2.02</v>
       </c>
       <c r="O26" t="n">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>16.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.28</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AA26" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.59</v>
+        <v>3.03</v>
       </c>
       <c r="M27" t="n">
-        <v>3.08</v>
+        <v>3.39</v>
       </c>
       <c r="N27" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="O27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG27" t="n">
         <v>2.25</v>
       </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V27" t="n">
-        <v>7</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2</v>
-      </c>
       <c r="AH27" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="M28" t="n">
-        <v>2.91</v>
+        <v>3.21</v>
       </c>
       <c r="N28" t="n">
-        <v>2.96</v>
+        <v>3.31</v>
       </c>
       <c r="O28" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="P28" t="n">
-        <v>6.4</v>
+        <v>11.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.3</v>
       </c>
-      <c r="V28" t="n">
-        <v>10</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AH28" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.03</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
-        <v>3.39</v>
+        <v>4.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.02</v>
+        <v>6.2</v>
       </c>
       <c r="O30" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="P30" t="n">
-        <v>13.5</v>
+        <v>16.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.67</v>
+        <v>3.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
         <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.19</v>
+        <v>4.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.97</v>
+        <v>2.59</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.31</v>
+        <v>2.45</v>
       </c>
       <c r="O31" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="P31" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T31" t="n">
-        <v>2.65</v>
+        <v>2.93</v>
       </c>
       <c r="U31" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AI31" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.1</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,40 +4634,40 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.07</v>
+        <v>1.76</v>
       </c>
       <c r="M32" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>2.02</v>
+        <v>3.84</v>
       </c>
       <c r="O32" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="P32" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V32" t="n">
         <v>6.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
         <v>1.05</v>
@@ -4676,34 +4676,34 @@
         <v>9.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC32" t="n">
         <v>1.91</v>
       </c>
       <c r="AD32" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="n">
         <v>5.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>2.91</v>
       </c>
       <c r="N33" t="n">
-        <v>3.84</v>
+        <v>2.96</v>
       </c>
       <c r="O33" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="P33" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="T33" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y33" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH33" t="n">
-        <v>5.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.39</v>
+        <v>3.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>1.84</v>
       </c>
       <c r="O34" t="n">
-        <v>1.97</v>
+        <v>2.71</v>
       </c>
       <c r="P34" t="n">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="R34" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>2.34</v>
+        <v>2.69</v>
       </c>
       <c r="T34" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="U34" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.35</v>
+        <v>8.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>2.98</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.55</v>
+        <v>3.52</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH34" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.8</v>
+        <v>2.39</v>
       </c>
       <c r="M35" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="N35" t="n">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="O35" t="n">
-        <v>2.71</v>
+        <v>1.97</v>
       </c>
       <c r="P35" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="R35" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="S35" t="n">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="T35" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="U35" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="V35" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.04</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,40 +5162,40 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5222,10 +5222,10 @@
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,40 +5294,40 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
@@ -5840,58 +5840,58 @@
         <v>2.75</v>
       </c>
       <c r="R41" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S41" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T41" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="U41" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="V41" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA41" t="n">
         <v>4.5</v>
       </c>
-      <c r="W41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>5</v>
-      </c>
       <c r="AB41" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="AE41" t="n">
         <v>1.6</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="O45" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="P45" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI45" t="n">
         <v>1.27</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V45" t="n">
-        <v>5</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1.2</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,40 +6482,40 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="M46" t="n">
-        <v>3.33</v>
+        <v>3.65</v>
       </c>
       <c r="N46" t="n">
-        <v>2.54</v>
+        <v>2.98</v>
       </c>
       <c r="O46" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="P46" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S46" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T46" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="U46" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V46" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X46" t="n">
         <v>1.04</v>
@@ -6527,13 +6527,13 @@
         <v>1.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD46" t="n">
         <v>2.55</v>
@@ -6542,13 +6542,13 @@
         <v>1.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH46" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI46" t="n">
         <v>1.2</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="M47" t="n">
-        <v>3.79</v>
+        <v>3.33</v>
       </c>
       <c r="N47" t="n">
-        <v>3.51</v>
+        <v>2.54</v>
       </c>
       <c r="O47" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q47" t="n">
         <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S47" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="T47" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V47" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC47" t="n">
         <v>2.2</v>
       </c>
-      <c r="U47" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V47" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AD47" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="M50" t="n">
-        <v>4.2</v>
+        <v>3.56</v>
       </c>
       <c r="N50" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC50" t="n">
         <v>2.1</v>
       </c>
-      <c r="U50" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V50" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AD50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P51" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T51" t="n">
         <v>2.1</v>
       </c>
-      <c r="M51" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -701,22 +701,22 @@
         <v>2.46</v>
       </c>
       <c r="U2" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="V2" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AA2" t="n">
         <v>4.2</v>
@@ -731,13 +731,13 @@
         <v>2.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF2" t="n">
         <v>1.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="n">
         <v>4.95</v>
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="O3" t="n">
         <v>1.83</v>
@@ -854,10 +854,10 @@
         <v>3.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD3" t="n">
         <v>3.1</v>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
         <v>3.73</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.01</v>
+        <v>2.68</v>
       </c>
       <c r="M14" t="n">
-        <v>3.59</v>
+        <v>3.31</v>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>2.25</v>
       </c>
       <c r="O14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1.67</v>
       </c>
-      <c r="P14" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC14" t="n">
         <v>1.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.22</v>
+        <v>2.77</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.96</v>
+        <v>1.6</v>
       </c>
       <c r="P15" t="n">
-        <v>8.300000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>3.18</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="T15" t="n">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V15" t="n">
-        <v>6.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.4</v>
+        <v>4.48</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.86</v>
+        <v>4.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="N16" t="n">
-        <v>4.78</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6</v>
+        <v>2.96</v>
       </c>
       <c r="P16" t="n">
-        <v>6.05</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.18</v>
+        <v>1.55</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="T16" t="n">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.48</v>
+        <v>3.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="M17" t="n">
-        <v>3.21</v>
+        <v>3.42</v>
       </c>
       <c r="N17" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
         <v>1.71</v>
@@ -2675,40 +2675,40 @@
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="T17" t="n">
         <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="Z17" t="n">
         <v>1.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.32</v>
+        <v>2.95</v>
       </c>
       <c r="AE17" t="n">
         <v>1.3</v>
@@ -2717,13 +2717,13 @@
         <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH17" t="n">
         <v>6.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>4.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AC18" t="n">
         <v>2.2</v>
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="N19" t="n">
-        <v>3.53</v>
+        <v>3.67</v>
       </c>
       <c r="O19" t="n">
         <v>1.58</v>
@@ -2936,58 +2936,58 @@
         <v>2.33</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
         <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
         <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3185,10 +3185,10 @@
         <v>8</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
         <v>4</v>
@@ -3206,13 +3206,13 @@
         <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
         <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.08</v>
@@ -3221,37 +3221,37 @@
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.8</v>
+        <v>9.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AA21" t="n">
         <v>3.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
         <v>1.62</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,73 +3446,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.76</v>
+        <v>4.05</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>3.79</v>
+        <v>1.94</v>
       </c>
       <c r="O23" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="R23" t="n">
         <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD23" t="n">
         <v>2.5</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.78</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="AH23" t="n">
-        <v>5.37</v>
+        <v>4.7</v>
       </c>
       <c r="AI23" t="n">
         <v>1.14</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.85</v>
+        <v>4.18</v>
       </c>
       <c r="O24" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="P24" t="n">
-        <v>8.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG24" t="n">
         <v>2.05</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2</v>
-      </c>
       <c r="AH24" t="n">
-        <v>6.75</v>
+        <v>4.95</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.37</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P25" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC25" t="n">
         <v>1.83</v>
       </c>
-      <c r="O25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="AD25" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.17</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.07</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="N26" t="n">
-        <v>2.02</v>
+        <v>8.5</v>
       </c>
       <c r="O26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P26" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.25</v>
       </c>
-      <c r="P26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="AD26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.5</v>
       </c>
-      <c r="V26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AH26" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.03</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.39</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>2.02</v>
+        <v>3.16</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="P27" t="n">
-        <v>13.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>3.26</v>
+        <v>2.84</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>10.5</v>
+        <v>9.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.19</v>
+        <v>3.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.97</v>
+        <v>3.38</v>
       </c>
       <c r="M28" t="n">
-        <v>3.21</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>3.31</v>
+        <v>2.45</v>
       </c>
       <c r="O28" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="P28" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
         <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
         <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD28" t="n">
         <v>3.3</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AE28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AH28" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.48</v>
       </c>
-      <c r="O29" t="n">
+      <c r="V29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AD29" t="n">
         <v>3.1</v>
       </c>
-      <c r="P29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V29" t="n">
-        <v>6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG29" t="n">
         <v>2</v>
       </c>
-      <c r="AD29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH29" t="n">
-        <v>5.45</v>
+        <v>5.88</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>3.07</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4</v>
+        <v>3.34</v>
       </c>
       <c r="N30" t="n">
-        <v>6.2</v>
+        <v>2.02</v>
       </c>
       <c r="O30" t="n">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="P30" t="n">
-        <v>16.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="R30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z30" t="n">
         <v>1.28</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AA30" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="N31" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG31" t="n">
         <v>2.25</v>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V31" t="n">
-        <v>7</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2</v>
-      </c>
       <c r="AH31" t="n">
-        <v>6.7</v>
+        <v>4.75</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="N32" t="n">
-        <v>3.84</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.53</v>
       </c>
-      <c r="P32" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.36</v>
-      </c>
       <c r="S32" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="T32" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="U32" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="V32" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y32" t="n">
         <v>6.5</v>
       </c>
-      <c r="W32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>9.5</v>
-      </c>
       <c r="Z32" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="AG32" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AH32" t="n">
-        <v>5.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.28</v>
+        <v>4.8</v>
       </c>
       <c r="M33" t="n">
-        <v>2.91</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>2.96</v>
+        <v>1.6</v>
       </c>
       <c r="O33" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="S33" t="n">
-        <v>2.46</v>
+        <v>3.04</v>
       </c>
       <c r="T33" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="U33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE33" t="n">
         <v>1.3</v>
       </c>
-      <c r="V33" t="n">
-        <v>10</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH33" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -5054,28 +5054,28 @@
         <v>2.34</v>
       </c>
       <c r="T35" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U35" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
         <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="Z35" t="n">
         <v>1.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="AB35" t="n">
         <v>2.2</v>
@@ -5084,13 +5084,13 @@
         <v>1.57</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="AE35" t="n">
         <v>1.13</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG35" t="n">
         <v>1.67</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,40 +5162,40 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5222,10 +5222,10 @@
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,40 +5294,40 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>5</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="AD39" t="n">
         <v>2.2</v>
@@ -5738,10 +5738,10 @@
         <v>4.33</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AD40" t="n">
         <v>2.62</v>
@@ -5840,16 +5840,16 @@
         <v>2.75</v>
       </c>
       <c r="R41" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S41" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V41" t="n">
         <v>4.75</v>
@@ -5867,31 +5867,31 @@
         <v>1.15</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AD41" t="n">
         <v>2.32</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF41" t="n">
         <v>1.7</v>
       </c>
       <c r="AG41" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5957,10 +5957,10 @@
         <v>2.75</v>
       </c>
       <c r="M42" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5996,16 +5996,16 @@
         <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB42" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="N45" t="n">
-        <v>3.5</v>
+        <v>2.54</v>
       </c>
       <c r="O45" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q45" t="n">
         <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S45" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="T45" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="U45" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="V45" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="W45" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="M47" t="n">
-        <v>3.33</v>
+        <v>3.88</v>
       </c>
       <c r="N47" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="P47" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="S47" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="U47" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="V47" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA47" t="n">
         <v>5.75</v>
       </c>
-      <c r="W47" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH47" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="M48" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="N48" t="n">
         <v>2.85</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7196,10 +7196,10 @@
         <v>2.37</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF51" t="n">
         <v>1.6</v>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1.64</v>
@@ -695,22 +695,22 @@
         <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V2" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>11</v>
@@ -722,28 +722,28 @@
         <v>4.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>2.79</v>
+        <v>4.05</v>
       </c>
       <c r="O3" t="n">
         <v>1.83</v>
@@ -824,22 +824,22 @@
         <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
         <v>1.05</v>
@@ -848,31 +848,31 @@
         <v>10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>1.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AI3" t="n">
         <v>1.11</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,40 +1070,40 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1130,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1198,80 +1198,80 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.73</v>
+        <v>4.45</v>
       </c>
       <c r="O10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.67</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="O14" t="n">
         <v>2.3</v>
@@ -2282,52 +2282,52 @@
         <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V14" t="n">
         <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="n">
         <v>1.24</v>
       </c>
       <c r="AA14" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="n">
         <v>5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6</v>
+        <v>2.96</v>
       </c>
       <c r="P15" t="n">
-        <v>6.05</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.18</v>
+        <v>1.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>9.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.48</v>
+        <v>3.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.1</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.96</v>
+        <v>1.6</v>
       </c>
       <c r="P16" t="n">
-        <v>8.300000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.55</v>
+        <v>3.18</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>6.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.4</v>
+        <v>4.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="M17" t="n">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.4</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.64</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.3</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.26</v>
+        <v>1.36</v>
       </c>
       <c r="O20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>8</v>
+        <v>2.75</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>1.36</v>
+        <v>2.26</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.05</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>1.94</v>
+        <v>4.18</v>
       </c>
       <c r="O23" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="P23" t="n">
-        <v>14.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
         <v>5.75</v>
       </c>
       <c r="W23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.14</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>4.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>4.18</v>
+        <v>1.94</v>
       </c>
       <c r="O24" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
         <v>5.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>2.35</v>
       </c>
       <c r="M26" t="n">
-        <v>4.33</v>
+        <v>3.04</v>
       </c>
       <c r="N26" t="n">
-        <v>8.5</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.29</v>
       </c>
-      <c r="P26" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.55</v>
-      </c>
       <c r="V26" t="n">
-        <v>4.4</v>
+        <v>9.75</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.8</v>
+        <v>6.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="n">
-        <v>4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N27" t="n">
         <v>2.05</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.16</v>
-      </c>
       <c r="O27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1.67</v>
       </c>
-      <c r="P27" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.38</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.84</v>
+        <v>3.26</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.55</v>
+        <v>3.96</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.38</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="N28" t="n">
-        <v>2.45</v>
+        <v>8.5</v>
       </c>
       <c r="O28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P28" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.25</v>
       </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD28" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AF28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.78</v>
       </c>
-      <c r="AG28" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,43 +4238,43 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
         <v>10</v>
@@ -4286,28 +4286,28 @@
         <v>3.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.88</v>
+        <v>5.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.07</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
         <v>3.34</v>
       </c>
       <c r="N30" t="n">
-        <v>2.02</v>
+        <v>3.16</v>
       </c>
       <c r="O30" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="P30" t="n">
-        <v>10.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
         <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD30" t="n">
         <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,28 +4502,28 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="P31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="R31" t="n">
         <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>3.26</v>
+        <v>2.93</v>
       </c>
       <c r="T31" t="n">
         <v>2.5</v>
@@ -4532,10 +4532,10 @@
         <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
         <v>1.02</v>
@@ -4544,34 +4544,34 @@
         <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.75</v>
+        <v>5.88</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.35</v>
+        <v>3.07</v>
       </c>
       <c r="M32" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="O32" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="P32" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="R32" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="T32" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="V32" t="n">
-        <v>9.75</v>
+        <v>6.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>9.199999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.8</v>
+        <v>3.38</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P33" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S33" t="n">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="T33" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U33" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
+        <v>7</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH33" t="n">
         <v>6</v>
       </c>
-      <c r="W33" t="n">
+      <c r="AI33" t="n">
         <v>1.09</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.11</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
         <v>1.97</v>
@@ -5048,58 +5048,58 @@
         <v>2.15</v>
       </c>
       <c r="R35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V35" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z35" t="n">
         <v>1.53</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V35" t="n">
-        <v>9</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AH35" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="O36" t="n">
         <v>2.25</v>
@@ -5180,58 +5180,58 @@
         <v>1.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="S36" t="n">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V36" t="n">
         <v>7</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="M42" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="N42" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>2.08</v>
       </c>
       <c r="AB42" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="M46" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="N46" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="O46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE46" t="n">
         <v>1.72</v>
       </c>
-      <c r="P46" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R46" t="n">
+      <c r="AF46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI46" t="n">
         <v>1.27</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V46" t="n">
-        <v>5</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.2</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="M47" t="n">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="N47" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="O47" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R47" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V47" t="n">
+        <v>5</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z47" t="n">
         <v>1.2</v>
       </c>
-      <c r="S47" t="n">
-        <v>4</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AA47" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="M48" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="N48" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="O48" t="n">
         <v>2.2</v>
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>3.11</v>
       </c>
       <c r="N49" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="O49" t="n">
         <v>1.67</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P50" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T50" t="n">
         <v>2.1</v>
       </c>
-      <c r="M50" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
-        <v>4.2</v>
+        <v>3.56</v>
       </c>
       <c r="N51" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="O51" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -802,80 +802,80 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -934,80 +934,80 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1066,44 +1066,44 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1130,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1990,80 +1990,80 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="M13" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>3.39</v>
+        <v>3.73</v>
       </c>
       <c r="O13" t="n">
         <v>1.67</v>
       </c>
       <c r="P13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.64</v>
+        <v>2.03</v>
       </c>
       <c r="M17" t="n">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.3</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="M18" t="n">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.4</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.88</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.78</v>
+        <v>4.8</v>
       </c>
       <c r="N19" t="n">
-        <v>3.67</v>
+        <v>1.36</v>
       </c>
       <c r="O19" t="n">
-        <v>1.58</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>15</v>
+        <v>9.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.95</v>
+        <v>6.95</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>8</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.36</v>
+        <v>2.26</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N21" t="n">
-        <v>2.26</v>
+        <v>3.67</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>4.05</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>4.18</v>
+        <v>1.94</v>
       </c>
       <c r="O23" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
         <v>5.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.05</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>1.94</v>
+        <v>2.84</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="P24" t="n">
-        <v>14.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>12.3</v>
+        <v>10.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.2</v>
+        <v>3.36</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.7</v>
+        <v>6.75</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.84</v>
+        <v>4.18</v>
       </c>
       <c r="O25" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="P25" t="n">
-        <v>8.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.25</v>
       </c>
       <c r="AF25" t="n">
         <v>1.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH25" t="n">
-        <v>6.75</v>
+        <v>4.95</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.35</v>
+        <v>3.07</v>
       </c>
       <c r="M26" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="O26" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="R26" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>9.75</v>
+        <v>6.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>9.199999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD27" t="n">
         <v>3.3</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>3.3</v>
       </c>
       <c r="M28" t="n">
-        <v>4.33</v>
+        <v>3.44</v>
       </c>
       <c r="N28" t="n">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>16.25</v>
+        <v>13.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>13.8</v>
+        <v>10</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.2</v>
+        <v>3.96</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AC28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG28" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AH28" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>3.16</v>
+        <v>4.1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P30" t="n">
-        <v>11.75</v>
+        <v>13</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
         <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
         <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF30" t="n">
         <v>1.7</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.5</v>
+        <v>5.88</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="N31" t="n">
-        <v>4.1</v>
+        <v>3.16</v>
       </c>
       <c r="O31" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="P31" t="n">
-        <v>13</v>
+        <v>11.75</v>
       </c>
       <c r="Q31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.75</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
         <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X31" t="n">
         <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF31" t="n">
         <v>1.7</v>
       </c>
       <c r="AG31" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.88</v>
+        <v>5.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.07</v>
+        <v>1.45</v>
       </c>
       <c r="M32" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="N32" t="n">
-        <v>2.02</v>
+        <v>8.5</v>
       </c>
       <c r="O32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P32" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC32" t="n">
         <v>2.25</v>
       </c>
-      <c r="P32" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="AD32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.5</v>
       </c>
-      <c r="V32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF32" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.38</v>
+        <v>2.35</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="N33" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="O33" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="S33" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>9.75</v>
       </c>
       <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
         <v>1.08</v>
       </c>
-      <c r="X33" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y33" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH33" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="N34" t="n">
-        <v>1.84</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
-        <v>2.71</v>
+        <v>1.97</v>
       </c>
       <c r="P34" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="R34" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="S34" t="n">
-        <v>2.69</v>
+        <v>2.29</v>
       </c>
       <c r="T34" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="U34" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="V34" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.52</v>
+        <v>4.95</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AH34" t="n">
-        <v>7.1</v>
+        <v>10.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="N35" t="n">
-        <v>3.2</v>
+        <v>1.84</v>
       </c>
       <c r="O35" t="n">
-        <v>1.97</v>
+        <v>2.71</v>
       </c>
       <c r="P35" t="n">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="R35" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="S35" t="n">
-        <v>2.29</v>
+        <v>2.69</v>
       </c>
       <c r="T35" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="U35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V35" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AE35" t="n">
         <v>1.22</v>
       </c>
-      <c r="V35" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF35" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="n">
-        <v>10.5</v>
+        <v>7.1</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N39" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O39" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P39" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V39" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="W39" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AD39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG39" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH39" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="O40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE40" t="n">
         <v>1.6</v>
       </c>
-      <c r="P40" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="M45" t="n">
-        <v>3.33</v>
+        <v>3.88</v>
       </c>
       <c r="N45" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="O45" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="P45" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="S45" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="T45" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="U45" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="V45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA45" t="n">
         <v>5.75</v>
       </c>
-      <c r="W45" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AB45" t="n">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="M46" t="n">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="N46" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="O46" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R46" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V46" t="n">
+        <v>5</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z46" t="n">
         <v>1.2</v>
       </c>
-      <c r="S46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V46" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AA46" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AH46" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,40 +6614,40 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="M47" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N47" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="O47" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S47" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T47" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U47" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V47" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W47" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X47" t="n">
         <v>1.04</v>
@@ -6659,13 +6659,13 @@
         <v>1.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AD47" t="n">
         <v>2.55</v>
@@ -6674,13 +6674,13 @@
         <v>1.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AI47" t="n">
         <v>1.2</v>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>2.83</v>
+        <v>3.73</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
         <v>2.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>4.45</v>
+        <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.73</v>
+        <v>2.14</v>
       </c>
       <c r="O13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1.67</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.3</v>
       </c>
       <c r="R13" t="n">
         <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
         <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
         <v>2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
         <v>2.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.96</v>
+        <v>1.6</v>
       </c>
       <c r="P15" t="n">
-        <v>8.300000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>3.18</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="T15" t="n">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V15" t="n">
-        <v>6.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.4</v>
+        <v>4.48</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>4.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6</v>
+        <v>2.96</v>
       </c>
       <c r="P16" t="n">
-        <v>6.05</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.18</v>
+        <v>1.55</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="T16" t="n">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>9.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.48</v>
+        <v>3.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="M17" t="n">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.4</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.64</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.3</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>8</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.36</v>
+        <v>2.26</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N20" t="n">
-        <v>2.26</v>
+        <v>3.67</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.78</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>3.67</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
-        <v>1.58</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>15</v>
+        <v>9.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.95</v>
+        <v>6.95</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.05</v>
+        <v>2.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.94</v>
+        <v>2.84</v>
       </c>
       <c r="O23" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="P23" t="n">
-        <v>14.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>12.3</v>
+        <v>10.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.2</v>
+        <v>3.36</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.7</v>
+        <v>6.75</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.84</v>
+        <v>4.18</v>
       </c>
       <c r="O24" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="P24" t="n">
-        <v>8.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
         <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="n">
-        <v>6.75</v>
+        <v>4.95</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.75</v>
+        <v>4.05</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>4.18</v>
+        <v>1.94</v>
       </c>
       <c r="O25" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="U25" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
         <v>5.75</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.07</v>
+        <v>2.35</v>
       </c>
       <c r="M26" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="N26" t="n">
-        <v>2.02</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="P26" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="T26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V26" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2.5</v>
       </c>
-      <c r="U26" t="n">
+      <c r="AB26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC26" t="n">
         <v>1.5</v>
       </c>
-      <c r="V26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="n">
-        <v>5.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,43 +4238,43 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>1.53</v>
       </c>
       <c r="P29" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="T29" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
         <v>10</v>
@@ -4286,28 +4286,28 @@
         <v>3.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.5</v>
+        <v>5.88</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1</v>
+        <v>8.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="P30" t="n">
-        <v>13</v>
+        <v>16.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X30" t="n">
         <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>10</v>
+        <v>13.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AG30" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.88</v>
+        <v>4</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.05</v>
+        <v>3.07</v>
       </c>
       <c r="M31" t="n">
         <v>3.34</v>
       </c>
       <c r="N31" t="n">
-        <v>3.16</v>
+        <v>2.02</v>
       </c>
       <c r="O31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q31" t="n">
         <v>1.67</v>
       </c>
-      <c r="P31" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.38</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
         <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD31" t="n">
         <v>3</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.45</v>
+        <v>4.8</v>
       </c>
       <c r="M32" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.29</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>16.25</v>
+        <v>14.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S32" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="T32" t="n">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="U32" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="V32" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>13.8</v>
+        <v>10</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AH32" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="M33" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="N33" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="O33" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="P33" t="n">
-        <v>6.4</v>
+        <v>11.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R33" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="S33" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="T33" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="Z33" t="n">
         <v>1.29</v>
       </c>
-      <c r="V33" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AA33" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AD33" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="M34" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>3.2</v>
+        <v>1.84</v>
       </c>
       <c r="O34" t="n">
-        <v>1.97</v>
+        <v>2.71</v>
       </c>
       <c r="P34" t="n">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="R34" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>2.29</v>
+        <v>2.69</v>
       </c>
       <c r="T34" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="U34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V34" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1.22</v>
       </c>
-      <c r="V34" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF34" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AH34" t="n">
-        <v>10.5</v>
+        <v>7.1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>1.84</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
-        <v>2.71</v>
+        <v>1.97</v>
       </c>
       <c r="P35" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="R35" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="S35" t="n">
-        <v>2.69</v>
+        <v>2.29</v>
       </c>
       <c r="T35" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="U35" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="V35" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y35" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.52</v>
+        <v>4.95</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AH35" t="n">
-        <v>7.1</v>
+        <v>10.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="M45" t="n">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="O45" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V45" t="n">
+        <v>5</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z45" t="n">
         <v>1.2</v>
       </c>
-      <c r="S45" t="n">
-        <v>4</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V45" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AA45" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AH45" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,40 +6482,40 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="M46" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N46" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="O46" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="P46" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S46" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T46" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U46" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V46" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W46" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X46" t="n">
         <v>1.04</v>
@@ -6527,13 +6527,13 @@
         <v>1.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AD46" t="n">
         <v>2.55</v>
@@ -6542,13 +6542,13 @@
         <v>1.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AI46" t="n">
         <v>1.2</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="M47" t="n">
-        <v>3.33</v>
+        <v>3.88</v>
       </c>
       <c r="N47" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="P47" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="S47" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="U47" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="V47" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA47" t="n">
         <v>5.75</v>
       </c>
-      <c r="W47" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AB47" t="n">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH47" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -802,80 +802,80 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -934,80 +934,80 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,40 +1202,40 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1262,10 +1262,10 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="N7" t="n">
-        <v>3.73</v>
+        <v>3.39</v>
       </c>
       <c r="O7" t="n">
         <v>1.67</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1594,80 +1594,80 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.39</v>
+        <v>2.83</v>
       </c>
       <c r="O11" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.35</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2122,80 +2122,80 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.64</v>
+        <v>2.03</v>
       </c>
       <c r="M17" t="n">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.3</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="M18" t="n">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.4</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N19" t="n">
-        <v>2.26</v>
+        <v>3.67</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.88</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.67</v>
+        <v>2.26</v>
       </c>
       <c r="O20" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.2</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG20" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.84</v>
+        <v>4.18</v>
       </c>
       <c r="O23" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="P23" t="n">
-        <v>8.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.25</v>
       </c>
       <c r="AF23" t="n">
         <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>6.75</v>
+        <v>4.95</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>4.18</v>
+        <v>2.84</v>
       </c>
       <c r="O24" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="P24" t="n">
-        <v>9.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>12.9</v>
+        <v>10.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.74</v>
+        <v>3.36</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
         <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.95</v>
+        <v>6.75</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P26" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AD26" t="n">
         <v>3.1</v>
       </c>
-      <c r="O26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V26" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>9.199999999999999</v>
+        <v>5.88</v>
       </c>
       <c r="AI26" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.38</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>2.45</v>
+        <v>3.16</v>
       </c>
       <c r="O27" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="T27" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="M28" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2.3</v>
       </c>
-      <c r="P28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.67</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="S28" t="n">
-        <v>3.26</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V28" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA28" t="n">
         <v>2.5</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.17</v>
       </c>
-      <c r="AA28" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.8</v>
+        <v>3.07</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>2.02</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="P29" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="R29" t="n">
         <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
         <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
         <v>6.5</v>
       </c>
       <c r="W29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.05</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y29" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AB29" t="n">
         <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG29" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.88</v>
+        <v>5.75</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>4.8</v>
       </c>
       <c r="M30" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="O30" t="n">
-        <v>1.29</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>16.25</v>
+        <v>14.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="T30" t="n">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="U30" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="V30" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.8</v>
+        <v>10</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AH30" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.07</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="N31" t="n">
-        <v>2.02</v>
+        <v>8.5</v>
       </c>
       <c r="O31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P31" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.25</v>
       </c>
-      <c r="P31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="AD31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.5</v>
       </c>
-      <c r="V31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF31" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.8</v>
+        <v>3.38</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P32" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S32" t="n">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="T32" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
+        <v>7</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH32" t="n">
         <v>6</v>
       </c>
-      <c r="W32" t="n">
+      <c r="AI32" t="n">
         <v>1.09</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.11</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N33" t="n">
         <v>2.05</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.16</v>
-      </c>
       <c r="O33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1.67</v>
       </c>
-      <c r="P33" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.38</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>2.84</v>
+        <v>3.26</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V33" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X33" t="n">
         <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.55</v>
+        <v>3.96</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="O39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE39" t="n">
         <v>1.6</v>
       </c>
-      <c r="P39" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V39" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF39" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O40" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P40" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R40" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V40" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="W40" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AD40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG40" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH40" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G44" t="n">

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="M2" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="O2" t="n">
         <v>1.64</v>
@@ -695,55 +695,55 @@
         <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>6.55</v>
       </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.5</v>
+        <v>5.45</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -802,80 +802,80 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -934,80 +934,80 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,40 +1202,40 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1262,10 +1262,10 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="M7" t="n">
-        <v>3.59</v>
+        <v>3.47</v>
       </c>
       <c r="N7" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="O7" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="T7" t="n">
-        <v>2.76</v>
+        <v>2.35</v>
       </c>
       <c r="U7" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.7</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.22</v>
+        <v>2.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.1</v>
+        <v>4.55</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1858,80 +1858,80 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2122,44 +2122,44 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2186,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="N14" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="O14" t="n">
         <v>2.3</v>
@@ -2276,58 +2276,58 @@
         <v>1.67</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="U14" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6</v>
+        <v>2.96</v>
       </c>
       <c r="P15" t="n">
-        <v>6.05</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.18</v>
+        <v>1.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>9.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.48</v>
+        <v>3.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.1</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.96</v>
+        <v>1.6</v>
       </c>
       <c r="P16" t="n">
-        <v>8.300000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="Q16" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.55</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="AD16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.08</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>3.42</v>
+        <v>3.21</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="O17" t="n">
         <v>1.71</v>
@@ -2681,46 +2681,46 @@
         <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V17" t="n">
         <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
         <v>8.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA17" t="n">
         <v>3.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF17" t="n">
         <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI17" t="n">
         <v>1.1</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.88</v>
+        <v>2.57</v>
       </c>
       <c r="M19" t="n">
-        <v>3.78</v>
+        <v>3.32</v>
       </c>
       <c r="N19" t="n">
-        <v>3.67</v>
+        <v>2.33</v>
       </c>
       <c r="O19" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.6</v>
       </c>
-      <c r="V19" t="n">
-        <v>5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG19" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>1.79</v>
       </c>
       <c r="M20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.3</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG20" t="n">
         <v>2.5</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="O21" t="n">
         <v>4</v>
@@ -3200,58 +3200,58 @@
         <v>1.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
         <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AG21" t="n">
         <v>1.62</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.95</v>
+        <v>6.9</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="O22" t="n">
         <v>1.62</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="M23" t="n">
         <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>4.18</v>
+        <v>3.79</v>
       </c>
       <c r="O23" t="n">
         <v>1.57</v>
@@ -3470,52 +3470,52 @@
         <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V23" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>12.9</v>
+        <v>10.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.78</v>
+        <v>2.93</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="N24" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>1.93</v>
@@ -3596,58 +3596,58 @@
         <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
         <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>10.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AA24" t="n">
         <v>3.36</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH24" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.05</v>
+        <v>3.37</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="N25" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="O25" t="n">
         <v>2.25</v>
@@ -3728,13 +3728,13 @@
         <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="T25" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
         <v>1.5</v>
@@ -3743,43 +3743,43 @@
         <v>5.75</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AE25" t="n">
         <v>1.45</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="P26" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
         <v>13</v>
       </c>
-      <c r="Q26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>10</v>
-      </c>
       <c r="Z26" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.1</v>
+        <v>2.16</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH26" t="n">
-        <v>5.88</v>
+        <v>4</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.21</v>
       </c>
       <c r="N27" t="n">
-        <v>3.16</v>
+        <v>3.31</v>
       </c>
       <c r="O27" t="n">
         <v>1.67</v>
@@ -3992,34 +3992,34 @@
         <v>2.38</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="W27" t="n">
         <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.25</v>
+        <v>8.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AB27" t="n">
         <v>1.85</v>
@@ -4028,22 +4028,22 @@
         <v>1.85</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH27" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="M28" t="n">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>3.84</v>
       </c>
       <c r="O28" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="P28" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="U28" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="V28" t="n">
-        <v>9.75</v>
+        <v>5.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AH28" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="N29" t="n">
         <v>2.02</v>
       </c>
       <c r="O29" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="P29" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="Q29" t="n">
         <v>1.67</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="T29" t="n">
         <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD29" t="n">
         <v>3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AF29" t="n">
         <v>1.62</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N30" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="O30" t="n">
         <v>3.1</v>
@@ -4388,58 +4388,58 @@
         <v>1.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="T30" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="U30" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF30" t="n">
         <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>2.59</v>
       </c>
       <c r="M31" t="n">
-        <v>4.33</v>
+        <v>3.08</v>
       </c>
       <c r="N31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V31" t="n">
+        <v>7</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y31" t="n">
         <v>8.5</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Z31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.29</v>
       </c>
-      <c r="P31" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF31" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AH31" t="n">
-        <v>4</v>
+        <v>6.65</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.38</v>
+        <v>2.28</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>2.91</v>
       </c>
       <c r="N32" t="n">
-        <v>2.45</v>
+        <v>2.96</v>
       </c>
       <c r="O32" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="S32" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH32" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,19 +4766,19 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="M33" t="n">
-        <v>3.44</v>
+        <v>3.34</v>
       </c>
       <c r="N33" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O33" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="P33" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q33" t="n">
         <v>1.67</v>
@@ -4787,55 +4787,55 @@
         <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
         <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W33" t="n">
         <v>1.11</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="N35" t="n">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="O35" t="n">
         <v>1.97</v>
@@ -5048,58 +5048,58 @@
         <v>2.15</v>
       </c>
       <c r="R35" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S35" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="T35" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U35" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="W35" t="n">
         <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AH35" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="O37" t="n">
         <v>2.25</v>
@@ -5312,28 +5312,28 @@
         <v>1.8</v>
       </c>
       <c r="R37" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S37" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U37" t="n">
         <v>1.37</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z37" t="n">
         <v>1.3</v>
@@ -5342,16 +5342,16 @@
         <v>3.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF37" t="n">
         <v>1.73</v>
@@ -5360,10 +5360,10 @@
         <v>2</v>
       </c>
       <c r="AH37" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N39" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O39" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P39" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V39" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="W39" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AD39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG39" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH39" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="O40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE40" t="n">
         <v>1.6</v>
       </c>
-      <c r="P40" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U41" t="n">
         <v>1.55</v>
@@ -5867,28 +5867,28 @@
         <v>1.15</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AE41" t="n">
         <v>1.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="AI41" t="n">
         <v>1.2</v>
@@ -5954,46 +5954,46 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="N42" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Z42" t="n">
         <v>1.7</v>
@@ -6002,28 +6002,28 @@
         <v>2.08</v>
       </c>
       <c r="AB42" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="O47" t="n">
         <v>1.8</v>
@@ -6632,22 +6632,22 @@
         <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="U47" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="V47" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="W47" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -6659,28 +6659,28 @@
         <v>1.11</v>
       </c>
       <c r="AA47" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG47" t="n">
         <v>2.7</v>
       </c>
       <c r="AH47" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AI47" t="n">
         <v>1.27</v>
@@ -6746,19 +6746,19 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="M48" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="N48" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="O48" t="n">
         <v>2.2</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q48" t="n">
         <v>2.3</v>
@@ -6770,22 +6770,22 @@
         <v>2</v>
       </c>
       <c r="T48" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="U48" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V48" t="n">
+        <v>11</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X48" t="n">
         <v>1.17</v>
       </c>
-      <c r="V48" t="n">
-        <v>17</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Z48" t="n">
         <v>1.75</v>
@@ -6794,28 +6794,28 @@
         <v>1.95</v>
       </c>
       <c r="AB48" t="n">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="M49" t="n">
-        <v>3.11</v>
+        <v>3.55</v>
       </c>
       <c r="N49" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="O49" t="n">
         <v>1.67</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC49" t="n">
         <v>2</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.8</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="M50" t="n">
-        <v>4.2</v>
+        <v>3.56</v>
       </c>
       <c r="N50" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P51" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T51" t="n">
         <v>2.1</v>
       </c>
-      <c r="M51" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -802,80 +802,80 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -934,80 +934,80 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>2.68</v>
       </c>
       <c r="M10" t="n">
-        <v>2.96</v>
+        <v>3.31</v>
       </c>
       <c r="N10" t="n">
-        <v>3.23</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="U10" t="n">
         <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="W10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1858,80 +1858,80 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="M13" t="n">
-        <v>3.09</v>
+        <v>3.47</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="O13" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.68</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.31</v>
+        <v>3.09</v>
       </c>
       <c r="N14" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="O14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2.3</v>
       </c>
-      <c r="P14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.67</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="M17" t="n">
-        <v>3.21</v>
+        <v>3.68</v>
       </c>
       <c r="N17" t="n">
-        <v>3.31</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.4</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
-        <v>3.68</v>
+        <v>3.21</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>3.31</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V18" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.57</v>
+        <v>1.79</v>
       </c>
       <c r="M19" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2.33</v>
       </c>
-      <c r="O19" t="n">
-        <v>2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.83</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG19" t="n">
         <v>2.5</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>2.57</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="N20" t="n">
-        <v>3.53</v>
+        <v>2.33</v>
       </c>
       <c r="O20" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.6</v>
       </c>
-      <c r="V20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AC20" t="n">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG20" t="n">
         <v>2.25</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AH20" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.76</v>
+        <v>2.31</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.03</v>
       </c>
       <c r="N23" t="n">
-        <v>3.79</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="P23" t="n">
-        <v>9.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH23" t="n">
         <v>6</v>
       </c>
-      <c r="W23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AI23" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.31</v>
+        <v>3.37</v>
       </c>
       <c r="M24" t="n">
-        <v>3.03</v>
+        <v>3.64</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="O24" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
-        <v>8.75</v>
+        <v>14.5</v>
       </c>
       <c r="Q24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2.05</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD24" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.37</v>
+        <v>1.76</v>
       </c>
       <c r="M25" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>1.83</v>
+        <v>3.79</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="P25" t="n">
-        <v>14.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="V25" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.37</v>
+        <v>3.07</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>3.34</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>2.02</v>
       </c>
       <c r="O26" t="n">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>16.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.28</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="AA26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AI26" t="n">
         <v>1.13</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.2</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="M27" t="n">
-        <v>3.21</v>
+        <v>2.91</v>
       </c>
       <c r="N27" t="n">
-        <v>3.31</v>
+        <v>2.96</v>
       </c>
       <c r="O27" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="P27" t="n">
-        <v>11.75</v>
+        <v>6.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V27" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.09</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y27" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N28" t="n">
-        <v>3.84</v>
+        <v>3.31</v>
       </c>
       <c r="O28" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="P28" t="n">
-        <v>13</v>
+        <v>11.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="U28" t="n">
         <v>1.42</v>
       </c>
       <c r="V28" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W28" t="n">
         <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z28" t="n">
         <v>1.22</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH28" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,73 +4238,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.03</v>
+        <v>1.76</v>
       </c>
       <c r="M29" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>2.02</v>
+        <v>3.84</v>
       </c>
       <c r="O29" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="P29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="W29" t="n">
         <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z29" t="n">
         <v>1.22</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AC29" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI29" t="n">
         <v>1.11</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.9</v>
+        <v>2.59</v>
       </c>
       <c r="M30" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="N30" t="n">
-        <v>1.48</v>
+        <v>2.45</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P30" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.4</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.39</v>
-      </c>
       <c r="S30" t="n">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF30" t="n">
         <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH30" t="n">
-        <v>6</v>
+        <v>6.65</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.59</v>
+        <v>3.03</v>
       </c>
       <c r="M31" t="n">
-        <v>3.08</v>
+        <v>3.39</v>
       </c>
       <c r="N31" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="O31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG31" t="n">
         <v>2.25</v>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V31" t="n">
-        <v>7</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AH31" t="n">
-        <v>6.65</v>
+        <v>4.75</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.28</v>
+        <v>4.9</v>
       </c>
       <c r="M32" t="n">
-        <v>2.91</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.96</v>
+        <v>1.48</v>
       </c>
       <c r="O32" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>2.4</v>
+        <v>2.93</v>
       </c>
       <c r="T32" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="U32" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V32" t="n">
-        <v>9.800000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="W32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X32" t="n">
         <v>1</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Y32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH32" t="n">
         <v>6</v>
       </c>
-      <c r="Z32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AI32" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.07</v>
+        <v>1.37</v>
       </c>
       <c r="M33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P33" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S33" t="n">
         <v>3.34</v>
       </c>
-      <c r="N33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V33" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AH33" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,73 +4898,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.8</v>
+        <v>2.39</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="N34" t="n">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="O34" t="n">
-        <v>2.71</v>
+        <v>1.97</v>
       </c>
       <c r="P34" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="R34" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="S34" t="n">
-        <v>2.69</v>
+        <v>2.36</v>
       </c>
       <c r="T34" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="U34" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="V34" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.98</v>
+        <v>2.45</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.52</v>
+        <v>4.7</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AH34" t="n">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI34" t="n">
         <v>1.04</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,73 +5030,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.39</v>
+        <v>3.8</v>
       </c>
       <c r="M35" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>1.84</v>
       </c>
       <c r="O35" t="n">
-        <v>1.97</v>
+        <v>2.71</v>
       </c>
       <c r="P35" t="n">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="R35" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="S35" t="n">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="T35" t="n">
-        <v>3.6</v>
+        <v>2.99</v>
       </c>
       <c r="U35" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="V35" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.2</v>
+        <v>8.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.45</v>
+        <v>2.98</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.7</v>
+        <v>3.52</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="n">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="AI35" t="n">
         <v>1.04</v>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="O39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE39" t="n">
         <v>1.6</v>
       </c>
-      <c r="P39" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V39" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF39" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O40" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P40" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R40" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V40" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="W40" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AD40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG40" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH40" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,40 +6350,40 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N45" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="O45" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="P45" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S45" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T45" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U45" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V45" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W45" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X45" t="n">
         <v>1.04</v>
@@ -6395,13 +6395,13 @@
         <v>1.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AD45" t="n">
         <v>2.55</v>
@@ -6410,13 +6410,13 @@
         <v>1.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AI45" t="n">
         <v>1.2</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,40 +6482,40 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="M46" t="n">
-        <v>3.33</v>
+        <v>3.65</v>
       </c>
       <c r="N46" t="n">
-        <v>2.54</v>
+        <v>2.98</v>
       </c>
       <c r="O46" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="P46" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S46" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T46" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="U46" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V46" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X46" t="n">
         <v>1.04</v>
@@ -6527,13 +6527,13 @@
         <v>1.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD46" t="n">
         <v>2.55</v>
@@ -6542,13 +6542,13 @@
         <v>1.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH46" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI46" t="n">
         <v>1.2</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P50" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T50" t="n">
         <v>2.1</v>
       </c>
-      <c r="M50" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
-        <v>4.2</v>
+        <v>3.56</v>
       </c>
       <c r="N51" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="O51" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -802,80 +802,80 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -934,80 +934,80 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>2.96</v>
+        <v>3.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.23</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
         <v>2.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3.39</v>
+        <v>4.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="M13" t="n">
-        <v>3.47</v>
+        <v>3.59</v>
       </c>
       <c r="N13" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.3</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.55</v>
+        <v>6.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.9</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.33</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
         <v>2.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.96</v>
+        <v>1.6</v>
       </c>
       <c r="P15" t="n">
-        <v>8.300000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.55</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="AD15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AI15" t="n">
         <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.08</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>4.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6</v>
+        <v>2.96</v>
       </c>
       <c r="P16" t="n">
-        <v>6.05</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.18</v>
+        <v>1.55</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="T16" t="n">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>9.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.57</v>
+        <v>8.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.32</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.33</v>
+        <v>1.28</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="R20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.3</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>2.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>8.5</v>
+        <v>2.57</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>3.32</v>
       </c>
       <c r="N21" t="n">
-        <v>1.28</v>
+        <v>2.33</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.31</v>
+        <v>3.37</v>
       </c>
       <c r="M23" t="n">
-        <v>3.03</v>
+        <v>3.64</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="O23" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>8.75</v>
+        <v>14.5</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.05</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD23" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.37</v>
+        <v>1.76</v>
       </c>
       <c r="M24" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>1.83</v>
+        <v>3.79</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="P24" t="n">
-        <v>14.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.76</v>
+        <v>2.31</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.03</v>
       </c>
       <c r="N25" t="n">
-        <v>3.79</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="P25" t="n">
-        <v>9.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="U25" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH25" t="n">
         <v>6</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AI25" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.07</v>
+        <v>2.59</v>
       </c>
       <c r="M26" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="N26" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="O26" t="n">
         <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z26" t="n">
         <v>1.28</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AH26" t="n">
-        <v>5.75</v>
+        <v>6.65</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.28</v>
+        <v>3.03</v>
       </c>
       <c r="M27" t="n">
-        <v>2.91</v>
+        <v>3.39</v>
       </c>
       <c r="N27" t="n">
-        <v>2.96</v>
+        <v>2.02</v>
       </c>
       <c r="O27" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="R27" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="T27" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="V27" t="n">
-        <v>9.800000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>9.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.97</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>3.21</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.31</v>
+        <v>6.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="P28" t="n">
-        <v>11.75</v>
+        <v>16.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="T28" t="n">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="V28" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.08</v>
+        <v>2.16</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.09</v>
+        <v>1.78</v>
       </c>
       <c r="AH28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N29" t="n">
-        <v>3.84</v>
+        <v>3.31</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="P29" t="n">
-        <v>13</v>
+        <v>11.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="U29" t="n">
         <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W29" t="n">
         <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z29" t="n">
         <v>1.22</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.59</v>
+        <v>2.28</v>
       </c>
       <c r="M30" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="N30" t="n">
-        <v>2.45</v>
+        <v>2.96</v>
       </c>
       <c r="O30" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="S30" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AH30" t="n">
-        <v>6.65</v>
+        <v>9.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,73 +4502,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.03</v>
+        <v>1.76</v>
       </c>
       <c r="M31" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>2.02</v>
+        <v>3.84</v>
       </c>
       <c r="O31" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="P31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V31" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.09</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
         <v>1.22</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AC31" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI31" t="n">
         <v>1.11</v>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.37</v>
+        <v>3.07</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>3.34</v>
       </c>
       <c r="N33" t="n">
-        <v>6.2</v>
+        <v>2.02</v>
       </c>
       <c r="O33" t="n">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="P33" t="n">
-        <v>16.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z33" t="n">
         <v>1.28</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W33" t="n">
+      <c r="AA33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AI33" t="n">
         <v>1.13</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.2</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,73 +4898,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.39</v>
+        <v>3.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>1.84</v>
       </c>
       <c r="O34" t="n">
-        <v>1.97</v>
+        <v>2.71</v>
       </c>
       <c r="P34" t="n">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="R34" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="T34" t="n">
-        <v>3.6</v>
+        <v>2.99</v>
       </c>
       <c r="U34" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="V34" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.2</v>
+        <v>8.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.45</v>
+        <v>2.98</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.7</v>
+        <v>3.52</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH34" t="n">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="AI34" t="n">
         <v>1.04</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,73 +5030,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.8</v>
+        <v>2.39</v>
       </c>
       <c r="M35" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="N35" t="n">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="O35" t="n">
-        <v>2.71</v>
+        <v>1.97</v>
       </c>
       <c r="P35" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="R35" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="S35" t="n">
-        <v>2.69</v>
+        <v>2.36</v>
       </c>
       <c r="T35" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="U35" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="V35" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.98</v>
+        <v>2.45</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.52</v>
+        <v>4.7</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AH35" t="n">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI35" t="n">
         <v>1.04</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G44" t="n">

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -657,30 +657,30 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="M2" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
         <v>1.64</v>
@@ -695,64 +695,64 @@
         <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="U2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>6.55</v>
+        <v>5.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC2" t="n">
         <v>2.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52', '65', '90+1']</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '80']</t>
         </is>
       </c>
       <c r="AL2" s="3" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -802,80 +802,80 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -934,80 +934,80 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1066,44 +1066,44 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1130,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="M8" t="n">
-        <v>3.09</v>
+        <v>3.59</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.39</v>
       </c>
       <c r="O8" t="n">
         <v>1.67</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="T8" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>2.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>3.31</v>
       </c>
       <c r="N11" t="n">
-        <v>4.45</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.68</v>
       </c>
-      <c r="AC11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG11" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="M13" t="n">
-        <v>3.59</v>
+        <v>3.47</v>
       </c>
       <c r="N13" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="O13" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.22</v>
+        <v>2.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6</v>
+        <v>2.96</v>
       </c>
       <c r="P15" t="n">
-        <v>6.05</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.18</v>
+        <v>1.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>9.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.1</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.96</v>
+        <v>1.6</v>
       </c>
       <c r="P16" t="n">
-        <v>8.300000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="Q16" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V16" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.55</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="AD16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.08</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>3.68</v>
+        <v>3.21</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>3.31</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.8</v>
       </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.3</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="M18" t="n">
-        <v>3.21</v>
+        <v>3.68</v>
       </c>
       <c r="N18" t="n">
-        <v>3.31</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.4</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2936,34 +2936,34 @@
         <v>2.33</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
         <v>5.2</v>
       </c>
       <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z19" t="n">
         <v>1.15</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AA19" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AB19" t="n">
         <v>1.46</v>
@@ -2978,7 +2978,7 @@
         <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG19" t="n">
         <v>2.5</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>8.5</v>
+        <v>2.57</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>3.32</v>
       </c>
       <c r="N20" t="n">
-        <v>1.28</v>
+        <v>2.33</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.57</v>
+        <v>8.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.32</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.33</v>
+        <v>1.28</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="R21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="Z21" t="n">
         <v>1.3</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG21" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3326,40 +3326,40 @@
         <v>1.62</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
         <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB22" t="n">
         <v>1.79</v>
@@ -3368,22 +3368,22 @@
         <v>1.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF22" t="n">
         <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.37</v>
+        <v>2.31</v>
       </c>
       <c r="M23" t="n">
-        <v>3.64</v>
+        <v>3.03</v>
       </c>
       <c r="N23" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="P23" t="n">
-        <v>14.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.73</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X23" t="n">
+      <c r="AG23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.13</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3611,19 +3611,19 @@
         <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
         <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AB24" t="n">
         <v>1.7</v>
@@ -3632,16 +3632,16 @@
         <v>1.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="AE24" t="n">
         <v>1.38</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AH24" t="n">
         <v>5.5</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.31</v>
+        <v>3.37</v>
       </c>
       <c r="M25" t="n">
-        <v>3.03</v>
+        <v>3.64</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="O25" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>8.75</v>
+        <v>14.5</v>
       </c>
       <c r="Q25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC25" t="n">
         <v>2.05</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD25" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3869,10 +3869,10 @@
         <v>2.88</v>
       </c>
       <c r="U26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.07</v>
@@ -3881,13 +3881,13 @@
         <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
         <v>1.96</v>
@@ -3896,22 +3896,22 @@
         <v>1.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AF26" t="n">
         <v>1.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="n">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.03</v>
+        <v>1.97</v>
       </c>
       <c r="M27" t="n">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="N27" t="n">
-        <v>2.02</v>
+        <v>3.31</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="P27" t="n">
-        <v>13.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U27" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="V27" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.09</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.11</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4127,19 +4127,19 @@
         <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="U28" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
@@ -4148,10 +4148,10 @@
         <v>13</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AB28" t="n">
         <v>1.57</v>
@@ -4166,16 +4166,16 @@
         <v>1.57</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AG28" t="n">
         <v>1.78</v>
       </c>
       <c r="AH28" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>2.91</v>
       </c>
       <c r="N29" t="n">
-        <v>3.31</v>
+        <v>2.96</v>
       </c>
       <c r="O29" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="P29" t="n">
-        <v>11.75</v>
+        <v>6.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.08</v>
+        <v>5.19</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.09</v>
+        <v>1.74</v>
       </c>
       <c r="AH29" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.28</v>
+        <v>3.03</v>
       </c>
       <c r="M30" t="n">
-        <v>2.91</v>
+        <v>3.39</v>
       </c>
       <c r="N30" t="n">
-        <v>2.96</v>
+        <v>2.02</v>
       </c>
       <c r="O30" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="P30" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="R30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF30" t="n">
         <v>1.55</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD30" t="n">
+      <c r="AG30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH30" t="n">
         <v>5</v>
       </c>
-      <c r="AE30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AI30" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4526,22 +4526,22 @@
         <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U31" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="V31" t="n">
         <v>5.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="Z31" t="n">
         <v>1.22</v>
@@ -4556,19 +4556,19 @@
         <v>1.91</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AI31" t="n">
         <v>1.11</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,73 +4634,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="N32" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P32" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="R32" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="T32" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V32" t="n">
         <v>6.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AI32" t="n">
         <v>1.13</v>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.07</v>
+        <v>4.9</v>
       </c>
       <c r="M33" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="O33" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V33" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.67</v>
       </c>
-      <c r="R33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH33" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.8</v>
+        <v>2.39</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="N34" t="n">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="O34" t="n">
-        <v>2.71</v>
+        <v>1.97</v>
       </c>
       <c r="P34" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="R34" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="S34" t="n">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="U34" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="V34" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="W34" t="n">
         <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.5</v>
+        <v>6.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.52</v>
+        <v>4.65</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH34" t="n">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,73 +5030,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.39</v>
+        <v>3.8</v>
       </c>
       <c r="M35" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>1.84</v>
       </c>
       <c r="O35" t="n">
-        <v>1.97</v>
+        <v>2.71</v>
       </c>
       <c r="P35" t="n">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="R35" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="S35" t="n">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="T35" t="n">
-        <v>3.6</v>
+        <v>2.99</v>
       </c>
       <c r="U35" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="V35" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.2</v>
+        <v>8.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.45</v>
+        <v>2.98</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.7</v>
+        <v>3.52</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="n">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="AI35" t="n">
         <v>1.04</v>
@@ -5312,13 +5312,13 @@
         <v>1.8</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T37" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
         <v>1.37</v>
@@ -5336,10 +5336,10 @@
         <v>8.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB37" t="n">
         <v>1.95</v>
@@ -5348,22 +5348,22 @@
         <v>1.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF37" t="n">
         <v>1.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH37" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N39" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O39" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P39" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V39" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="W39" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AD39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG39" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH39" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="O40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE40" t="n">
         <v>1.6</v>
       </c>
-      <c r="P40" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5975,19 +5975,19 @@
         <v>1.74</v>
       </c>
       <c r="S42" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="T42" t="n">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="U42" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="V42" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X42" t="n">
         <v>1.15</v>
@@ -6008,7 +6008,7 @@
         <v>1.32</v>
       </c>
       <c r="AD42" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AE42" t="n">
         <v>1.09</v>
@@ -6017,13 +6017,13 @@
         <v>2.4</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="M48" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="N48" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="O48" t="n">
         <v>2.2</v>
@@ -6764,10 +6764,10 @@
         <v>2.3</v>
       </c>
       <c r="R48" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="T48" t="n">
         <v>4.33</v>
@@ -6776,22 +6776,22 @@
         <v>1.18</v>
       </c>
       <c r="V48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W48" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X48" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Y48" t="n">
         <v>4.75</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB48" t="n">
         <v>3.27</v>
@@ -6803,16 +6803,16 @@
         <v>6.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH48" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AI48" t="n">
         <v>1.02</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="M50" t="n">
-        <v>4.2</v>
+        <v>3.56</v>
       </c>
       <c r="N50" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P51" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T51" t="n">
         <v>2.1</v>
       </c>
-      <c r="M51" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1066,44 +1066,44 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1130,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1176,29 +1176,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '90+4']</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,29 +1430,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1462,89 +1462,89 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.01</v>
+        <v>3.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>3.39</v>
+        <v>1.96</v>
       </c>
       <c r="O8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.67</v>
       </c>
-      <c r="P8" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="T8" t="n">
-        <v>2.76</v>
+        <v>2.57</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.05</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y8" t="n">
-        <v>11.7</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.56</v>
+        <v>3.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.22</v>
+        <v>2.98</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62', '68']</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '71']</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,106 +1572,106 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '78']</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,19 +1704,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54', '63', '90']</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,111 +1836,111 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.68</v>
+        <v>1.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.31</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="P11" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="U11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.42</v>
       </c>
-      <c r="V11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI11" t="n">
         <v>1.13</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3', '90+10']</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '68']</t>
         </is>
       </c>
       <c r="AL11" s="3" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,111 +1968,111 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '18', '37', '52']</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AL12" s="3" t="n">
@@ -2090,121 +2090,121 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>3.47</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>3.61</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.3</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG13" t="n">
         <v>2.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '77', '51', '90+3']</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '17', '69', '81', '88']</t>
         </is>
       </c>
       <c r="AL13" s="3" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,111 +2364,111 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.96</v>
+        <v>1.6</v>
       </c>
       <c r="P15" t="n">
-        <v>8.300000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>3.18</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="S15" t="n">
-        <v>2.73</v>
+        <v>2.23</v>
       </c>
       <c r="T15" t="n">
-        <v>2.89</v>
+        <v>4.05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>6.9</v>
+        <v>10.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.5</v>
+        <v>6.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.92</v>
+        <v>2.49</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AL15" s="3" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>4.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6</v>
+        <v>2.96</v>
       </c>
       <c r="P16" t="n">
-        <v>6.05</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.18</v>
+        <v>1.55</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="T16" t="n">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2657,10 +2657,10 @@
         <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>3.21</v>
+        <v>3.58</v>
       </c>
       <c r="N17" t="n">
-        <v>3.31</v>
+        <v>3.89</v>
       </c>
       <c r="O17" t="n">
         <v>1.71</v>
@@ -2672,58 +2672,58 @@
         <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
         <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.79</v>
+        <v>8.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.53</v>
+        <v>1.31</v>
       </c>
       <c r="O19" t="n">
-        <v>1.58</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.28</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.95</v>
+        <v>6.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="M20" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>8.5</v>
+        <v>1.81</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>3.96</v>
       </c>
       <c r="N21" t="n">
-        <v>1.28</v>
+        <v>3.73</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>1.58</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.17</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.28</v>
+        <v>5.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.28</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.57</v>
+        <v>2.54</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
         <v>1.62</v>
@@ -3335,19 +3335,19 @@
         <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>6.2</v>
+        <v>6.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
         <v>1.05</v>
@@ -3356,34 +3356,34 @@
         <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG22" t="n">
         <v>2.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="M23" t="n">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="P23" t="n">
-        <v>8.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="V23" t="n">
-        <v>7.6</v>
+        <v>5.65</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>10</v>
+        <v>12.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AH23" t="n">
-        <v>6.55</v>
+        <v>5.66</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.76</v>
+        <v>2.59</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.79</v>
+        <v>2.55</v>
       </c>
       <c r="O24" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="P24" t="n">
-        <v>9.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA24" t="n">
         <v>3</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.9</v>
       </c>
-      <c r="AD24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AH24" t="n">
-        <v>5.5</v>
+        <v>7.9</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="O25" t="n">
         <v>2.25</v>
@@ -3728,7 +3728,7 @@
         <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
         <v>3.2</v>
@@ -3737,49 +3737,49 @@
         <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V25" t="n">
         <v>5.75</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
         <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AB25" t="n">
         <v>1.65</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AE25" t="n">
         <v>1.45</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AH25" t="n">
         <v>4.9</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.59</v>
+        <v>4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.45</v>
+        <v>1.96</v>
       </c>
       <c r="O26" t="n">
         <v>2.25</v>
@@ -3860,10 +3860,10 @@
         <v>1.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="T26" t="n">
         <v>2.88</v>
@@ -3872,46 +3872,46 @@
         <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="W26" t="n">
         <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>3.41</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH26" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,22 +3974,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.97</v>
+        <v>4.07</v>
       </c>
       <c r="M27" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>3.31</v>
+        <v>1.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>11.75</v>
+        <v>14.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
@@ -3998,52 +3998,52 @@
         <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U27" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.25</v>
+        <v>9.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AH27" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="P28" t="n">
-        <v>16.25</v>
+        <v>6.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T28" t="n">
         <v>3.3</v>
       </c>
-      <c r="T28" t="n">
-        <v>2.46</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="V28" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI28" t="n">
         <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.19</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>1.34</v>
       </c>
       <c r="M29" t="n">
-        <v>2.91</v>
+        <v>4.75</v>
       </c>
       <c r="N29" t="n">
-        <v>2.96</v>
+        <v>7.8</v>
       </c>
       <c r="O29" t="n">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="P29" t="n">
-        <v>6.4</v>
+        <v>16.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.5</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF29" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="AG29" t="n">
         <v>1.74</v>
       </c>
       <c r="AH29" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>2.3</v>
@@ -4388,58 +4388,58 @@
         <v>1.67</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z30" t="n">
         <v>1.22</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AB30" t="n">
         <v>1.67</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AF30" t="n">
         <v>1.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,73 +4502,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.76</v>
+        <v>2.31</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N31" t="n">
-        <v>3.84</v>
+        <v>2.9</v>
       </c>
       <c r="O31" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="P31" t="n">
-        <v>13</v>
+        <v>11.75</v>
       </c>
       <c r="Q31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.75</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.45</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.5</v>
+        <v>8.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AI31" t="n">
         <v>1.11</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="M32" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.02</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="P32" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
         <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AD32" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH32" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.9</v>
+        <v>3.07</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="N33" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P33" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE33" t="n">
         <v>1.38</v>
       </c>
-      <c r="V33" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AF33" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.39</v>
+        <v>3.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>1.84</v>
       </c>
       <c r="O34" t="n">
-        <v>1.97</v>
+        <v>2.71</v>
       </c>
       <c r="P34" t="n">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="R34" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="T34" t="n">
-        <v>3.6</v>
+        <v>2.99</v>
       </c>
       <c r="U34" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="V34" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="W34" t="n">
         <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.25</v>
+        <v>8.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>2.98</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.65</v>
+        <v>3.52</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH34" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="M35" t="n">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="N35" t="n">
-        <v>1.84</v>
+        <v>3.3</v>
       </c>
       <c r="O35" t="n">
-        <v>2.71</v>
+        <v>1.97</v>
       </c>
       <c r="P35" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="R35" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="S35" t="n">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="T35" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="V35" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="W35" t="n">
         <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y35" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="AB35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF35" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.9</v>
       </c>
       <c r="AG35" t="n">
         <v>1.8</v>
       </c>
       <c r="AH35" t="n">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M37" t="n">
         <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="O37" t="n">
         <v>2.25</v>
@@ -5312,58 +5312,58 @@
         <v>1.8</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
         <v>2.9</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U37" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="W37" t="n">
         <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>8.5</v>
+        <v>9.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AB37" t="n">
         <v>1.95</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="n">
         <v>6.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="O39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE39" t="n">
         <v>1.6</v>
       </c>
-      <c r="P39" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V39" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF39" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O40" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P40" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R40" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V40" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="W40" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AD40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG40" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH40" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5840,58 +5840,58 @@
         <v>2.75</v>
       </c>
       <c r="R41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V41" t="n">
+        <v>4</v>
+      </c>
+      <c r="W41" t="n">
         <v>1.22</v>
       </c>
-      <c r="S41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V41" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.15</v>
-      </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AB41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF41" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AG41" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="M42" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="N42" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
         <v>2.25</v>
@@ -5972,58 +5972,58 @@
         <v>2.2</v>
       </c>
       <c r="R42" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="S42" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="T42" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="U42" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="V42" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="W42" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y42" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AB42" t="n">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG42" t="n">
         <v>1.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI42" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,40 +6350,40 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="M45" t="n">
-        <v>3.33</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>2.54</v>
+        <v>2.98</v>
       </c>
       <c r="O45" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="P45" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R45" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S45" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T45" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="U45" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V45" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X45" t="n">
         <v>1.04</v>
@@ -6395,13 +6395,13 @@
         <v>1.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD45" t="n">
         <v>2.55</v>
@@ -6410,13 +6410,13 @@
         <v>1.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI45" t="n">
         <v>1.2</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,40 +6482,40 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="M46" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N46" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="O46" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="P46" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S46" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T46" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U46" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V46" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W46" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X46" t="n">
         <v>1.04</v>
@@ -6527,13 +6527,13 @@
         <v>1.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AD46" t="n">
         <v>2.55</v>
@@ -6542,13 +6542,13 @@
         <v>1.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AI46" t="n">
         <v>1.2</v>
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="N47" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="O47" t="n">
         <v>1.8</v>
@@ -6635,19 +6635,19 @@
         <v>1.22</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T47" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="U47" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="V47" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="W47" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -6656,34 +6656,34 @@
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AA47" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="M48" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="N48" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="O48" t="n">
         <v>2.2</v>
@@ -6764,58 +6764,58 @@
         <v>2.3</v>
       </c>
       <c r="R48" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="S48" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="T48" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V48" t="n">
+        <v>10</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Y48" t="n">
         <v>4.33</v>
       </c>
-      <c r="U48" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V48" t="n">
-        <v>9</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>4.75</v>
-      </c>
       <c r="Z48" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB48" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD48" t="n">
         <v>6.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF48" t="n">
         <v>2.38</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AH48" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="O49" t="n">
         <v>1.67</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -802,80 +802,80 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -934,80 +934,80 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,19 +1044,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54', '63', '90']</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1430,29 +1430,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1462,89 +1462,89 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>['62', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>['50', '71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -1704,25 +1704,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>['54', '63', '90']</t>
+          <t>['13', '18', '37', '52']</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -1958,35 +1958,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1994,85 +1994,85 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>['13', '18', '37', '52']</t>
+          <t>['62', '68']</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['50', '71']</t>
         </is>
       </c>
       <c r="AL12" s="3" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,111 +2364,111 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.8</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P15" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AH15" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL15" s="3" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,111 +2496,111 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.96</v>
+        <v>1.6</v>
       </c>
       <c r="P16" t="n">
-        <v>8.300000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.55</v>
+        <v>3.18</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="S16" t="n">
-        <v>2.73</v>
+        <v>2.23</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>4.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="V16" t="n">
-        <v>6.9</v>
+        <v>10.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.5</v>
+        <v>6.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.92</v>
+        <v>2.49</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AH16" t="n">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AL16" s="3" t="n">
@@ -2618,121 +2618,121 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="M17" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="N17" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.4</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.62</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
         <v>1.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '45+4', '88']</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '74']</t>
         </is>
       </c>
       <c r="AL17" s="3" t="n">
@@ -2750,121 +2750,121 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>3.89</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
         <v>1.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53', '51']</t>
         </is>
       </c>
       <c r="AL18" s="3" t="n">
@@ -2904,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AL19" s="3" t="n">
@@ -3024,111 +3024,111 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.56</v>
+        <v>1.81</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="N20" t="n">
-        <v>2.04</v>
+        <v>3.73</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
         <v>3.4</v>
       </c>
       <c r="T20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.5</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AL20" s="3" t="n">
@@ -3156,16 +3156,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -3178,84 +3178,84 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.81</v>
+        <v>2.56</v>
       </c>
       <c r="M21" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3.73</v>
+        <v>2.04</v>
       </c>
       <c r="O21" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
         <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.65</v>
       </c>
-      <c r="V21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC21" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="O23" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="R23" t="n">
         <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>12.9</v>
+        <v>9</v>
       </c>
       <c r="Z23" t="n">
         <v>1.22</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="AH23" t="n">
-        <v>5.66</v>
+        <v>4.9</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,111 +3552,111 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.59</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P24" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S24" t="n">
         <v>3.25</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="P24" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>5.65</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>8</v>
+        <v>12.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AA24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD24" t="n">
         <v>3</v>
       </c>
-      <c r="AB24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AH24" t="n">
-        <v>7.9</v>
+        <v>5.66</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '55']</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81', '90+1', '87']</t>
         </is>
       </c>
       <c r="AL24" s="3" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="P25" t="n">
-        <v>14.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>5.75</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.9</v>
+        <v>7.9</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,31 +3842,31 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="O26" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
         <v>1.36</v>
@@ -3878,16 +3878,16 @@
         <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="AB26" t="n">
         <v>1.95</v>
@@ -3899,19 +3899,19 @@
         <v>3.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AH26" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,31 +3974,31 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1.8</v>
       </c>
-      <c r="O27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.4</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="T27" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U27" t="n">
         <v>1.36</v>
@@ -4010,16 +4010,16 @@
         <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="AB27" t="n">
         <v>1.95</v>
@@ -4031,19 +4031,19 @@
         <v>3.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH27" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG28" t="n">
         <v>2.25</v>
       </c>
-      <c r="M28" t="n">
-        <v>3</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V28" t="n">
-        <v>10</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH28" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,19 +4370,19 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="O30" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="P30" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q30" t="n">
         <v>1.67</v>
@@ -4391,55 +4391,55 @@
         <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
         <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AA30" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.7</v>
+        <v>5.75</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P31" t="n">
-        <v>11.75</v>
+        <v>13</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.4</v>
       </c>
-      <c r="V31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF31" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AH31" t="n">
-        <v>6.4</v>
+        <v>4.75</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="O32" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="P32" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="T32" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="U32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>10</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z32" t="n">
         <v>1.43</v>
       </c>
-      <c r="V32" t="n">
-        <v>6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AA32" t="n">
-        <v>3.95</v>
+        <v>2.55</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.74</v>
+        <v>4.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.19</v>
+        <v>1.75</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.75</v>
+        <v>10</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.07</v>
+        <v>2.31</v>
       </c>
       <c r="M33" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="N33" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="P33" t="n">
-        <v>10.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA33" t="n">
         <v>3.25</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W33" t="n">
+      <c r="AB33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AI33" t="n">
         <v>1.11</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.13</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="N34" t="n">
-        <v>1.84</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
-        <v>2.71</v>
+        <v>1.97</v>
       </c>
       <c r="P34" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="R34" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="S34" t="n">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="T34" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="V34" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="W34" t="n">
         <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="AB34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF34" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.9</v>
       </c>
       <c r="AG34" t="n">
         <v>1.8</v>
       </c>
       <c r="AH34" t="n">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="M35" t="n">
-        <v>3.03</v>
+        <v>3.19</v>
       </c>
       <c r="N35" t="n">
-        <v>3.3</v>
+        <v>1.84</v>
       </c>
       <c r="O35" t="n">
-        <v>1.97</v>
+        <v>2.71</v>
       </c>
       <c r="P35" t="n">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="R35" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="S35" t="n">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="T35" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="U35" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="V35" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="W35" t="n">
         <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.5</v>
+        <v>3.52</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG35" t="n">
         <v>1.8</v>
       </c>
       <c r="AH35" t="n">
-        <v>10</v>
+        <v>7.1</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="M45" t="n">
         <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="O45" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="P45" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T45" t="n">
         <v>2.2</v>
       </c>
-      <c r="R45" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U45" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V45" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="W45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.2</v>
       </c>
       <c r="AA45" t="n">
         <v>4.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="M47" t="n">
         <v>3.65</v>
       </c>
       <c r="N47" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="O47" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S47" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T47" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U47" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V47" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AA47" t="n">
         <v>4.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL51"/>
+  <dimension ref="A1:AL50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,35 +1034,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1070,85 +1070,85 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>['54', '63', '90']</t>
+          <t>['45+3', '90+10']</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['6', '68']</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,25 +1176,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
+          <t>['21', '78']</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>['6', '90+4']</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,111 +1308,111 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '77', '51', '90+3']</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '17', '69', '81', '88']</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,29 +1440,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '18', '37', '52']</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,22 +1572,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1598,85 +1598,85 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>['21', '78']</t>
+          <t>['54', '63', '90']</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,111 +1704,111 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>['13', '18', '37', '52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1862,85 +1862,85 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>['45+3', '90+10']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>['6', '68']</t>
+          <t>['6', '90+4']</t>
         </is>
       </c>
       <c r="AL11" s="3" t="n">
@@ -1958,29 +1958,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1990,89 +1990,89 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>['62', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>['50', '71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL12" s="3" t="n">
@@ -2090,35 +2090,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2126,85 +2126,85 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>1.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="T13" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>['38', '77', '51', '90+3']</t>
+          <t>['62', '68']</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>['41', '17', '69', '81', '88']</t>
+          <t>['50', '71']</t>
         </is>
       </c>
       <c r="AL13" s="3" t="n">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.01</v>
+        <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.59</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>1.77</v>
       </c>
       <c r="O14" t="n">
-        <v>1.67</v>
+        <v>2.96</v>
       </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="U14" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.7</v>
+        <v>8.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.56</v>
+        <v>3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45863.54166666666</v>
+        <v>45863.57291666666</v>
       </c>
     </row>
     <row r="15">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,111 +2364,111 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.96</v>
+        <v>1.6</v>
       </c>
       <c r="P15" t="n">
-        <v>8.300000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>3.18</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="S15" t="n">
-        <v>2.73</v>
+        <v>2.23</v>
       </c>
       <c r="T15" t="n">
-        <v>2.89</v>
+        <v>4.05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>6.9</v>
+        <v>10.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.5</v>
+        <v>6.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.92</v>
+        <v>2.49</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AL15" s="3" t="n">
@@ -2481,37 +2481,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2522,89 +2522,89 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="M16" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
         <v>3.2</v>
       </c>
-      <c r="N16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.23</v>
-      </c>
       <c r="T16" t="n">
-        <v>4.05</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.18</v>
       </c>
-      <c r="V16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['14', '45+4', '88']</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['39', '74']</t>
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45863.57291666666</v>
+        <v>45863.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2618,35 +2618,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2654,85 +2654,85 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>3.89</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
         <v>1.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>['14', '45+4', '88']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>['39', '74']</t>
+          <t>['53', '51']</t>
         </is>
       </c>
       <c r="AL17" s="3" t="n">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,19 +2760,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -2786,89 +2786,89 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="M18" t="n">
-        <v>3.58</v>
+        <v>3.96</v>
       </c>
       <c r="N18" t="n">
-        <v>3.89</v>
+        <v>3.73</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="P18" t="n">
-        <v>8.75</v>
+        <v>18.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.7</v>
+        <v>5.35</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="AH18" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>['53', '51']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>45863.58333333334</v>
+        <v>45863.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,19 +2892,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2918,85 +2918,85 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>8.5</v>
+        <v>2.56</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.31</v>
+        <v>2.04</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
           <t>[]</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
         </is>
       </c>
       <c r="AL19" s="3" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,22 +3024,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -3050,85 +3050,85 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.81</v>
+        <v>8.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="N20" t="n">
-        <v>3.73</v>
+        <v>1.31</v>
       </c>
       <c r="O20" t="n">
-        <v>1.58</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="V20" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.35</v>
+        <v>3.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>3.28</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.54</v>
-      </c>
       <c r="AH20" t="n">
-        <v>3.5</v>
+        <v>6.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AL20" s="3" t="n">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,22 +3156,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3182,89 +3182,89 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.56</v>
+        <v>1.91</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
         <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>6.35</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF21" t="n">
         <v>1.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['3', '45+1', '63']</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>45863.60416666666</v>
+        <v>45863.625</v>
       </c>
     </row>
     <row r="22">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,115 +3288,115 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="P22" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q22" t="n">
         <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="V22" t="n">
-        <v>6.35</v>
+        <v>5.65</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>11</v>
+        <v>12.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.6</v>
+        <v>5.66</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '55']</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81', '90+1', '87']</t>
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45863.625</v>
+        <v>45863.64583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,111 +3420,111 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="O23" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="P23" t="n">
-        <v>14.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>5.75</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.9</v>
+        <v>7.9</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AL23" s="3" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,25 +3552,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3578,85 +3578,85 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="O24" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="R24" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="V24" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>12.9</v>
+        <v>9</v>
       </c>
       <c r="Z24" t="n">
         <v>1.22</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>5.66</v>
+        <v>4.9</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>['27', '55']</t>
+          <t>['28', '58']</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>['81', '90+1', '87']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AL24" s="3" t="n">
@@ -3669,130 +3669,130 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.59</v>
+        <v>1.34</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="N25" t="n">
-        <v>2.55</v>
+        <v>7.8</v>
       </c>
       <c r="O25" t="n">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="P25" t="n">
-        <v>8.75</v>
+        <v>16.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="V25" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
       <c r="W25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.01</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y25" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>1.52</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.7</v>
+        <v>2.67</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AH25" t="n">
-        <v>7.9</v>
+        <v>4.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '30', '62']</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '86']</t>
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45863.64583333334</v>
+        <v>45863.65625</v>
       </c>
     </row>
     <row r="26">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,111 +3816,111 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.07</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="P26" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.07</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y26" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AH26" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+5']</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AL26" s="3" t="n">
@@ -3960,17 +3960,17 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '45+3', '54']</t>
         </is>
       </c>
       <c r="AL27" s="3" t="n">
@@ -4080,111 +4080,111 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O28" t="n">
         <v>3.1</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.3</v>
-      </c>
       <c r="P28" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="W28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AI28" t="n">
         <v>1.1</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '66']</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '39']</t>
         </is>
       </c>
       <c r="AL28" s="3" t="n">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.34</v>
+        <v>3.07</v>
       </c>
       <c r="M29" t="n">
-        <v>4.75</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
-        <v>7.8</v>
+        <v>2.02</v>
       </c>
       <c r="O29" t="n">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="P29" t="n">
-        <v>16.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="R29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z29" t="n">
         <v>1.28</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T29" t="n">
+      <c r="AA29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG29" t="n">
         <v>2.2</v>
       </c>
-      <c r="U29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="AH29" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.13</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.14</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,121 +4334,121 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.07</v>
+        <v>2.31</v>
       </c>
       <c r="M30" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="N30" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="O30" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="P30" t="n">
-        <v>10.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA30" t="n">
         <v>3.25</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W30" t="n">
+      <c r="AB30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.11</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '56']</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60', '79', '89']</t>
         </is>
       </c>
       <c r="AL30" s="3" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,111 +4476,111 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="P31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="U31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.43</v>
       </c>
-      <c r="V31" t="n">
-        <v>6</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AF31" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '28']</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62', '63']</t>
         </is>
       </c>
       <c r="AL31" s="3" t="n">
@@ -4608,111 +4608,111 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="M32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P32" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.32</v>
-      </c>
       <c r="T32" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z32" t="n">
         <v>1.25</v>
       </c>
-      <c r="V32" t="n">
-        <v>10</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AA32" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.5</v>
+        <v>2.74</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.75</v>
+        <v>2.19</v>
       </c>
       <c r="AH32" t="n">
-        <v>10</v>
+        <v>4.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59', '74']</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31', '47', '72', '77']</t>
         </is>
       </c>
       <c r="AL32" s="3" t="n">
@@ -4725,27 +4725,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.31</v>
+        <v>3.8</v>
       </c>
       <c r="M33" t="n">
-        <v>3.37</v>
+        <v>3.19</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>1.84</v>
       </c>
       <c r="O33" t="n">
-        <v>1.67</v>
+        <v>2.71</v>
       </c>
       <c r="P33" t="n">
-        <v>11.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S33" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V33" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH33" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45863.65625</v>
+        <v>45863.66666666666</v>
       </c>
     </row>
     <row r="34">
@@ -4881,20 +4881,20 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '87']</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '50', '72']</t>
         </is>
       </c>
       <c r="AL34" s="3" t="n">
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="M35" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="O35" t="n">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="P35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="R35" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="T35" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="U35" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V35" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
         <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>8.5</v>
+        <v>9.15</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="AB35" t="n">
         <v>1.95</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH35" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45863.66666666666</v>
+        <v>45863.79166666666</v>
       </c>
     </row>
     <row r="36">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45863.79166666666</v>
+        <v>45863.83333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P38" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD38" t="n">
         <v>2.2</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P38" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V38" t="n">
-        <v>7</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AE38" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG38" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AH38" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45863.83333333334</v>
+        <v>45863.85416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N39" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O39" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P39" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V39" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="W39" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AD39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG39" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH39" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5649,12 +5649,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.9</v>
       </c>
       <c r="N40" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="O40" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="P40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R40" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S40" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="V40" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="W40" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.62</v>
+        <v>1.89</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.75</v>
+        <v>2.92</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="AL40" s="3" t="n">
-        <v>45863.85416666666</v>
+        <v>45863.875</v>
       </c>
     </row>
     <row r="41">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.62</v>
+        <v>2.76</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>2.68</v>
       </c>
       <c r="N41" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="O41" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="U41" t="n">
-        <v>1.73</v>
+        <v>1.14</v>
       </c>
       <c r="V41" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="Y41" t="n">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.09</v>
+        <v>1.77</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.4</v>
+        <v>2.01</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.35</v>
+        <v>3.3</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.89</v>
+        <v>7</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.85</v>
+        <v>1.06</v>
       </c>
       <c r="AF41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.5</v>
       </c>
-      <c r="AG41" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AH41" t="n">
-        <v>2.92</v>
+        <v>13</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="AL41" s="3" t="n">
-        <v>45863.875</v>
+        <v>45863.88194444445</v>
       </c>
     </row>
     <row r="42">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="AL42" s="3" t="n">
-        <v>45863.88194444445</v>
+        <v>45863.88541666666</v>
       </c>
     </row>
     <row r="43">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="AL44" s="3" t="n">
-        <v>45863.88541666666</v>
+        <v>45863.89583333334</v>
       </c>
     </row>
     <row r="45">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,76 +6350,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N45" t="n">
-        <v>3.25</v>
+        <v>2.54</v>
       </c>
       <c r="O45" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q45" t="n">
         <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S45" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="T45" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="U45" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="V45" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA45" t="n">
         <v>4.33</v>
       </c>
-      <c r="W45" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="AB45" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH45" t="n">
         <v>4.5</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AI45" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,76 +6482,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="M46" t="n">
-        <v>3.33</v>
+        <v>3.65</v>
       </c>
       <c r="N46" t="n">
-        <v>2.54</v>
+        <v>3.25</v>
       </c>
       <c r="O46" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="P46" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S46" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T46" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="U46" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V46" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="W46" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X46" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.08</v>
+        <v>2.43</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6573,12 +6573,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V47" t="n">
+        <v>10</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA47" t="n">
         <v>1.96</v>
       </c>
-      <c r="M47" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="P47" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V47" t="n">
-        <v>5</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.55</v>
+        <v>6.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.51</v>
+        <v>2.38</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.35</v>
+        <v>1.46</v>
       </c>
       <c r="AH47" t="n">
-        <v>4.33</v>
+        <v>15.5</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="AL47" s="3" t="n">
-        <v>45863.89583333334</v>
+        <v>45863.91666666666</v>
       </c>
     </row>
     <row r="48">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="M48" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="O48" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="P48" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>2.3</v>
       </c>
       <c r="R48" t="n">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="S48" t="n">
-        <v>1.98</v>
+        <v>3.4</v>
       </c>
       <c r="T48" t="n">
-        <v>4.6</v>
+        <v>2.38</v>
       </c>
       <c r="U48" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V48" t="n">
+        <v>5</v>
+      </c>
+      <c r="W48" t="n">
         <v>1.14</v>
       </c>
-      <c r="V48" t="n">
-        <v>10</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X48" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC48" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA48" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AD48" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="AH48" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="AL48" s="3" t="n">
-        <v>45863.91666666666</v>
+        <v>45863.95833333334</v>
       </c>
     </row>
     <row r="49">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,76 +6878,76 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P49" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG49" t="n">
         <v>2.15</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V49" t="n">
-        <v>5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="AL49" s="3" t="n">
-        <v>45863.95833333334</v>
+        <v>45863.97916666666</v>
       </c>
     </row>
     <row r="50">
@@ -7092,138 +7092,6 @@
         </is>
       </c>
       <c r="AL50" s="3" t="n">
-        <v>45863.97916666666</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M51" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N51" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P51" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V51" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL51" s="3" t="n">
         <v>45863.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -1034,121 +1034,121 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>['45+3', '90+10']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>['6', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,111 +1176,111 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>['21', '78']</t>
+          <t>['13', '18', '37', '52']</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,25 +1440,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1466,85 +1466,85 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>['13', '18', '37', '52']</t>
+          <t>['21', '78']</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -1562,35 +1562,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1598,85 +1598,85 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>['54', '63', '90']</t>
+          <t>['45+3', '90+10']</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['6', '68']</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
@@ -1694,29 +1694,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1726,89 +1726,89 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.01</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>3.39</v>
+        <v>1.96</v>
       </c>
       <c r="O10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.67</v>
       </c>
-      <c r="P10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="T10" t="n">
-        <v>2.76</v>
+        <v>2.57</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.05</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y10" t="n">
-        <v>11.7</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.56</v>
+        <v>3.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.22</v>
+        <v>2.98</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62', '68']</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '71']</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -1836,25 +1836,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54', '63', '90']</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>['6', '90+4']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AL11" s="3" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,26 +2090,26 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2126,85 +2126,85 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>['62', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>['50', '71']</t>
+          <t>['6', '90+4']</t>
         </is>
       </c>
       <c r="AL13" s="3" t="n">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,85 +3842,85 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O26" t="n">
         <v>2.25</v>
       </c>
-      <c r="M26" t="n">
+      <c r="P26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD26" t="n">
         <v>3</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V26" t="n">
-        <v>10</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>5.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>['45+5']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AL26" s="3" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,111 +3948,111 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S27" t="n">
         <v>3</v>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.96</v>
-      </c>
       <c r="T27" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V27" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.41</v>
+        <v>3.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59', '74']</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>['25', '45+3', '54']</t>
+          <t>['31', '47', '72', '77']</t>
         </is>
       </c>
       <c r="AL27" s="3" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4095,96 +4095,96 @@
         <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="M28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.8</v>
-      </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD28" t="n">
         <v>2.7</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V28" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>['38', '66']</t>
+          <t>['26', '28']</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>['20', '39']</t>
+          <t>['62', '63']</t>
         </is>
       </c>
       <c r="AL28" s="3" t="n">
@@ -4202,121 +4202,121 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.07</v>
+        <v>4.07</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="O29" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
         <v>9.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.75</v>
+        <v>6.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '66']</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '39']</t>
         </is>
       </c>
       <c r="AL29" s="3" t="n">
@@ -4344,19 +4344,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -4370,85 +4370,85 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3.37</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O30" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="P30" t="n">
-        <v>11.75</v>
+        <v>6.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.75</v>
+        <v>6.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH30" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>['7', '56']</t>
+          <t>['45+5']</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>['60', '79', '89']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AL30" s="3" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,22 +4476,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4502,85 +4502,85 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="O31" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="P31" t="n">
-        <v>13.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="W31" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AA31" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AC31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG31" t="n">
         <v>2.05</v>
       </c>
-      <c r="AD31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH31" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>['26', '28']</t>
+          <t>['7', '56']</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>['62', '63']</t>
+          <t>['60', '79', '89']</t>
         </is>
       </c>
       <c r="AL31" s="3" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,111 +4608,111 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="H32" t="n">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
         <v>4</v>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>1.8</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N32" t="n">
-        <v>4</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P32" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.75</v>
-      </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T32" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="W32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X32" t="n">
         <v>1.06</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y32" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.95</v>
+        <v>3.41</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>['59', '74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>['31', '47', '72', '77']</t>
+          <t>['25', '45+3', '54']</t>
         </is>
       </c>
       <c r="AL32" s="3" t="n">
@@ -4730,121 +4730,121 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="M33" t="n">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="N33" t="n">
-        <v>1.84</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
-        <v>2.71</v>
+        <v>1.97</v>
       </c>
       <c r="P33" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="R33" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="S33" t="n">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="T33" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="V33" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="W33" t="n">
         <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y33" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="AB33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF33" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.9</v>
       </c>
       <c r="AG33" t="n">
         <v>1.8</v>
       </c>
       <c r="AH33" t="n">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '87']</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '50', '72']</t>
         </is>
       </c>
       <c r="AL33" s="3" t="n">
@@ -4862,121 +4862,121 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.03</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>1.84</v>
       </c>
       <c r="O34" t="n">
-        <v>1.97</v>
+        <v>2.71</v>
       </c>
       <c r="P34" t="n">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="R34" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="T34" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="U34" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="V34" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="W34" t="n">
         <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.5</v>
+        <v>3.52</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG34" t="n">
         <v>1.8</v>
       </c>
       <c r="AH34" t="n">
-        <v>10</v>
+        <v>7.1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>['16', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>['27', '50', '72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL34" s="3" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,111 +5136,111 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '88']</t>
         </is>
       </c>
       <c r="AL36" s="3" t="n">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="N38" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="O38" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="P38" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R38" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S38" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T38" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U38" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V38" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="W38" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AD38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG38" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH38" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="O39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE39" t="n">
         <v>1.6</v>
       </c>
-      <c r="P39" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V39" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF39" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH39" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5673,20 +5673,20 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -5708,22 +5708,22 @@
         <v>2.75</v>
       </c>
       <c r="R40" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="U40" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="V40" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="W40" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X40" t="n">
         <v>1</v>
@@ -5732,38 +5732,38 @@
         <v>12</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '31', '62', '77']</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M46" t="n">
         <v>3.65</v>
       </c>
       <c r="N46" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O46" t="n">
         <v>1.8</v>
@@ -6500,58 +6500,58 @@
         <v>2</v>
       </c>
       <c r="R46" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W46" t="n">
         <v>1.22</v>
       </c>
-      <c r="S46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V46" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.15</v>
-      </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z46" t="n">
         <v>1.14</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.22</v>
+        <v>2.51</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH46" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="N48" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="O48" t="n">
         <v>1.67</v>
@@ -6764,58 +6764,58 @@
         <v>2.3</v>
       </c>
       <c r="R48" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S48" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T48" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="V48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W48" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB48" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG48" t="n">
         <v>2</v>
       </c>
-      <c r="AC48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>

--- a/jogos_2025-07-25.xlsx
+++ b/jogos_2025-07-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL50"/>
+  <dimension ref="A1:AK51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,85 +543,80 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -683,13 +678,13 @@
         <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="P2" t="n">
-        <v>20</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.19</v>
+        <v>3.95</v>
       </c>
       <c r="R2" t="n">
         <v>1.3</v>
@@ -704,58 +699,55 @@
         <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>5.3</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>1.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.9</v>
+        <v>2.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['52', '65', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['2', '80']</t>
+        </is>
       </c>
       <c r="AG2" t="n">
-        <v>2.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>5.55</v>
+        <v>1.9</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>['52', '65', '90+1']</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>['2', '80']</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>45863.27083333334</v>
       </c>
     </row>
@@ -862,11 +854,15 @@
       <c r="AD3" t="n">
         <v>0</v>
       </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -877,17 +873,10 @@
       <c r="AI3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>45863.45833333334</v>
       </c>
     </row>
@@ -947,13 +936,13 @@
         <v>2.79</v>
       </c>
       <c r="O4" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
@@ -968,58 +957,55 @@
         <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>8.300000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>3.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.2</v>
+        <v>1.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.31</v>
+        <v>1.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AI4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>45863.45833333334</v>
       </c>
     </row>
@@ -1053,20 +1039,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1126,11 +1112,15 @@
       <c r="AD5" t="n">
         <v>0</v>
       </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['30', '64', '83']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1141,17 +1131,10 @@
       <c r="AI5" t="n">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="3" t="n">
         <v>45863.54166666666</v>
       </c>
     </row>
@@ -1176,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1258,11 +1241,15 @@
       <c r="AD6" t="n">
         <v>0</v>
       </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['6', '90+4']</t>
+        </is>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1273,17 +1260,10 @@
       <c r="AI6" t="n">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>['13', '18', '37', '52']</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>['39']</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3" t="n">
         <v>45863.54166666666</v>
       </c>
     </row>
@@ -1298,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,114 +1288,111 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['13', '18', '37', '52']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>['38', '77', '51', '90+3']</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>['41', '17', '69', '81', '88']</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="3" t="n">
         <v>45863.54166666666</v>
       </c>
     </row>
@@ -1430,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1455,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1466,88 +1443,85 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>3.59</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>3.39</v>
       </c>
       <c r="O8" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['90+1', '90+7']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI8" t="n">
         <v>1.67</v>
       </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>['21', '78']</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
+      <c r="AJ8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK8" s="3" t="n">
         <v>45863.54166666666</v>
       </c>
     </row>
@@ -1562,35 +1536,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1598,88 +1572,85 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.53</v>
+        <v>2.55</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
         <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
         <v>1.48</v>
       </c>
       <c r="V9" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>1.76</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.22</v>
+        <v>2.07</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['21', '78']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG9" t="n">
-        <v>2.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.2</v>
+        <v>1.77</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>['45+3', '90+10']</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>['6', '68']</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK9" s="3" t="n">
         <v>45863.54166666666</v>
       </c>
     </row>
@@ -1694,29 +1665,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1730,88 +1701,85 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['54', '63', '90']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
       </c>
       <c r="AG10" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>['62', '68']</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>['50', '71']</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="3" t="n">
         <v>45863.54166666666</v>
       </c>
     </row>
@@ -1826,29 +1794,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1862,88 +1830,85 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.32</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['62', '68']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['50', '71']</t>
+        </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>['54', '63', '90']</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK11" s="3" t="n">
         <v>45863.54166666666</v>
       </c>
     </row>
@@ -1958,124 +1923,121 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="M12" t="n">
-        <v>3.59</v>
+        <v>3.65</v>
       </c>
       <c r="N12" t="n">
-        <v>3.39</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>2.21</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>4.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.7</v>
+        <v>1.49</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.56</v>
+        <v>2.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.73</v>
+        <v>2.08</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['45+3', '90+10']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['6', '68']</t>
+        </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.99</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK12" s="3" t="n">
         <v>45863.54166666666</v>
       </c>
     </row>
@@ -2090,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,114 +2062,111 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['38', '77', '51', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['41', '17', '69', '81', '88']</t>
+        </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>['6', '90+4']</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK13" s="3" t="n">
         <v>45863.54166666666</v>
       </c>
     </row>
@@ -2244,17 +2203,17 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2267,13 +2226,13 @@
         <v>1.77</v>
       </c>
       <c r="O14" t="n">
-        <v>2.96</v>
+        <v>5.36</v>
       </c>
       <c r="P14" t="n">
-        <v>8.300000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.55</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
@@ -2288,58 +2247,55 @@
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.9</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.5</v>
+        <v>1.95</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['2', '17', '35']</t>
+        </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.5</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK14" s="3" t="n">
         <v>45863.57291666666</v>
       </c>
     </row>
@@ -2399,13 +2355,13 @@
         <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6</v>
+        <v>2.53</v>
       </c>
       <c r="P15" t="n">
-        <v>6.05</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.18</v>
+        <v>6.3</v>
       </c>
       <c r="R15" t="n">
         <v>1.61</v>
@@ -2420,58 +2376,55 @@
         <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>10.5</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>2.28</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.05</v>
+        <v>2.75</v>
       </c>
       <c r="Z15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI15" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>['62']</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="AL15" s="3" t="n">
+      <c r="AJ15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>45863.57291666666</v>
       </c>
     </row>
@@ -2531,13 +2484,13 @@
         <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
         <v>1.3</v>
@@ -2552,58 +2505,55 @@
         <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>1.59</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.22</v>
+        <v>2.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['14', '45+4', '88']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['39', '74']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH16" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AI16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>['14', '45+4', '88']</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>['39', '74']</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK16" s="3" t="n">
         <v>45863.58333333334</v>
       </c>
     </row>
@@ -2663,13 +2613,13 @@
         <v>3.89</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>8.75</v>
+        <v>2.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
         <v>1.36</v>
@@ -2684,58 +2634,55 @@
         <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>3.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.69</v>
+        <v>2.24</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['53', '51']</t>
+        </is>
       </c>
       <c r="AG17" t="n">
-        <v>2.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.5</v>
+        <v>1.77</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>['4']</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>['53', '51']</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK17" s="3" t="n">
         <v>45863.58333333334</v>
       </c>
     </row>
@@ -2750,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2786,88 +2733,85 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.81</v>
+        <v>8.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.73</v>
+        <v>1.31</v>
       </c>
       <c r="O18" t="n">
-        <v>1.58</v>
+        <v>6.3</v>
       </c>
       <c r="P18" t="n">
-        <v>18.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.33</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="V18" t="n">
-        <v>4.4</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>1.91</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.09</v>
+        <v>1.83</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.35</v>
+        <v>3.28</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE18" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF18" t="n">
-        <v>1.43</v>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
       </c>
       <c r="AG18" t="n">
-        <v>2.54</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.5</v>
+        <v>1.06</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>['7']</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="AL18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK18" s="3" t="n">
         <v>45863.60416666666</v>
       </c>
     </row>
@@ -2892,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2918,88 +2862,85 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.56</v>
+        <v>1.81</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="N19" t="n">
-        <v>2.04</v>
+        <v>3.73</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.83</v>
+        <v>3.85</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
         <v>3.4</v>
       </c>
       <c r="T19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.5</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>2.54</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
       </c>
       <c r="AG19" t="n">
-        <v>2.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>['61']</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AK19" s="3" t="n">
         <v>45863.60416666666</v>
       </c>
     </row>
@@ -3014,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -3050,88 +2991,85 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>8.5</v>
+        <v>2.56</v>
       </c>
       <c r="M20" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>1.31</v>
+        <v>2.04</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.33</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.5</v>
+        <v>1.65</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD20" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AL20" s="3" t="n">
+      <c r="AK20" s="3" t="n">
         <v>45863.60416666666</v>
       </c>
     </row>
@@ -3191,13 +3129,13 @@
         <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.62</v>
+        <v>2.43</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
         <v>1.33</v>
@@ -3212,58 +3150,55 @@
         <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>6.35</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>3.78</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>1.75</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.78</v>
+        <v>2.78</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.34</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['3', '45+1', '63']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
       </c>
       <c r="AG21" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>['3', '45+1', '63']</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AL21" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK21" s="3" t="n">
         <v>45863.625</v>
       </c>
     </row>
@@ -3278,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,19 +3223,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -3314,88 +3249,85 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="P22" t="n">
         <v>2.05</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P22" t="n">
-        <v>9.5</v>
-      </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.51</v>
       </c>
-      <c r="V22" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>5.66</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>['27', '55']</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>['81', '90+1', '87']</t>
-        </is>
-      </c>
-      <c r="AL22" s="3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK22" s="3" t="n">
         <v>45863.64583333334</v>
       </c>
     </row>
@@ -3410,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,16 +3352,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -3438,7 +3370,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3446,88 +3378,85 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>2.55</v>
+        <v>1.94</v>
       </c>
       <c r="O23" t="n">
-        <v>1.93</v>
+        <v>3.75</v>
       </c>
       <c r="P23" t="n">
-        <v>8.75</v>
+        <v>2.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>4.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>8</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['28', '58']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>7.9</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>['14']</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>['61']</t>
-        </is>
-      </c>
-      <c r="AL23" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK23" s="3" t="n">
         <v>45863.64583333334</v>
       </c>
     </row>
@@ -3542,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3578,88 +3507,85 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N24" t="n">
         <v>3.3</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.94</v>
-      </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="P24" t="n">
-        <v>14.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.73</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="U24" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="V24" t="n">
-        <v>5.75</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>9</v>
+        <v>1.78</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.22</v>
+        <v>1.98</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AD24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['27', '55']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['81', '90+1', '87']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>2.5</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>['28', '58']</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>['33']</t>
-        </is>
-      </c>
-      <c r="AL24" s="3" t="n">
+      <c r="AK24" s="3" t="n">
         <v>45863.64583333334</v>
       </c>
     </row>
@@ -3674,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,114 +3610,111 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P25" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="V25" t="n">
-        <v>5.1</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>1.71</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.14</v>
+        <v>2.03</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.4</v>
+        <v>2.74</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['59', '74']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['31', '47', '72', '77']</t>
+        </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.5</v>
+        <v>1.85</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>['2', '30', '62']</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>['50', '86']</t>
-        </is>
-      </c>
-      <c r="AL25" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK25" s="3" t="n">
         <v>45863.65625</v>
       </c>
     </row>
@@ -3806,32 +3729,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3842,88 +3765,85 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.07</v>
+        <v>1.34</v>
       </c>
       <c r="M26" t="n">
-        <v>3.34</v>
+        <v>4.75</v>
       </c>
       <c r="N26" t="n">
-        <v>2.02</v>
+        <v>7.8</v>
       </c>
       <c r="O26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z26" t="n">
         <v>2.25</v>
       </c>
-      <c r="P26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="AA26" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.5</v>
       </c>
-      <c r="V26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC26" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['2', '30', '62']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['50', '86']</t>
+        </is>
       </c>
       <c r="AG26" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>5.75</v>
+        <v>3.15</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
-      <c r="AL26" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK26" s="3" t="n">
         <v>45863.65625</v>
       </c>
     </row>
@@ -3938,35 +3858,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3974,88 +3894,85 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.8</v>
+        <v>3.07</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>2.02</v>
       </c>
       <c r="O27" t="n">
-        <v>1.53</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>13</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
         <v>2.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA27" t="n">
         <v>3</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V27" t="n">
-        <v>6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
       </c>
       <c r="AG27" t="n">
-        <v>2.19</v>
+        <v>1.68</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.75</v>
+        <v>1.34</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>['59', '74']</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>['31', '47', '72', '77']</t>
-        </is>
-      </c>
-      <c r="AL27" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK27" s="3" t="n">
         <v>45863.65625</v>
       </c>
     </row>
@@ -4070,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4106,88 +4023,85 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="P28" t="n">
-        <v>13.5</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['7', '56']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['60', '79', '89']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI28" t="n">
         <v>1.67</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>['26', '28']</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>['62', '63']</t>
-        </is>
-      </c>
-      <c r="AL28" s="3" t="n">
+      <c r="AJ28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK28" s="3" t="n">
         <v>45863.65625</v>
       </c>
     </row>
@@ -4247,13 +4161,13 @@
         <v>1.8</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="P29" t="n">
-        <v>14.5</v>
+        <v>2.07</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="R29" t="n">
         <v>1.4</v>
@@ -4268,58 +4182,55 @@
         <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>6.9</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.5</v>
+        <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['38', '66']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['20', '39']</t>
+        </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.92</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>6.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>['38', '66']</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>['20', '39']</t>
-        </is>
-      </c>
-      <c r="AL29" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK29" s="3" t="n">
         <v>45863.65625</v>
       </c>
     </row>
@@ -4334,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4370,88 +4281,85 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD30" t="n">
         <v>2.25</v>
       </c>
-      <c r="M30" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['26', '28']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['62', '63']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI30" t="n">
         <v>2.3</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V30" t="n">
-        <v>10</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>['45+5']</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="AL30" s="3" t="n">
+      <c r="AJ30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK30" s="3" t="n">
         <v>45863.65625</v>
       </c>
     </row>
@@ -4466,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4502,88 +4410,85 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>2.9</v>
+        <v>1.96</v>
       </c>
       <c r="O31" t="n">
-        <v>1.67</v>
+        <v>3.85</v>
       </c>
       <c r="P31" t="n">
-        <v>11.75</v>
+        <v>2.18</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="R31" t="n">
         <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="T31" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>6.2</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>3.41</v>
       </c>
       <c r="Y31" t="n">
-        <v>8.75</v>
+        <v>1.95</v>
       </c>
       <c r="Z31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.29</v>
       </c>
-      <c r="AA31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AC31" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['25', '45+3', '54']</t>
+        </is>
       </c>
       <c r="AG31" t="n">
-        <v>2.05</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>6.4</v>
+        <v>1.27</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>['7', '56']</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>['60', '79', '89']</t>
-        </is>
-      </c>
-      <c r="AL31" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK31" s="3" t="n">
         <v>45863.65625</v>
       </c>
     </row>
@@ -4598,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,114 +4513,111 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M32" t="n">
         <v>3</v>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T32" t="n">
         <v>3.3</v>
       </c>
-      <c r="N32" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.88</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V32" t="n">
-        <v>6.9</v>
+        <v>1.07</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.43</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>2.55</v>
       </c>
       <c r="Y32" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.41</v>
+        <v>4.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>1.2</v>
       </c>
       <c r="AC32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF32" t="n">
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['45+5']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.83</v>
       </c>
-      <c r="AG32" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>['25', '45+3', '54']</t>
-        </is>
-      </c>
-      <c r="AL32" s="3" t="n">
+      <c r="AJ32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK32" s="3" t="n">
         <v>45863.65625</v>
       </c>
     </row>
@@ -4730,124 +4632,121 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>0</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>['16', '87']</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>['27', '50', '72']</t>
-        </is>
-      </c>
-      <c r="AL33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3" t="n">
         <v>45863.66666666666</v>
       </c>
     </row>
@@ -4862,124 +4761,121 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q34" t="n">
         <v>3.8</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="P34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['16', '87']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['27', '50', '72']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.62</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V34" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>7.1</v>
-      </c>
       <c r="AI34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL34" s="3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK34" s="3" t="n">
         <v>45863.66666666666</v>
       </c>
     </row>
@@ -4994,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,114 +4900,111 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.95</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['7', '88']</t>
+        </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL35" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK35" s="3" t="n">
         <v>45863.79166666666</v>
       </c>
     </row>
@@ -5126,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,114 +5029,111 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.81</v>
+        <v>0</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>['7', '88']</t>
-        </is>
-      </c>
-      <c r="AL36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="3" t="n">
         <v>45863.79166666666</v>
       </c>
     </row>
@@ -5280,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -5290,7 +5180,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -5303,13 +5193,13 @@
         <v>3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="P37" t="n">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.25</v>
+        <v>3.45</v>
       </c>
       <c r="R37" t="n">
         <v>1.38</v>
@@ -5324,58 +5214,55 @@
         <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>1.05</v>
       </c>
       <c r="W37" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>3.35</v>
       </c>
       <c r="Y37" t="n">
-        <v>8.5</v>
+        <v>1.91</v>
       </c>
       <c r="Z37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB37" t="n">
         <v>1.3</v>
       </c>
-      <c r="AA37" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AC37" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.67</v>
+        <v>2</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
       </c>
       <c r="AG37" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AH37" t="n">
-        <v>5.8</v>
+        <v>1.62</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL37" s="3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK37" s="3" t="n">
         <v>45863.83333333334</v>
       </c>
     </row>
@@ -5409,20 +5296,20 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -5435,13 +5322,13 @@
         <v>3.64</v>
       </c>
       <c r="O38" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="P38" t="n">
-        <v>13</v>
+        <v>2.35</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
         <v>1.28</v>
@@ -5456,58 +5343,55 @@
         <v>1.55</v>
       </c>
       <c r="V38" t="n">
-        <v>5.25</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>4.33</v>
       </c>
       <c r="Y38" t="n">
-        <v>10</v>
+        <v>1.58</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.2</v>
+        <v>2.22</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.33</v>
+        <v>2.62</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.22</v>
+        <v>1.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['9', '36', '90+5']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI38" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL38" s="3" t="n">
+      <c r="AJ38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK38" s="3" t="n">
         <v>45863.85416666666</v>
       </c>
     </row>
@@ -5517,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,115 +5416,112 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="O39" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="P39" t="n">
-        <v>17</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S39" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V39" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="W39" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>17</v>
+        <v>1.37</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.17</v>
+        <v>2.62</v>
       </c>
       <c r="AA39" t="n">
-        <v>5</v>
+        <v>1.93</v>
       </c>
       <c r="AB39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC39" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC39" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AD39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['43', '31', '62', '77']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AI39" t="n">
         <v>1.44</v>
       </c>
-      <c r="AG39" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL39" s="3" t="n">
-        <v>45863.85416666666</v>
+      <c r="AJ39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK39" s="3" t="n">
+        <v>45863.875</v>
       </c>
     </row>
     <row r="40">
@@ -5654,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,114 +5545,111 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N40" t="n">
         <v>4</v>
       </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="O40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD40" t="n">
         <v>2</v>
       </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N40" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S40" t="n">
-        <v>4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.53</v>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['27', '78']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['37', '46']</t>
+        </is>
       </c>
       <c r="AG40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>['43', '31', '62', '77']</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL40" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK40" s="3" t="n">
         <v>45863.875</v>
       </c>
     </row>
@@ -5805,7 +5683,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -5818,92 +5696,89 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="M41" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N41" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O41" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="P41" t="n">
-        <v>5</v>
+        <v>1.76</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.2</v>
+        <v>3.96</v>
       </c>
       <c r="R41" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="S41" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="T41" t="n">
         <v>4.4</v>
       </c>
       <c r="U41" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="V41" t="n">
-        <v>12.5</v>
+        <v>1.17</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="X41" t="n">
-        <v>1.14</v>
+        <v>1.96</v>
       </c>
       <c r="Y41" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.01</v>
+        <v>6.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>3.3</v>
+        <v>1.08</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH41" t="n">
-        <v>13</v>
+        <v>1.36</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL41" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK41" s="3" t="n">
         <v>45863.88194444445</v>
       </c>
     </row>
@@ -6010,11 +5885,15 @@
       <c r="AD42" t="n">
         <v>0</v>
       </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -6025,17 +5904,10 @@
       <c r="AI42" t="n">
         <v>0</v>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL42" s="3" t="n">
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
         <v>45863.88541666666</v>
       </c>
     </row>
@@ -6142,11 +6014,15 @@
       <c r="AD43" t="n">
         <v>0</v>
       </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -6157,17 +6033,10 @@
       <c r="AI43" t="n">
         <v>0</v>
       </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL43" s="3" t="n">
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3" t="n">
         <v>45863.88541666666</v>
       </c>
     </row>
@@ -6192,114 +6061,111 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.96</v>
+        <v>2.37</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="O44" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y44" t="n">
         <v>1.72</v>
       </c>
-      <c r="P44" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q44" t="n">
+      <c r="Z44" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD44" t="n">
         <v>2.2</v>
       </c>
-      <c r="R44" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V44" t="n">
-        <v>5</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.51</v>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['15', '17', '45+8']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>['11', '22', '46', '84']</t>
+        </is>
       </c>
       <c r="AG44" t="n">
-        <v>2.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>4.33</v>
+        <v>1.49</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3" t="n">
         <v>45863.89583333334</v>
       </c>
     </row>
@@ -6324,19 +6190,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -6346,92 +6212,89 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="M45" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="N45" t="n">
-        <v>2.54</v>
+        <v>3.45</v>
       </c>
       <c r="O45" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="P45" t="n">
-        <v>11.5</v>
+        <v>2.51</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>3.55</v>
       </c>
       <c r="R45" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S45" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T45" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="U45" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC45" t="n">
         <v>1.5</v>
       </c>
-      <c r="V45" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AD45" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>['76', '79', '90+6']</t>
+        </is>
       </c>
       <c r="AG45" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>4.5</v>
+        <v>1.72</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3" t="n">
         <v>45863.89583333334</v>
       </c>
     </row>
@@ -6446,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6478,92 +6341,89 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="M46" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N46" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q46" t="n">
         <v>3.5</v>
       </c>
-      <c r="O46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2</v>
-      </c>
       <c r="R46" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S46" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T46" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="U46" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X46" t="n">
         <v>4.5</v>
       </c>
-      <c r="W46" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1</v>
-      </c>
       <c r="Y46" t="n">
-        <v>12</v>
+        <v>1.64</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.14</v>
+        <v>2.27</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.19</v>
+        <v>1.47</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG46" t="n">
-        <v>2.38</v>
+        <v>1.35</v>
       </c>
       <c r="AH46" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3" t="n">
         <v>45863.89583333334</v>
       </c>
     </row>
@@ -6573,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,115 +6448,112 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>2.63</v>
+        <v>3.65</v>
       </c>
       <c r="N47" t="n">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="P47" t="n">
-        <v>4.75</v>
+        <v>2.21</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="R47" t="n">
-        <v>1.71</v>
+        <v>1.27</v>
       </c>
       <c r="S47" t="n">
-        <v>1.98</v>
+        <v>3.3</v>
       </c>
       <c r="T47" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="U47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>1.14</v>
       </c>
-      <c r="V47" t="n">
-        <v>10</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X47" t="n">
-        <v>1.19</v>
+        <v>4.4</v>
       </c>
       <c r="Y47" t="n">
-        <v>4.33</v>
+        <v>1.64</v>
       </c>
       <c r="Z47" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>['35', '42']</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI47" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA47" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL47" s="3" t="n">
-        <v>45863.91666666666</v>
+      <c r="AJ47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK47" s="3" t="n">
+        <v>45863.89583333334</v>
       </c>
     </row>
     <row r="48">
@@ -6705,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-       